--- a/countries/de/2026-2029.xlsx
+++ b/countries/de/2026-2029.xlsx
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2797562027509408</v>
+        <v>0.2809517420789363</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O33" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3287733151987552</v>
+        <v>0.3299688545267507</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -10120,13 +10120,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="O67" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="R67" t="n">
-        <v>2.024048082296336</v>
+        <v>2.025243621624332</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O147" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R147" t="n">
-        <v>0.08607883161567409</v>
+        <v>0.08727437094366955</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -30856,13 +30856,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="O211" t="n">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="R211" t="n">
-        <v>1.782549138041251</v>
+        <v>1.783744677369246</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -32296,13 +32296,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O221" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="R221" t="n">
-        <v>0.4829978885101712</v>
+        <v>0.4841934278381667</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -32728,13 +32728,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O224" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R224" t="n">
-        <v>0.4686514165742255</v>
+        <v>0.4710424952302165</v>
       </c>
       <c r="U224" t="inlineStr">
         <is>
@@ -35752,13 +35752,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O245" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R245" t="n">
-        <v>0.0812966743036922</v>
+        <v>0.08249221363168767</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -39064,13 +39064,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O268" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R268" t="n">
-        <v>0.5033220570860943</v>
+        <v>0.5045175964140898</v>
       </c>
       <c r="U268" t="inlineStr">
         <is>
@@ -39208,13 +39208,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O269" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R269" t="n">
-        <v>0.2426944835830811</v>
+        <v>0.2438900229110766</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -39496,13 +39496,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O271" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R271" t="n">
-        <v>0.008368775295968314</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
@@ -40360,13 +40360,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O277" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R277" t="n">
-        <v>0.292907135358891</v>
+        <v>0.2941026746868864</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -43528,13 +43528,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="O299" t="n">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="R299" t="n">
-        <v>1.755051733497355</v>
+        <v>1.757442812153346</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
@@ -45544,13 +45544,13 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O313" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R313" t="n">
-        <v>0.2546498768630359</v>
+        <v>0.2570409555190268</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
@@ -46984,13 +46984,13 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O323" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R323" t="n">
-        <v>0.3072536072948367</v>
+        <v>0.3084491466228322</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
@@ -47272,13 +47272,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O325" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R325" t="n">
-        <v>0.0179330899199321</v>
+        <v>0.01912862924792757</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
@@ -47992,13 +47992,13 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O330" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R330" t="n">
-        <v>0.1374870227194794</v>
+        <v>0.1386825620474749</v>
       </c>
       <c r="U330" t="inlineStr">
         <is>
@@ -52024,13 +52024,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O358" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R358" t="n">
-        <v>0.2187836970231716</v>
+        <v>0.2199792363511671</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
@@ -53176,13 +53176,13 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O366" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R366" t="n">
-        <v>0.007173235967972841</v>
+        <v>0.008368775295968314</v>
       </c>
       <c r="U366" t="inlineStr">
         <is>
@@ -53320,13 +53320,13 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O367" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R367" t="n">
-        <v>0.2510632588790494</v>
+        <v>0.2522587982070449</v>
       </c>
       <c r="U367" t="inlineStr">
         <is>
@@ -53752,13 +53752,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="O370" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="R370" t="n">
-        <v>0.4889755851501486</v>
+        <v>0.4865845064941577</v>
       </c>
       <c r="U370" t="inlineStr">
         <is>
@@ -54184,13 +54184,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O373" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R373" t="n">
-        <v>0.1530290339834206</v>
+        <v>0.1518334946554251</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -54328,13 +54328,13 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O374" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="R374" t="n">
-        <v>0.1374870227194794</v>
+        <v>0.1398781013754704</v>
       </c>
       <c r="U374" t="inlineStr">
         <is>
@@ -55307,17 +55307,17 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
@@ -55336,17 +55336,17 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O381" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R381" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U381" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_ca130aab0bf5860c8f5942f9a84e</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -55366,7 +55366,7 @@
       </c>
       <c r="AS381" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_ca130aab0bf5860c8f5942f9a84e</t>
         </is>
       </c>
       <c r="AT381" t="n">
@@ -55451,22 +55451,22 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -55480,17 +55480,17 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="O382" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="R382" t="n">
-        <v>0.02749740454389589</v>
+        <v>0.009564314623963786</v>
       </c>
       <c r="U382" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -55510,7 +55510,7 @@
       </c>
       <c r="AS382" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AT382" t="n">
@@ -55595,22 +55595,22 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -55624,17 +55624,17 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="O383" t="n">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="R383" t="n">
-        <v>0.3801815063025605</v>
+        <v>0.02749740454389589</v>
       </c>
       <c r="U383" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -55654,7 +55654,7 @@
       </c>
       <c r="AS383" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT383" t="n">
@@ -55739,17 +55739,17 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -55768,17 +55768,17 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>3</v>
+        <v>318</v>
       </c>
       <c r="O384" t="n">
-        <v>3</v>
+        <v>318</v>
       </c>
       <c r="R384" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.3801815063025605</v>
       </c>
       <c r="U384" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -55798,7 +55798,7 @@
       </c>
       <c r="AS384" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT384" t="n">
@@ -55883,17 +55883,17 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -55912,17 +55912,17 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R385" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U385" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -55942,7 +55942,7 @@
       </c>
       <c r="AS385" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT385" t="n">
@@ -56027,17 +56027,17 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -56056,17 +56056,17 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="O386" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="R386" t="n">
-        <v>0.2905160567029</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U386" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -56086,7 +56086,7 @@
       </c>
       <c r="AS386" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AT386" t="n">
@@ -56171,17 +56171,17 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -56200,17 +56200,17 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="O387" t="n">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="R387" t="n">
-        <v>0.02869294387189136</v>
+        <v>0.2905160567029</v>
       </c>
       <c r="U387" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -56230,7 +56230,7 @@
       </c>
       <c r="AS387" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT387" t="n">
@@ -56315,17 +56315,17 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>D089</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>Arboviral diseases</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>虫媒病毒病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -56344,17 +56344,17 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O388" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R388" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.02869294387189136</v>
       </c>
       <c r="U388" t="inlineStr">
         <is>
-          <t>HOLD_DE_cc965d367599c3748e02fe739b89</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -56374,7 +56374,7 @@
       </c>
       <c r="AS388" t="inlineStr">
         <is>
-          <t>HOLD_DE_cc965d367599c3748e02fe739b89</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT388" t="n">
@@ -56459,22 +56459,22 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>D091</t>
+          <t>D089</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Arboviral diseases</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>肉毒杆菌中毒</t>
+          <t>虫媒病毒病</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -56498,7 +56498,7 @@
       </c>
       <c r="U389" t="inlineStr">
         <is>
-          <t>HOLD_DE_0ad808f22f487dc25a3c1ca78c80</t>
+          <t>HOLD_DE_cc965d367599c3748e02fe739b89</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -56518,7 +56518,7 @@
       </c>
       <c r="AS389" t="inlineStr">
         <is>
-          <t>HOLD_DE_0ad808f22f487dc25a3c1ca78c80</t>
+          <t>HOLD_DE_cc965d367599c3748e02fe739b89</t>
         </is>
       </c>
       <c r="AT389" t="n">
@@ -56603,17 +56603,17 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D091</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Botulism</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>肉毒杆菌中毒</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -56632,17 +56632,17 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>1246</v>
+        <v>1</v>
       </c>
       <c r="O390" t="n">
-        <v>1246</v>
+        <v>1</v>
       </c>
       <c r="R390" t="n">
-        <v>1.48964200268236</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U390" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_0ad808f22f487dc25a3c1ca78c80</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -56662,7 +56662,7 @@
       </c>
       <c r="AS390" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_0ad808f22f487dc25a3c1ca78c80</t>
         </is>
       </c>
       <c r="AT390" t="n">
@@ -56747,22 +56747,22 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -56776,17 +56776,17 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>65</v>
+        <v>1248</v>
       </c>
       <c r="O391" t="n">
-        <v>65</v>
+        <v>1248</v>
       </c>
       <c r="R391" t="n">
-        <v>0.07771005631970578</v>
+        <v>1.492033081338351</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
@@ -56806,7 +56806,7 @@
       </c>
       <c r="AS391" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT391" t="n">
@@ -56891,17 +56891,17 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -56920,17 +56920,17 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="O392" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R392" t="n">
-        <v>0.0896654495996605</v>
+        <v>0.07771005631970578</v>
       </c>
       <c r="U392" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -56950,7 +56950,7 @@
       </c>
       <c r="AS392" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT392" t="n">
@@ -57035,22 +57035,22 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>D101</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Candida auris infection</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>耳念珠菌感染</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Fungal</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -57064,17 +57064,17 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="O393" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="R393" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.0896654495996605</v>
       </c>
       <c r="U393" t="inlineStr">
         <is>
-          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
@@ -57094,7 +57094,7 @@
       </c>
       <c r="AS393" t="inlineStr">
         <is>
-          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT393" t="n">
@@ -57179,22 +57179,22 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Candida auris infection</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>耳念珠菌感染</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -57208,17 +57208,17 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O394" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R394" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U394" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
@@ -57238,7 +57238,7 @@
       </c>
       <c r="AS394" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
         </is>
       </c>
       <c r="AT394" t="n">
@@ -57323,22 +57323,22 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -57352,17 +57352,17 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O395" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R395" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U395" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
@@ -57382,7 +57382,7 @@
       </c>
       <c r="AS395" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT395" t="n">
@@ -57467,17 +57467,17 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -57496,17 +57496,17 @@
         </is>
       </c>
       <c r="N396" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="O396" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="R396" t="n">
-        <v>0.11357623615957</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U396" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
@@ -57526,7 +57526,7 @@
       </c>
       <c r="AS396" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT396" t="n">
@@ -57611,17 +57611,17 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -57640,17 +57640,17 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="O397" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="R397" t="n">
-        <v>0.1291182474235111</v>
+        <v>0.11357623615957</v>
       </c>
       <c r="U397" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
@@ -57670,7 +57670,7 @@
       </c>
       <c r="AS397" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT397" t="n">
@@ -57755,17 +57755,17 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -57784,17 +57784,17 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="O398" t="n">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="R398" t="n">
-        <v>0.07412343833571934</v>
+        <v>0.1291182474235111</v>
       </c>
       <c r="U398" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
@@ -57814,7 +57814,7 @@
       </c>
       <c r="AS398" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT398" t="n">
@@ -57899,17 +57899,17 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -57928,17 +57928,17 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="O399" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="R399" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.07412343833571934</v>
       </c>
       <c r="U399" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
@@ -57958,7 +57958,7 @@
       </c>
       <c r="AS399" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT399" t="n">
@@ -58043,17 +58043,17 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -58072,17 +58072,17 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>263</v>
+        <v>12</v>
       </c>
       <c r="O400" t="n">
-        <v>263</v>
+        <v>12</v>
       </c>
       <c r="R400" t="n">
-        <v>0.3144268432628095</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U400" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
@@ -58102,7 +58102,7 @@
       </c>
       <c r="AS400" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT400" t="n">
@@ -58187,17 +58187,17 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -58216,17 +58216,17 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="O401" t="n">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="R401" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.315622382590805</v>
       </c>
       <c r="U401" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
@@ -58246,7 +58246,7 @@
       </c>
       <c r="AS401" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT401" t="n">
@@ -58331,17 +58331,17 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -58360,17 +58360,17 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O402" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R402" t="n">
-        <v>0.007173235967972841</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U402" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA402" t="inlineStr">
@@ -58390,7 +58390,7 @@
       </c>
       <c r="AS402" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT402" t="n">
@@ -58475,17 +58475,17 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -58504,17 +58504,17 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>384</v>
+        <v>6</v>
       </c>
       <c r="O403" t="n">
-        <v>384</v>
+        <v>6</v>
       </c>
       <c r="R403" t="n">
-        <v>0.4590871019502618</v>
+        <v>0.007173235967972841</v>
       </c>
       <c r="U403" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA403" t="inlineStr">
@@ -58534,7 +58534,7 @@
       </c>
       <c r="AS403" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT403" t="n">
@@ -58619,17 +58619,17 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -58648,17 +58648,17 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>204</v>
+        <v>387</v>
       </c>
       <c r="O404" t="n">
-        <v>204</v>
+        <v>387</v>
       </c>
       <c r="R404" t="n">
-        <v>0.2438900229110766</v>
+        <v>0.4626737199342482</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
@@ -58678,7 +58678,7 @@
       </c>
       <c r="AS404" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT404" t="n">
@@ -58763,17 +58763,17 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -58792,17 +58792,17 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="O405" t="n">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="R405" t="n">
-        <v>0.008368775295968314</v>
+        <v>0.2438900229110766</v>
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA405" t="inlineStr">
@@ -58822,7 +58822,7 @@
       </c>
       <c r="AS405" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT405" t="n">
@@ -58907,17 +58907,17 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -58936,17 +58936,17 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O406" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R406" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.008368775295968314</v>
       </c>
       <c r="U406" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
@@ -58966,7 +58966,7 @@
       </c>
       <c r="AS406" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT406" t="n">
@@ -59051,17 +59051,17 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -59080,17 +59080,17 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O407" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R407" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA407" t="inlineStr">
@@ -59110,7 +59110,7 @@
       </c>
       <c r="AS407" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT407" t="n">
@@ -59195,22 +59195,22 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -59224,17 +59224,17 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O408" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R408" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U408" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA408" t="inlineStr">
@@ -59254,7 +59254,7 @@
       </c>
       <c r="AS408" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT408" t="n">
@@ -59339,17 +59339,17 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>D137</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>Epidemic keratoconjunctivitis</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>流行性角结膜炎</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -59368,17 +59368,17 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O409" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R409" t="n">
-        <v>0.005977696639977366</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U409" t="inlineStr">
         <is>
-          <t>HOLD_DE_4453676e0c9e3e23d4fae9a7449b</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA409" t="inlineStr">
@@ -59398,7 +59398,7 @@
       </c>
       <c r="AS409" t="inlineStr">
         <is>
-          <t>HOLD_DE_4453676e0c9e3e23d4fae9a7449b</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AT409" t="n">
@@ -59483,17 +59483,17 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D137</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Epidemic keratoconjunctivitis</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>流行性角结膜炎</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -59512,17 +59512,17 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="O410" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R410" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.005977696639977366</v>
       </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_4453676e0c9e3e23d4fae9a7449b</t>
         </is>
       </c>
       <c r="AA410" t="inlineStr">
@@ -59542,7 +59542,7 @@
       </c>
       <c r="AS410" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_4453676e0c9e3e23d4fae9a7449b</t>
         </is>
       </c>
       <c r="AT410" t="n">
@@ -59627,22 +59627,22 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -59656,17 +59656,17 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="O411" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="R411" t="n">
-        <v>0.07651451699171029</v>
+        <v>0.02032416857592305</v>
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA411" t="inlineStr">
@@ -59686,7 +59686,7 @@
       </c>
       <c r="AS411" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT411" t="n">
@@ -59771,22 +59771,22 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -59800,17 +59800,17 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>212</v>
+        <v>64</v>
       </c>
       <c r="O412" t="n">
-        <v>212</v>
+        <v>64</v>
       </c>
       <c r="R412" t="n">
-        <v>0.2534543375350404</v>
+        <v>0.07651451699171029</v>
       </c>
       <c r="U412" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA412" t="inlineStr">
@@ -59830,7 +59830,7 @@
       </c>
       <c r="AS412" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT412" t="n">
@@ -59915,17 +59915,17 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -59944,17 +59944,17 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="O413" t="n">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="R413" t="n">
-        <v>0.01075985395195926</v>
+        <v>0.2534543375350404</v>
       </c>
       <c r="U413" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA413" t="inlineStr">
@@ -59974,7 +59974,7 @@
       </c>
       <c r="AS413" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT413" t="n">
@@ -60059,22 +60059,22 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -60088,17 +60088,17 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="O414" t="n">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="R414" t="n">
-        <v>0.2307390903031264</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -60118,7 +60118,7 @@
       </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT414" t="n">
@@ -60203,17 +60203,17 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>D234</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>副伤寒</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -60232,17 +60232,17 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="O415" t="n">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="R415" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.2307390903031264</v>
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA415" t="inlineStr">
@@ -60262,7 +60262,7 @@
       </c>
       <c r="AS415" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT415" t="n">
@@ -60347,17 +60347,17 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D234</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>副伤寒</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -60376,17 +60376,17 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="O416" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="R416" t="n">
-        <v>0.0406483371518461</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
@@ -60406,7 +60406,7 @@
       </c>
       <c r="AS416" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AT416" t="n">
@@ -60491,27 +60491,27 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D236</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -60520,17 +60520,17 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>598</v>
+        <v>34</v>
       </c>
       <c r="O417" t="n">
-        <v>598</v>
+        <v>34</v>
       </c>
       <c r="R417" t="n">
-        <v>0.7149325181412931</v>
+        <v>0.0406483371518461</v>
       </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AA417" t="inlineStr">
@@ -60550,7 +60550,7 @@
       </c>
       <c r="AS417" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AT417" t="n">
@@ -60635,17 +60635,17 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -60664,17 +60664,17 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>40</v>
+        <v>597</v>
       </c>
       <c r="O418" t="n">
-        <v>40</v>
+        <v>597</v>
       </c>
       <c r="R418" t="n">
-        <v>0.04782157311981893</v>
+        <v>0.7137369788132977</v>
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AA418" t="inlineStr">
@@ -60694,7 +60694,7 @@
       </c>
       <c r="AS418" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AT418" t="n">
@@ -60779,17 +60779,17 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>D008</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>乙型肝炎</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -60808,17 +60808,17 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="O419" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="R419" t="n">
-        <v>0.2988848319988684</v>
+        <v>0.04782157311981893</v>
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AA419" t="inlineStr">
@@ -60838,7 +60838,7 @@
       </c>
       <c r="AS419" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AT419" t="n">
@@ -60923,17 +60923,17 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -60952,17 +60952,17 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="O420" t="n">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="R420" t="n">
-        <v>0.136291483391484</v>
+        <v>0.2976892926708729</v>
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
@@ -60982,7 +60982,7 @@
       </c>
       <c r="AS420" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AT420" t="n">
@@ -61067,17 +61067,17 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -61096,17 +61096,17 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O421" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="R421" t="n">
-        <v>0.1279227080955156</v>
+        <v>0.1350959440634885</v>
       </c>
       <c r="U421" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AA421" t="inlineStr">
@@ -61126,7 +61126,7 @@
       </c>
       <c r="AS421" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AT421" t="n">
@@ -61211,17 +61211,17 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -61240,17 +61240,17 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="O422" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="R422" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.1279227080955156</v>
       </c>
       <c r="U422" t="inlineStr">
         <is>
-          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AA422" t="inlineStr">
@@ -61270,7 +61270,7 @@
       </c>
       <c r="AS422" t="inlineStr">
         <is>
-          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AT422" t="n">
@@ -61355,17 +61355,17 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -61384,17 +61384,17 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O423" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R423" t="n">
-        <v>0.01554201126394116</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U423" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
         </is>
       </c>
       <c r="AA423" t="inlineStr">
@@ -61414,7 +61414,7 @@
       </c>
       <c r="AS423" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
         </is>
       </c>
       <c r="AT423" t="n">
@@ -61499,22 +61499,22 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -61528,17 +61528,17 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="O424" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="R424" t="n">
-        <v>0.05738588774378273</v>
+        <v>0.01554201126394116</v>
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
@@ -61558,7 +61558,7 @@
       </c>
       <c r="AS424" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AT424" t="n">
@@ -61643,17 +61643,17 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -61672,17 +61672,17 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>378</v>
+        <v>48</v>
       </c>
       <c r="O425" t="n">
-        <v>378</v>
+        <v>48</v>
       </c>
       <c r="R425" t="n">
-        <v>0.4519138659822889</v>
+        <v>0.05738588774378273</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AA425" t="inlineStr">
@@ -61702,7 +61702,7 @@
       </c>
       <c r="AS425" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT425" t="n">
@@ -61787,17 +61787,17 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Scarlet fever</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>猩红热</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -61816,17 +61816,17 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>4</v>
+        <v>379</v>
       </c>
       <c r="O426" t="n">
-        <v>4</v>
+        <v>379</v>
       </c>
       <c r="R426" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.4531094053102844</v>
       </c>
       <c r="U426" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AA426" t="inlineStr">
@@ -61846,7 +61846,7 @@
       </c>
       <c r="AS426" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AT426" t="n">
@@ -61931,17 +61931,17 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -61960,17 +61960,17 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R427" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U427" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AA427" t="inlineStr">
@@ -61990,7 +61990,7 @@
       </c>
       <c r="AS427" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AT427" t="n">
@@ -62075,22 +62075,22 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Scarlet fever</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>猩红热</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -62104,17 +62104,17 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="O428" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R428" t="n">
-        <v>0.022715247231914</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U428" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AA428" t="inlineStr">
@@ -62134,7 +62134,7 @@
       </c>
       <c r="AS428" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AT428" t="n">
@@ -62219,22 +62219,22 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -62248,17 +62248,17 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>469</v>
+        <v>3</v>
       </c>
       <c r="O429" t="n">
-        <v>469</v>
+        <v>3</v>
       </c>
       <c r="R429" t="n">
-        <v>0.5607079448298771</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
@@ -62278,7 +62278,7 @@
       </c>
       <c r="AS429" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AT429" t="n">
@@ -62363,22 +62363,22 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -62392,17 +62392,17 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O430" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R430" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.022715247231914</v>
       </c>
       <c r="U430" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA430" t="inlineStr">
@@ -62422,7 +62422,7 @@
       </c>
       <c r="AS430" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT430" t="n">
@@ -62507,17 +62507,17 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -62536,17 +62536,17 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="O431" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="R431" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.5607079448298771</v>
       </c>
       <c r="U431" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA431" t="inlineStr">
@@ -62566,7 +62566,7 @@
       </c>
       <c r="AS431" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT431" t="n">
@@ -62651,17 +62651,17 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -62680,17 +62680,17 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>276</v>
+        <v>8</v>
       </c>
       <c r="O432" t="n">
-        <v>276</v>
+        <v>8</v>
       </c>
       <c r="R432" t="n">
-        <v>0.3299688545267507</v>
+        <v>0.009564314623963786</v>
       </c>
       <c r="U432" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA432" t="inlineStr">
@@ -62710,7 +62710,7 @@
       </c>
       <c r="AS432" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT432" t="n">
@@ -62795,17 +62795,17 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -62824,17 +62824,17 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O433" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="R433" t="n">
-        <v>0.04184387647984157</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U433" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AA433" t="inlineStr">
@@ -62854,7 +62854,7 @@
       </c>
       <c r="AS433" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AT433" t="n">
@@ -62939,22 +62939,22 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>D085</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Toxoplasmosis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>弓形体病</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -62968,17 +62968,17 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="O434" t="n">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="R434" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.3299688545267507</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
@@ -62998,7 +62998,7 @@
       </c>
       <c r="AS434" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT434" t="n">
@@ -63083,22 +63083,22 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -63112,17 +63112,17 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>1159</v>
+        <v>35</v>
       </c>
       <c r="O435" t="n">
-        <v>1159</v>
+        <v>35</v>
       </c>
       <c r="R435" t="n">
-        <v>1.385630081146754</v>
+        <v>0.04184387647984157</v>
       </c>
       <c r="U435" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA435" t="inlineStr">
@@ -63142,7 +63142,7 @@
       </c>
       <c r="AS435" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT435" t="n">
@@ -63227,17 +63227,17 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D085</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>弓形体病</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -63256,17 +63256,17 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="O436" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="R436" t="n">
-        <v>0.07173235967972839</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U436" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA436" t="inlineStr">
@@ -63286,7 +63286,7 @@
       </c>
       <c r="AS436" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT436" t="n">
@@ -63371,22 +63371,22 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -63400,17 +63400,17 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>64</v>
+        <v>1168</v>
       </c>
       <c r="O437" t="n">
-        <v>64</v>
+        <v>1168</v>
       </c>
       <c r="R437" t="n">
-        <v>0.07651451699171029</v>
+        <v>1.396389935098713</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA437" t="inlineStr">
@@ -63430,7 +63430,7 @@
       </c>
       <c r="AS437" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT437" t="n">
@@ -63515,22 +63515,22 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -63544,17 +63544,17 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="O438" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="R438" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.07173235967972839</v>
       </c>
       <c r="U438" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA438" t="inlineStr">
@@ -63574,7 +63574,7 @@
       </c>
       <c r="AS438" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT438" t="n">
@@ -63659,22 +63659,22 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -63688,17 +63688,17 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="O439" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="R439" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.07651451699171029</v>
       </c>
       <c r="U439" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA439" t="inlineStr">
@@ -63718,7 +63718,7 @@
       </c>
       <c r="AS439" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT439" t="n">
@@ -63803,22 +63803,22 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -63832,17 +63832,17 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="O440" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="R440" t="n">
-        <v>0.1052074608636017</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA440" t="inlineStr">
@@ -63862,7 +63862,7 @@
       </c>
       <c r="AS440" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT440" t="n">
@@ -63947,17 +63947,17 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -63976,17 +63976,17 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="O441" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="R441" t="n">
-        <v>0.1434647193594568</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U441" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA441" t="inlineStr">
@@ -64006,7 +64006,7 @@
       </c>
       <c r="AS441" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT441" t="n">
@@ -64091,17 +64091,17 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -64120,17 +64120,17 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O442" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="R442" t="n">
-        <v>0.08488329228767862</v>
+        <v>0.1064030001915971</v>
       </c>
       <c r="U442" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA442" t="inlineStr">
@@ -64150,7 +64150,7 @@
       </c>
       <c r="AS442" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT442" t="n">
@@ -64235,17 +64235,17 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -64264,17 +64264,17 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="O443" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="R443" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.1434647193594568</v>
       </c>
       <c r="U443" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA443" t="inlineStr">
@@ -64294,7 +64294,7 @@
       </c>
       <c r="AS443" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT443" t="n">
@@ -64379,17 +64379,17 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -64408,17 +64408,17 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>242</v>
+        <v>71</v>
       </c>
       <c r="O444" t="n">
-        <v>242</v>
+        <v>71</v>
       </c>
       <c r="R444" t="n">
-        <v>0.2893205173749046</v>
+        <v>0.08488329228767862</v>
       </c>
       <c r="U444" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
@@ -64438,7 +64438,7 @@
       </c>
       <c r="AS444" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT444" t="n">
@@ -64523,17 +64523,17 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -64552,17 +64552,17 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O445" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R445" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.009564314623963786</v>
       </c>
       <c r="U445" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA445" t="inlineStr">
@@ -64582,7 +64582,7 @@
       </c>
       <c r="AS445" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT445" t="n">
@@ -64667,17 +64667,17 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -64696,17 +64696,17 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="O446" t="n">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="R446" t="n">
-        <v>0.01673755059193663</v>
+        <v>0.2893205173749046</v>
       </c>
       <c r="U446" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA446" t="inlineStr">
@@ -64726,7 +64726,7 @@
       </c>
       <c r="AS446" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT446" t="n">
@@ -64811,17 +64811,17 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -64840,17 +64840,17 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>329</v>
+        <v>2</v>
       </c>
       <c r="O447" t="n">
-        <v>329</v>
+        <v>2</v>
       </c>
       <c r="R447" t="n">
-        <v>0.3933324389105108</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U447" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
@@ -64870,7 +64870,7 @@
       </c>
       <c r="AS447" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT447" t="n">
@@ -64955,17 +64955,17 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -64984,17 +64984,17 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="O448" t="n">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="R448" t="n">
-        <v>0.202046146431235</v>
+        <v>0.01673755059193663</v>
       </c>
       <c r="U448" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
@@ -65014,7 +65014,7 @@
       </c>
       <c r="AS448" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT448" t="n">
@@ -65099,17 +65099,17 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
@@ -65128,17 +65128,17 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>4</v>
+        <v>328</v>
       </c>
       <c r="O449" t="n">
-        <v>4</v>
+        <v>328</v>
       </c>
       <c r="R449" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.3921368995825153</v>
       </c>
       <c r="U449" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
@@ -65158,7 +65158,7 @@
       </c>
       <c r="AS449" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT449" t="n">
@@ -65243,17 +65243,17 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
@@ -65272,17 +65272,17 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="O450" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="R450" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.202046146431235</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
@@ -65302,7 +65302,7 @@
       </c>
       <c r="AS450" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT450" t="n">
@@ -65387,17 +65387,17 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -65416,17 +65416,17 @@
         </is>
       </c>
       <c r="N451" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O451" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R451" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U451" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA451" t="inlineStr">
@@ -65446,7 +65446,7 @@
       </c>
       <c r="AS451" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT451" t="n">
@@ -65531,22 +65531,22 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="U452" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA452" t="inlineStr">
@@ -65590,7 +65590,7 @@
       </c>
       <c r="AS452" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT452" t="n">
@@ -65675,22 +65675,22 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -65704,17 +65704,17 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O453" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="R453" t="n">
-        <v>0.022715247231914</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U453" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA453" t="inlineStr">
@@ -65734,7 +65734,7 @@
       </c>
       <c r="AS453" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT453" t="n">
@@ -65819,22 +65819,22 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -65848,17 +65848,17 @@
         </is>
       </c>
       <c r="N454" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="O454" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="R454" t="n">
-        <v>0.05260373043180083</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U454" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA454" t="inlineStr">
@@ -65878,7 +65878,7 @@
       </c>
       <c r="AS454" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AT454" t="n">
@@ -65963,17 +65963,17 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
@@ -65992,17 +65992,17 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="O455" t="n">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="R455" t="n">
-        <v>0.2187836970231716</v>
+        <v>0.022715247231914</v>
       </c>
       <c r="U455" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA455" t="inlineStr">
@@ -66022,7 +66022,7 @@
       </c>
       <c r="AS455" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT455" t="n">
@@ -66107,22 +66107,22 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -66136,17 +66136,17 @@
         </is>
       </c>
       <c r="N456" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="O456" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="R456" t="n">
-        <v>0.01195539327995473</v>
+        <v>0.05260373043180083</v>
       </c>
       <c r="U456" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA456" t="inlineStr">
@@ -66166,7 +66166,7 @@
       </c>
       <c r="AS456" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT456" t="n">
@@ -66251,22 +66251,22 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -66280,17 +66280,17 @@
         </is>
       </c>
       <c r="N457" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="O457" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="R457" t="n">
-        <v>0.22715247231914</v>
+        <v>0.2187836970231716</v>
       </c>
       <c r="U457" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA457" t="inlineStr">
@@ -66310,7 +66310,7 @@
       </c>
       <c r="AS457" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT457" t="n">
@@ -66395,22 +66395,22 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>D234</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>副伤寒</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -66424,17 +66424,17 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O458" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R458" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U458" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA458" t="inlineStr">
@@ -66454,7 +66454,7 @@
       </c>
       <c r="AS458" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT458" t="n">
@@ -66539,17 +66539,17 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
@@ -66568,17 +66568,17 @@
         </is>
       </c>
       <c r="N459" t="n">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="O459" t="n">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="R459" t="n">
-        <v>0.02151970790391852</v>
+        <v>0.22715247231914</v>
       </c>
       <c r="U459" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA459" t="inlineStr">
@@ -66598,7 +66598,7 @@
       </c>
       <c r="AS459" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT459" t="n">
@@ -66683,46 +66683,46 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D234</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>副伤寒</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N460" t="n">
-        <v>858</v>
+        <v>1</v>
       </c>
       <c r="O460" t="n">
-        <v>858</v>
+        <v>1</v>
       </c>
       <c r="R460" t="n">
-        <v>1.025772743420116</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U460" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AA460" t="inlineStr">
@@ -66742,7 +66742,7 @@
       </c>
       <c r="AS460" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AT460" t="n">
@@ -66827,46 +66827,46 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D236</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N461" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="O461" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="R461" t="n">
-        <v>0.0406483371518461</v>
+        <v>0.02151970790391852</v>
       </c>
       <c r="U461" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AA461" t="inlineStr">
@@ -66886,7 +66886,7 @@
       </c>
       <c r="AS461" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AT461" t="n">
@@ -66971,17 +66971,17 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>D008</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>乙型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -67000,17 +67000,17 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>268</v>
+        <v>860</v>
       </c>
       <c r="O462" t="n">
-        <v>268</v>
+        <v>860</v>
       </c>
       <c r="R462" t="n">
-        <v>0.3204045399027869</v>
+        <v>1.028163822076107</v>
       </c>
       <c r="U462" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AA462" t="inlineStr">
@@ -67030,7 +67030,7 @@
       </c>
       <c r="AS462" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AT462" t="n">
@@ -67115,17 +67115,17 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -67144,17 +67144,17 @@
         </is>
       </c>
       <c r="N463" t="n">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="O463" t="n">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="R463" t="n">
-        <v>0.1458557980154478</v>
+        <v>0.0406483371518461</v>
       </c>
       <c r="U463" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AA463" t="inlineStr">
@@ -67174,7 +67174,7 @@
       </c>
       <c r="AS463" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AT463" t="n">
@@ -67259,17 +67259,17 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
@@ -67288,17 +67288,17 @@
         </is>
       </c>
       <c r="N464" t="n">
-        <v>113</v>
+        <v>267</v>
       </c>
       <c r="O464" t="n">
-        <v>113</v>
+        <v>267</v>
       </c>
       <c r="R464" t="n">
-        <v>0.1350959440634885</v>
+        <v>0.3192090005747914</v>
       </c>
       <c r="U464" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AA464" t="inlineStr">
@@ -67318,7 +67318,7 @@
       </c>
       <c r="AS464" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AT464" t="n">
@@ -67403,17 +67403,17 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -67432,17 +67432,17 @@
         </is>
       </c>
       <c r="N465" t="n">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="O465" t="n">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="R465" t="n">
-        <v>0.01554201126394116</v>
+        <v>0.1458557980154478</v>
       </c>
       <c r="U465" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AA465" t="inlineStr">
@@ -67462,7 +67462,7 @@
       </c>
       <c r="AS465" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AT465" t="n">
@@ -67547,22 +67547,22 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -67576,17 +67576,17 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="O466" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="R466" t="n">
-        <v>0.06216804505576462</v>
+        <v>0.1374870227194794</v>
       </c>
       <c r="U466" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AA466" t="inlineStr">
@@ -67606,7 +67606,7 @@
       </c>
       <c r="AS466" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AT466" t="n">
@@ -67691,22 +67691,22 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -67720,17 +67720,17 @@
         </is>
       </c>
       <c r="N467" t="n">
-        <v>436</v>
+        <v>13</v>
       </c>
       <c r="O467" t="n">
-        <v>436</v>
+        <v>13</v>
       </c>
       <c r="R467" t="n">
-        <v>0.5212551470060264</v>
+        <v>0.01554201126394116</v>
       </c>
       <c r="U467" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AA467" t="inlineStr">
@@ -67750,7 +67750,7 @@
       </c>
       <c r="AS467" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AT467" t="n">
@@ -67835,17 +67835,17 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Scarlet fever</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>猩红热</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -67864,17 +67864,17 @@
         </is>
       </c>
       <c r="N468" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="O468" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="R468" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.06336358438376009</v>
       </c>
       <c r="U468" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AA468" t="inlineStr">
@@ -67894,7 +67894,7 @@
       </c>
       <c r="AS468" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT468" t="n">
@@ -67979,17 +67979,17 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -68008,17 +68008,17 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>1</v>
+        <v>437</v>
       </c>
       <c r="O469" t="n">
-        <v>1</v>
+        <v>437</v>
       </c>
       <c r="R469" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.5224506863340219</v>
       </c>
       <c r="U469" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AA469" t="inlineStr">
@@ -68038,7 +68038,7 @@
       </c>
       <c r="AS469" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AT469" t="n">
@@ -68123,22 +68123,22 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -68152,17 +68152,17 @@
         </is>
       </c>
       <c r="N470" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="O470" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R470" t="n">
-        <v>0.02988848319988684</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U470" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AA470" t="inlineStr">
@@ -68182,7 +68182,7 @@
       </c>
       <c r="AS470" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AT470" t="n">
@@ -68267,22 +68267,22 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Scarlet fever</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>猩红热</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -68296,17 +68296,17 @@
         </is>
       </c>
       <c r="N471" t="n">
-        <v>582</v>
+        <v>12</v>
       </c>
       <c r="O471" t="n">
-        <v>582</v>
+        <v>12</v>
       </c>
       <c r="R471" t="n">
-        <v>0.6958038888933655</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U471" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AA471" t="inlineStr">
@@ -68326,7 +68326,7 @@
       </c>
       <c r="AS471" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AT471" t="n">
@@ -68411,22 +68411,22 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -68440,17 +68440,17 @@
         </is>
       </c>
       <c r="N472" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O472" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R472" t="n">
-        <v>0.005977696639977366</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U472" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AA472" t="inlineStr">
@@ -68470,7 +68470,7 @@
       </c>
       <c r="AS472" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AT472" t="n">
@@ -68555,22 +68555,22 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -68584,17 +68584,17 @@
         </is>
       </c>
       <c r="N473" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O473" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R473" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.02988848319988684</v>
       </c>
       <c r="U473" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA473" t="inlineStr">
@@ -68614,7 +68614,7 @@
       </c>
       <c r="AS473" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT473" t="n">
@@ -68699,17 +68699,17 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -68728,17 +68728,17 @@
         </is>
       </c>
       <c r="N474" t="n">
-        <v>243</v>
+        <v>582</v>
       </c>
       <c r="O474" t="n">
-        <v>243</v>
+        <v>582</v>
       </c>
       <c r="R474" t="n">
-        <v>0.2905160567029</v>
+        <v>0.6958038888933655</v>
       </c>
       <c r="U474" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA474" t="inlineStr">
@@ -68758,7 +68758,7 @@
       </c>
       <c r="AS474" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT474" t="n">
@@ -68843,17 +68843,17 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
@@ -68872,17 +68872,17 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O475" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="R475" t="n">
-        <v>0.03347510118387326</v>
+        <v>0.005977696639977366</v>
       </c>
       <c r="U475" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA475" t="inlineStr">
@@ -68902,7 +68902,7 @@
       </c>
       <c r="AS475" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT475" t="n">
@@ -68987,22 +68987,22 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -69016,17 +69016,17 @@
         </is>
       </c>
       <c r="N476" t="n">
-        <v>975</v>
+        <v>1</v>
       </c>
       <c r="O476" t="n">
-        <v>975</v>
+        <v>1</v>
       </c>
       <c r="R476" t="n">
-        <v>1.165650844795587</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U476" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AA476" t="inlineStr">
@@ -69046,7 +69046,7 @@
       </c>
       <c r="AS476" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AT476" t="n">
@@ -69131,22 +69131,22 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -69160,17 +69160,17 @@
         </is>
       </c>
       <c r="N477" t="n">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="O477" t="n">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="R477" t="n">
-        <v>0.06575466303975104</v>
+        <v>0.2893205173749046</v>
       </c>
       <c r="U477" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA477" t="inlineStr">
@@ -69190,7 +69190,7 @@
       </c>
       <c r="AS477" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT477" t="n">
@@ -69275,22 +69275,22 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -69304,17 +69304,17 @@
         </is>
       </c>
       <c r="N478" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O478" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="R478" t="n">
-        <v>0.06695020236774651</v>
+        <v>0.03347510118387326</v>
       </c>
       <c r="U478" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA478" t="inlineStr">
@@ -69334,7 +69334,7 @@
       </c>
       <c r="AS478" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT478" t="n">
@@ -69419,22 +69419,22 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -69448,17 +69448,17 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>9</v>
+        <v>1010</v>
       </c>
       <c r="O479" t="n">
-        <v>9</v>
+        <v>1010</v>
       </c>
       <c r="R479" t="n">
-        <v>0.01075985395195926</v>
+        <v>1.207494721275428</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA479" t="inlineStr">
@@ -69478,7 +69478,7 @@
       </c>
       <c r="AS479" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT479" t="n">
@@ -69563,22 +69563,22 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -69592,17 +69592,17 @@
         </is>
       </c>
       <c r="N480" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="O480" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="R480" t="n">
-        <v>0.1004253035516198</v>
+        <v>0.07053682035173293</v>
       </c>
       <c r="U480" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA480" t="inlineStr">
@@ -69622,7 +69622,7 @@
       </c>
       <c r="AS480" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT480" t="n">
@@ -69707,22 +69707,22 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -69736,17 +69736,17 @@
         </is>
       </c>
       <c r="N481" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="O481" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="R481" t="n">
-        <v>0.1948729104632622</v>
+        <v>0.07053682035173293</v>
       </c>
       <c r="U481" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA481" t="inlineStr">
@@ -69766,7 +69766,7 @@
       </c>
       <c r="AS481" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT481" t="n">
@@ -69851,22 +69851,22 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -69880,17 +69880,17 @@
         </is>
       </c>
       <c r="N482" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="O482" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="R482" t="n">
-        <v>0.06695020236774651</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U482" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA482" t="inlineStr">
@@ -69910,7 +69910,7 @@
       </c>
       <c r="AS482" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT482" t="n">
@@ -69995,17 +69995,17 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
@@ -70024,17 +70024,17 @@
         </is>
       </c>
       <c r="N483" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="O483" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="R483" t="n">
-        <v>0.005977696639977366</v>
+        <v>0.1064030001915971</v>
       </c>
       <c r="U483" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA483" t="inlineStr">
@@ -70054,7 +70054,7 @@
       </c>
       <c r="AS483" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT483" t="n">
@@ -70139,17 +70139,17 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
@@ -70168,17 +70168,17 @@
         </is>
       </c>
       <c r="N484" t="n">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="O484" t="n">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="R484" t="n">
-        <v>0.2438900229110766</v>
+        <v>0.1948729104632622</v>
       </c>
       <c r="U484" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA484" t="inlineStr">
@@ -70198,7 +70198,7 @@
       </c>
       <c r="AS484" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT484" t="n">
@@ -70283,17 +70283,17 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
@@ -70312,17 +70312,17 @@
         </is>
       </c>
       <c r="N485" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="O485" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="R485" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.06695020236774651</v>
       </c>
       <c r="U485" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA485" t="inlineStr">
@@ -70342,7 +70342,7 @@
       </c>
       <c r="AS485" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT485" t="n">
@@ -70427,17 +70427,17 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
@@ -70456,17 +70456,17 @@
         </is>
       </c>
       <c r="N486" t="n">
-        <v>268</v>
+        <v>5</v>
       </c>
       <c r="O486" t="n">
-        <v>268</v>
+        <v>5</v>
       </c>
       <c r="R486" t="n">
-        <v>0.3204045399027869</v>
+        <v>0.005977696639977366</v>
       </c>
       <c r="U486" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA486" t="inlineStr">
@@ -70486,7 +70486,7 @@
       </c>
       <c r="AS486" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT486" t="n">
@@ -70571,17 +70571,17 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
@@ -70600,17 +70600,17 @@
         </is>
       </c>
       <c r="N487" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="O487" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="R487" t="n">
-        <v>0.2056327644152214</v>
+        <v>0.2462811015670675</v>
       </c>
       <c r="U487" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA487" t="inlineStr">
@@ -70630,7 +70630,7 @@
       </c>
       <c r="AS487" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT487" t="n">
@@ -70715,17 +70715,17 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
@@ -70744,17 +70744,17 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R488" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U488" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA488" t="inlineStr">
@@ -70774,7 +70774,7 @@
       </c>
       <c r="AS488" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT488" t="n">
@@ -70859,22 +70859,22 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -70888,17 +70888,17 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>3</v>
+        <v>280</v>
       </c>
       <c r="O489" t="n">
-        <v>3</v>
+        <v>280</v>
       </c>
       <c r="R489" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.3347510118387326</v>
       </c>
       <c r="U489" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA489" t="inlineStr">
@@ -70918,7 +70918,7 @@
       </c>
       <c r="AS489" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT489" t="n">
@@ -71003,22 +71003,22 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -71032,17 +71032,17 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="O490" t="n">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="R490" t="n">
-        <v>0.03825725849585514</v>
+        <v>0.2068283037432169</v>
       </c>
       <c r="U490" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA490" t="inlineStr">
@@ -71062,7 +71062,7 @@
       </c>
       <c r="AS490" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT490" t="n">
@@ -71147,17 +71147,17 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
@@ -71176,17 +71176,17 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="O491" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="R491" t="n">
-        <v>0.08010113497569672</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U491" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA491" t="inlineStr">
@@ -71206,7 +71206,7 @@
       </c>
       <c r="AS491" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT491" t="n">
@@ -71291,22 +71291,22 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -71320,17 +71320,17 @@
         </is>
       </c>
       <c r="N492" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="O492" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="R492" t="n">
-        <v>0.1841130565113029</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U492" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA492" t="inlineStr">
@@ -71350,7 +71350,7 @@
       </c>
       <c r="AS492" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT492" t="n">
@@ -71435,17 +71435,17 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
@@ -71464,17 +71464,17 @@
         </is>
       </c>
       <c r="N493" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O493" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R493" t="n">
-        <v>0.01673755059193663</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U493" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA493" t="inlineStr">
@@ -71494,7 +71494,7 @@
       </c>
       <c r="AS493" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AT493" t="n">
@@ -71579,22 +71579,22 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -71608,17 +71608,17 @@
         </is>
       </c>
       <c r="N494" t="n">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="O494" t="n">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="R494" t="n">
-        <v>0.2438900229110766</v>
+        <v>0.03825725849585514</v>
       </c>
       <c r="U494" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA494" t="inlineStr">
@@ -71638,7 +71638,7 @@
       </c>
       <c r="AS494" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT494" t="n">
@@ -71723,17 +71723,17 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>D234</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>副伤寒</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -71752,17 +71752,17 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="O495" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="R495" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.08607883161567409</v>
       </c>
       <c r="U495" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA495" t="inlineStr">
@@ -71782,7 +71782,7 @@
       </c>
       <c r="AS495" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT495" t="n">
@@ -71867,22 +71867,22 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -71896,17 +71896,17 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="O496" t="n">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="R496" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.1865041351672939</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA496" t="inlineStr">
@@ -71926,7 +71926,7 @@
       </c>
       <c r="AS496" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT496" t="n">
@@ -72011,17 +72011,17 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -72031,7 +72031,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
@@ -72040,17 +72040,17 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>848</v>
+        <v>14</v>
       </c>
       <c r="O497" t="n">
-        <v>848</v>
+        <v>14</v>
       </c>
       <c r="R497" t="n">
-        <v>1.013817350140161</v>
+        <v>0.01673755059193663</v>
       </c>
       <c r="U497" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA497" t="inlineStr">
@@ -72070,7 +72070,7 @@
       </c>
       <c r="AS497" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT497" t="n">
@@ -72155,27 +72155,27 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
@@ -72184,17 +72184,17 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="O498" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="R498" t="n">
-        <v>0.0358661798398642</v>
+        <v>0.245085562239072</v>
       </c>
       <c r="U498" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA498" t="inlineStr">
@@ -72214,7 +72214,7 @@
       </c>
       <c r="AS498" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT498" t="n">
@@ -72299,27 +72299,27 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>D008</t>
+          <t>D234</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>乙型肝炎</t>
+          <t>副伤寒</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
@@ -72328,17 +72328,17 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>229</v>
+        <v>2</v>
       </c>
       <c r="O499" t="n">
-        <v>229</v>
+        <v>2</v>
       </c>
       <c r="R499" t="n">
-        <v>0.2737785061109634</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U499" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AA499" t="inlineStr">
@@ -72358,7 +72358,7 @@
       </c>
       <c r="AS499" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AT499" t="n">
@@ -72443,27 +72443,27 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D236</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -72472,17 +72472,17 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="O500" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="R500" t="n">
-        <v>0.1398781013754704</v>
+        <v>0.02032416857592305</v>
       </c>
       <c r="U500" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AA500" t="inlineStr">
@@ -72502,7 +72502,7 @@
       </c>
       <c r="AS500" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AT500" t="n">
@@ -72587,17 +72587,17 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
@@ -72616,17 +72616,17 @@
         </is>
       </c>
       <c r="N501" t="n">
-        <v>41</v>
+        <v>909</v>
       </c>
       <c r="O501" t="n">
-        <v>41</v>
+        <v>909</v>
       </c>
       <c r="R501" t="n">
-        <v>0.04901711244781441</v>
+        <v>1.086745249147885</v>
       </c>
       <c r="U501" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AA501" t="inlineStr">
@@ -72646,7 +72646,7 @@
       </c>
       <c r="AS501" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AT501" t="n">
@@ -72731,17 +72731,17 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
@@ -72760,17 +72760,17 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O502" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="R502" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.03945279782385062</v>
       </c>
       <c r="U502" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AA502" t="inlineStr">
@@ -72790,7 +72790,7 @@
       </c>
       <c r="AS502" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AT502" t="n">
@@ -72875,22 +72875,22 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -72904,17 +72904,17 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="O503" t="n">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="R503" t="n">
-        <v>0.05140819110380536</v>
+        <v>0.2952982140148819</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AA503" t="inlineStr">
@@ -72934,7 +72934,7 @@
       </c>
       <c r="AS503" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AT503" t="n">
@@ -73019,22 +73019,22 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -73048,17 +73048,17 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>312</v>
+        <v>123</v>
       </c>
       <c r="O504" t="n">
-        <v>312</v>
+        <v>123</v>
       </c>
       <c r="R504" t="n">
-        <v>0.3730082703345877</v>
+        <v>0.1470513373434432</v>
       </c>
       <c r="U504" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AA504" t="inlineStr">
@@ -73078,7 +73078,7 @@
       </c>
       <c r="AS504" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AT504" t="n">
@@ -73163,22 +73163,22 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Scarlet fever</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>猩红热</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -73192,17 +73192,17 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="O505" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="R505" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.07412343833571934</v>
       </c>
       <c r="U505" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AA505" t="inlineStr">
@@ -73222,7 +73222,7 @@
       </c>
       <c r="AS505" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AT505" t="n">
@@ -73307,22 +73307,22 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -73336,17 +73336,17 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O506" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R506" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AA506" t="inlineStr">
@@ -73366,7 +73366,7 @@
       </c>
       <c r="AS506" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AT506" t="n">
@@ -73451,22 +73451,22 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -73480,17 +73480,17 @@
         </is>
       </c>
       <c r="N507" t="n">
-        <v>521</v>
+        <v>48</v>
       </c>
       <c r="O507" t="n">
-        <v>521</v>
+        <v>48</v>
       </c>
       <c r="R507" t="n">
-        <v>0.6228759898856416</v>
+        <v>0.05738588774378273</v>
       </c>
       <c r="U507" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AA507" t="inlineStr">
@@ -73510,7 +73510,7 @@
       </c>
       <c r="AS507" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT507" t="n">
@@ -73595,22 +73595,22 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -73624,17 +73624,17 @@
         </is>
       </c>
       <c r="N508" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="O508" t="n">
-        <v>3</v>
+        <v>347</v>
       </c>
       <c r="R508" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.4148521468144293</v>
       </c>
       <c r="U508" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AA508" t="inlineStr">
@@ -73654,7 +73654,7 @@
       </c>
       <c r="AS508" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AT508" t="n">
@@ -73739,22 +73739,22 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -73768,17 +73768,17 @@
         </is>
       </c>
       <c r="N509" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="O509" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="R509" t="n">
-        <v>0.2773651240949498</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U509" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AA509" t="inlineStr">
@@ -73798,7 +73798,7 @@
       </c>
       <c r="AS509" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AT509" t="n">
@@ -73883,22 +73883,22 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Scarlet fever</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>猩红热</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -73912,17 +73912,17 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="O510" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R510" t="n">
-        <v>0.022715247231914</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U510" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AA510" t="inlineStr">
@@ -73942,7 +73942,7 @@
       </c>
       <c r="AS510" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AT510" t="n">
@@ -74027,22 +74027,22 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -74056,17 +74056,17 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>540</v>
+        <v>11</v>
       </c>
       <c r="O511" t="n">
-        <v>540</v>
+        <v>11</v>
       </c>
       <c r="R511" t="n">
-        <v>0.6455912371175556</v>
+        <v>0.01315093260795021</v>
       </c>
       <c r="U511" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA511" t="inlineStr">
@@ -74086,7 +74086,7 @@
       </c>
       <c r="AS511" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT511" t="n">
@@ -74171,22 +74171,22 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -74200,17 +74200,17 @@
         </is>
       </c>
       <c r="N512" t="n">
-        <v>29</v>
+        <v>546</v>
       </c>
       <c r="O512" t="n">
-        <v>29</v>
+        <v>546</v>
       </c>
       <c r="R512" t="n">
-        <v>0.03467064051186873</v>
+        <v>0.6527644730855285</v>
       </c>
       <c r="U512" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA512" t="inlineStr">
@@ -74230,7 +74230,7 @@
       </c>
       <c r="AS512" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT512" t="n">
@@ -74315,22 +74315,22 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -74344,17 +74344,17 @@
         </is>
       </c>
       <c r="N513" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="O513" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="R513" t="n">
-        <v>0.03467064051186873</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U513" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA513" t="inlineStr">
@@ -74374,7 +74374,7 @@
       </c>
       <c r="AS513" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT513" t="n">
@@ -74459,17 +74459,17 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
@@ -74488,17 +74488,17 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>4</v>
+        <v>247</v>
       </c>
       <c r="O514" t="n">
-        <v>4</v>
+        <v>247</v>
       </c>
       <c r="R514" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.2952982140148819</v>
       </c>
       <c r="U514" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA514" t="inlineStr">
@@ -74518,7 +74518,7 @@
       </c>
       <c r="AS514" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT514" t="n">
@@ -74603,22 +74603,22 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -74632,17 +74632,17 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O515" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R515" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.02391078655990947</v>
       </c>
       <c r="U515" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA515" t="inlineStr">
@@ -74662,7 +74662,7 @@
       </c>
       <c r="AS515" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT515" t="n">
@@ -74747,17 +74747,17 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
@@ -74776,17 +74776,17 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="O516" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="R516" t="n">
-        <v>0.07890559564770125</v>
+        <v>0.7818827205090396</v>
       </c>
       <c r="U516" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA516" t="inlineStr">
@@ -74806,7 +74806,7 @@
       </c>
       <c r="AS516" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT516" t="n">
@@ -74891,22 +74891,22 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -74920,17 +74920,17 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="O517" t="n">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="R517" t="n">
-        <v>0.1769398205433301</v>
+        <v>0.03945279782385062</v>
       </c>
       <c r="U517" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA517" t="inlineStr">
@@ -74950,7 +74950,7 @@
       </c>
       <c r="AS517" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT517" t="n">
@@ -75035,22 +75035,22 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -75064,17 +75064,17 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="O518" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="R518" t="n">
-        <v>0.06575466303975104</v>
+        <v>0.03945279782385062</v>
       </c>
       <c r="U518" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA518" t="inlineStr">
@@ -75094,7 +75094,7 @@
       </c>
       <c r="AS518" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT518" t="n">
@@ -75179,22 +75179,22 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -75208,17 +75208,17 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O519" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R519" t="n">
-        <v>0.01075985395195926</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U519" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA519" t="inlineStr">
@@ -75238,7 +75238,7 @@
       </c>
       <c r="AS519" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT519" t="n">
@@ -75323,17 +75323,17 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
@@ -75352,17 +75352,17 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="O520" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="R520" t="n">
-        <v>0.1960684497912576</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA520" t="inlineStr">
@@ -75382,7 +75382,7 @@
       </c>
       <c r="AS520" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT520" t="n">
@@ -75467,17 +75467,17 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -75496,17 +75496,17 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="O521" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="R521" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.09444760691164239</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA521" t="inlineStr">
@@ -75526,7 +75526,7 @@
       </c>
       <c r="AS521" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT521" t="n">
@@ -75611,17 +75611,17 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
@@ -75640,17 +75640,17 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="O522" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="R522" t="n">
-        <v>0.2032416857592305</v>
+        <v>0.1948729104632622</v>
       </c>
       <c r="U522" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA522" t="inlineStr">
@@ -75670,7 +75670,7 @@
       </c>
       <c r="AS522" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT522" t="n">
@@ -75755,17 +75755,17 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
@@ -75784,17 +75784,17 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="O523" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="R523" t="n">
-        <v>0.1291182474235111</v>
+        <v>0.07173235967972839</v>
       </c>
       <c r="U523" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA523" t="inlineStr">
@@ -75814,7 +75814,7 @@
       </c>
       <c r="AS523" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT523" t="n">
@@ -75899,17 +75899,17 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -75928,17 +75928,17 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O524" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R524" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.01315093260795021</v>
       </c>
       <c r="U524" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA524" t="inlineStr">
@@ -75958,7 +75958,7 @@
       </c>
       <c r="AS524" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT524" t="n">
@@ -76043,22 +76043,22 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -76072,17 +76072,17 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>31</v>
+        <v>176</v>
       </c>
       <c r="O525" t="n">
-        <v>31</v>
+        <v>176</v>
       </c>
       <c r="R525" t="n">
-        <v>0.03706171916785967</v>
+        <v>0.2104149217272033</v>
       </c>
       <c r="U525" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA525" t="inlineStr">
@@ -76102,7 +76102,7 @@
       </c>
       <c r="AS525" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT525" t="n">
@@ -76187,17 +76187,17 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -76216,17 +76216,17 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O526" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R526" t="n">
-        <v>0.0358661798398642</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA526" t="inlineStr">
@@ -76246,7 +76246,7 @@
       </c>
       <c r="AS526" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT526" t="n">
@@ -76331,22 +76331,22 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -76360,17 +76360,17 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="O527" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="R527" t="n">
-        <v>0.1255316294395247</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U527" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA527" t="inlineStr">
@@ -76390,7 +76390,7 @@
       </c>
       <c r="AS527" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT527" t="n">
@@ -76475,22 +76475,22 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -76504,17 +76504,17 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="O528" t="n">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="R528" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.2510632588790494</v>
       </c>
       <c r="U528" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA528" t="inlineStr">
@@ -76534,7 +76534,7 @@
       </c>
       <c r="AS528" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT528" t="n">
@@ -76619,17 +76619,17 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -76648,17 +76648,17 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="O529" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="R529" t="n">
-        <v>0.22715247231914</v>
+        <v>0.1434647193594568</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA529" t="inlineStr">
@@ -76678,7 +76678,7 @@
       </c>
       <c r="AS529" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT529" t="n">
@@ -76763,17 +76763,17 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -76792,17 +76792,17 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O530" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R530" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U530" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA530" t="inlineStr">
@@ -76822,7 +76822,7 @@
       </c>
       <c r="AS530" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT530" t="n">
@@ -76864,6 +76864,1014 @@
         </is>
       </c>
       <c r="BC530" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N531" t="n">
+        <v>1</v>
+      </c>
+      <c r="O531" t="n">
+        <v>1</v>
+      </c>
+      <c r="R531" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO531" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP531" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS531" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AT531" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV531" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW531" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX531" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY531" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA531" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB531" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC531" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N532" t="n">
+        <v>38</v>
+      </c>
+      <c r="O532" t="n">
+        <v>38</v>
+      </c>
+      <c r="R532" t="n">
+        <v>0.04543049446382799</v>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+        </is>
+      </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO532" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP532" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS532" t="inlineStr">
+        <is>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+        </is>
+      </c>
+      <c r="AT532" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV532" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW532" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX532" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY532" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA532" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB532" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC532" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N533" t="n">
+        <v>35</v>
+      </c>
+      <c r="O533" t="n">
+        <v>35</v>
+      </c>
+      <c r="R533" t="n">
+        <v>0.04184387647984157</v>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+        </is>
+      </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO533" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP533" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS533" t="inlineStr">
+        <is>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+        </is>
+      </c>
+      <c r="AT533" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV533" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW533" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX533" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY533" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA533" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB533" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC533" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N534" t="n">
+        <v>129</v>
+      </c>
+      <c r="O534" t="n">
+        <v>129</v>
+      </c>
+      <c r="R534" t="n">
+        <v>0.1542245733114161</v>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+        </is>
+      </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO534" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP534" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS534" t="inlineStr">
+        <is>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+        </is>
+      </c>
+      <c r="AT534" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV534" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW534" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX534" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY534" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA534" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB534" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC534" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N535" t="n">
+        <v>5</v>
+      </c>
+      <c r="O535" t="n">
+        <v>5</v>
+      </c>
+      <c r="R535" t="n">
+        <v>0.005977696639977366</v>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO535" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP535" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS535" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AT535" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV535" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW535" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX535" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY535" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA535" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB535" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC535" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N536" t="n">
+        <v>199</v>
+      </c>
+      <c r="O536" t="n">
+        <v>199</v>
+      </c>
+      <c r="R536" t="n">
+        <v>0.2379123262710992</v>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO536" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP536" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS536" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AT536" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV536" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW536" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX536" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY536" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA536" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB536" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC536" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N537" t="n">
+        <v>17</v>
+      </c>
+      <c r="O537" t="n">
+        <v>17</v>
+      </c>
+      <c r="R537" t="n">
+        <v>0.02032416857592305</v>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO537" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP537" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS537" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT537" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV537" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW537" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX537" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY537" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA537" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB537" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC537" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -76985,7 +77993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10">
@@ -76995,7 +78003,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11">
@@ -77047,7 +78055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60280</v>
+        <v>60862</v>
       </c>
     </row>
     <row r="16">

--- a/countries/de/2026-2029.xlsx
+++ b/countries/de/2026-2029.xlsx
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O49" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R49" t="n">
-        <v>0.2654097308149951</v>
+        <v>0.2642141914869996</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O55" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R55" t="n">
-        <v>0.09444760691164239</v>
+        <v>0.09325206758364693</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -14008,13 +14008,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O94" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R94" t="n">
-        <v>0.02869294387189136</v>
+        <v>0.02988848319988684</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O137" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R137" t="n">
-        <v>0.3311643938547461</v>
+        <v>0.3323599331827416</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -26968,13 +26968,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O184" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R184" t="n">
-        <v>0.3670305736946103</v>
+        <v>0.3682261130226058</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -34312,13 +34312,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O235" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R235" t="n">
-        <v>0.2498677195510539</v>
+        <v>0.2510632588790494</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -35608,13 +35608,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O244" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R244" t="n">
-        <v>0.01912862924792757</v>
+        <v>0.0179330899199321</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
@@ -40648,13 +40648,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O279" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R279" t="n">
-        <v>0.2678008094709861</v>
+        <v>0.270191888126977</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
@@ -41368,13 +41368,13 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O284" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R284" t="n">
-        <v>0.2773651240949498</v>
+        <v>0.2785606634229453</v>
       </c>
       <c r="U284" t="inlineStr">
         <is>
@@ -41944,13 +41944,13 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O288" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R288" t="n">
-        <v>0.06575466303975104</v>
+        <v>0.06695020236774651</v>
       </c>
       <c r="U288" t="inlineStr">
         <is>
@@ -43528,13 +43528,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="O299" t="n">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="R299" t="n">
-        <v>1.757442812153346</v>
+        <v>1.761029430137332</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
@@ -45544,13 +45544,13 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O313" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="R313" t="n">
-        <v>0.2570409555190268</v>
+        <v>0.2582364948470223</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
@@ -47848,13 +47848,13 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O329" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R329" t="n">
-        <v>0.1470513373434432</v>
+        <v>0.1494424159994342</v>
       </c>
       <c r="U329" t="inlineStr">
         <is>
@@ -50152,13 +50152,13 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="O345" t="n">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="R345" t="n">
-        <v>1.652235351289744</v>
+        <v>1.655821969273731</v>
       </c>
       <c r="U345" t="inlineStr">
         <is>
@@ -52024,13 +52024,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O358" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R358" t="n">
-        <v>0.2199792363511671</v>
+        <v>0.2211747756791626</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
@@ -53032,13 +53032,13 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O365" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R365" t="n">
-        <v>0.2462811015670675</v>
+        <v>0.247476640895063</v>
       </c>
       <c r="U365" t="inlineStr">
         <is>
@@ -54040,13 +54040,13 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O372" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R372" t="n">
-        <v>0.3192090005747914</v>
+        <v>0.3204045399027869</v>
       </c>
       <c r="U372" t="inlineStr">
         <is>
@@ -56776,13 +56776,13 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="O391" t="n">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="R391" t="n">
-        <v>1.492033081338351</v>
+        <v>1.499206317306324</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
@@ -57640,13 +57640,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O397" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R397" t="n">
-        <v>0.11357623615957</v>
+        <v>0.1147717754875655</v>
       </c>
       <c r="U397" t="inlineStr">
         <is>
@@ -57928,13 +57928,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O399" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R399" t="n">
-        <v>0.07412343833571934</v>
+        <v>0.07292789900772388</v>
       </c>
       <c r="U399" t="inlineStr">
         <is>
@@ -58648,13 +58648,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O404" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R404" t="n">
-        <v>0.4626737199342482</v>
+        <v>0.4638692592622436</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -60088,13 +60088,13 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O414" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R414" t="n">
-        <v>0.01075985395195926</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
@@ -60664,13 +60664,13 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O418" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="R418" t="n">
-        <v>0.7137369788132977</v>
+        <v>0.7149325181412931</v>
       </c>
       <c r="U418" t="inlineStr">
         <is>
@@ -60952,13 +60952,13 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O420" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R420" t="n">
-        <v>0.2976892926708729</v>
+        <v>0.2964937533428774</v>
       </c>
       <c r="U420" t="inlineStr">
         <is>
@@ -61672,13 +61672,13 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O425" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R425" t="n">
-        <v>0.05738588774378273</v>
+        <v>0.05858142707177819</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -63400,13 +63400,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="O437" t="n">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="R437" t="n">
-        <v>1.396389935098713</v>
+        <v>1.407149789050672</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -64408,13 +64408,13 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O444" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R444" t="n">
-        <v>0.08488329228767862</v>
+        <v>0.08607883161567409</v>
       </c>
       <c r="U444" t="inlineStr">
         <is>
@@ -64696,13 +64696,13 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O446" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R446" t="n">
-        <v>0.2893205173749046</v>
+        <v>0.2905160567029</v>
       </c>
       <c r="U446" t="inlineStr">
         <is>
@@ -65128,13 +65128,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O449" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="R449" t="n">
-        <v>0.3921368995825153</v>
+        <v>0.3945279782385062</v>
       </c>
       <c r="U449" t="inlineStr">
         <is>
@@ -66280,13 +66280,13 @@
         </is>
       </c>
       <c r="N457" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O457" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R457" t="n">
-        <v>0.2187836970231716</v>
+        <v>0.2199792363511671</v>
       </c>
       <c r="U457" t="inlineStr">
         <is>
@@ -66424,13 +66424,13 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O458" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R458" t="n">
-        <v>0.01075985395195926</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U458" t="inlineStr">
         <is>
@@ -66568,13 +66568,13 @@
         </is>
       </c>
       <c r="N459" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O459" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R459" t="n">
-        <v>0.22715247231914</v>
+        <v>0.2283480116471354</v>
       </c>
       <c r="U459" t="inlineStr">
         <is>
@@ -67000,13 +67000,13 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="O462" t="n">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="R462" t="n">
-        <v>1.028163822076107</v>
+        <v>1.030554900732098</v>
       </c>
       <c r="U462" t="inlineStr">
         <is>
@@ -67144,13 +67144,13 @@
         </is>
       </c>
       <c r="N463" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O463" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R463" t="n">
-        <v>0.0406483371518461</v>
+        <v>0.03945279782385062</v>
       </c>
       <c r="U463" t="inlineStr">
         <is>
@@ -67576,13 +67576,13 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O466" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R466" t="n">
-        <v>0.1374870227194794</v>
+        <v>0.1422691800314613</v>
       </c>
       <c r="U466" t="inlineStr">
         <is>
@@ -67864,13 +67864,13 @@
         </is>
       </c>
       <c r="N468" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O468" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R468" t="n">
-        <v>0.06336358438376009</v>
+        <v>0.06216804505576462</v>
       </c>
       <c r="U468" t="inlineStr">
         <is>
@@ -68008,13 +68008,13 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="O469" t="n">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="R469" t="n">
-        <v>0.5224506863340219</v>
+        <v>0.5308194616299902</v>
       </c>
       <c r="U469" t="inlineStr">
         <is>
@@ -69160,13 +69160,13 @@
         </is>
       </c>
       <c r="N477" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O477" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R477" t="n">
-        <v>0.2893205173749046</v>
+        <v>0.2905160567029</v>
       </c>
       <c r="U477" t="inlineStr">
         <is>
@@ -69448,13 +69448,13 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>1010</v>
+        <v>1049</v>
       </c>
       <c r="O479" t="n">
-        <v>1010</v>
+        <v>1049</v>
       </c>
       <c r="R479" t="n">
-        <v>1.207494721275428</v>
+        <v>1.254120755067252</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
@@ -70024,13 +70024,13 @@
         </is>
       </c>
       <c r="N483" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="O483" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="R483" t="n">
-        <v>0.1064030001915971</v>
+        <v>0.1123806968315745</v>
       </c>
       <c r="U483" t="inlineStr">
         <is>
@@ -70312,13 +70312,13 @@
         </is>
       </c>
       <c r="N485" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O485" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R485" t="n">
-        <v>0.06695020236774651</v>
+        <v>0.06814574169574199</v>
       </c>
       <c r="U485" t="inlineStr">
         <is>
@@ -70600,13 +70600,13 @@
         </is>
       </c>
       <c r="N487" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O487" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R487" t="n">
-        <v>0.2462811015670675</v>
+        <v>0.247476640895063</v>
       </c>
       <c r="U487" t="inlineStr">
         <is>
@@ -70715,17 +70715,17 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
@@ -70744,17 +70744,17 @@
         </is>
       </c>
       <c r="N488" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O488" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R488" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U488" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA488" t="inlineStr">
@@ -70774,7 +70774,7 @@
       </c>
       <c r="AS488" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT488" t="n">
@@ -70859,17 +70859,17 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
@@ -70888,17 +70888,17 @@
         </is>
       </c>
       <c r="N489" t="n">
-        <v>280</v>
+        <v>3</v>
       </c>
       <c r="O489" t="n">
-        <v>280</v>
+        <v>3</v>
       </c>
       <c r="R489" t="n">
-        <v>0.3347510118387326</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U489" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA489" t="inlineStr">
@@ -70918,7 +70918,7 @@
       </c>
       <c r="AS489" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT489" t="n">
@@ -71003,17 +71003,17 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
@@ -71032,17 +71032,17 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="O490" t="n">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="R490" t="n">
-        <v>0.2068283037432169</v>
+        <v>0.3371420904947235</v>
       </c>
       <c r="U490" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA490" t="inlineStr">
@@ -71062,7 +71062,7 @@
       </c>
       <c r="AS490" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT490" t="n">
@@ -71147,17 +71147,17 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
@@ -71176,17 +71176,17 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>3</v>
+        <v>176</v>
       </c>
       <c r="O491" t="n">
-        <v>3</v>
+        <v>176</v>
       </c>
       <c r="R491" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.2104149217272033</v>
       </c>
       <c r="U491" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA491" t="inlineStr">
@@ -71206,7 +71206,7 @@
       </c>
       <c r="AS491" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT491" t="n">
@@ -71291,17 +71291,17 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
@@ -71320,17 +71320,17 @@
         </is>
       </c>
       <c r="N492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R492" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U492" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA492" t="inlineStr">
@@ -71350,7 +71350,7 @@
       </c>
       <c r="AS492" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT492" t="n">
@@ -71435,22 +71435,22 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -71464,17 +71464,17 @@
         </is>
       </c>
       <c r="N493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R493" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U493" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA493" t="inlineStr">
@@ -71494,7 +71494,7 @@
       </c>
       <c r="AS493" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT493" t="n">
@@ -71579,17 +71579,17 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
@@ -71608,17 +71608,17 @@
         </is>
       </c>
       <c r="N494" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="O494" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="R494" t="n">
-        <v>0.03825725849585514</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U494" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA494" t="inlineStr">
@@ -71638,7 +71638,7 @@
       </c>
       <c r="AS494" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AT494" t="n">
@@ -71723,22 +71723,22 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -71752,17 +71752,17 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="O495" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="R495" t="n">
-        <v>0.08607883161567409</v>
+        <v>0.03825725849585514</v>
       </c>
       <c r="U495" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA495" t="inlineStr">
@@ -71782,7 +71782,7 @@
       </c>
       <c r="AS495" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT495" t="n">
@@ -71867,22 +71867,22 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -71896,17 +71896,17 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="O496" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="R496" t="n">
-        <v>0.1865041351672939</v>
+        <v>0.08846991027166504</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA496" t="inlineStr">
@@ -71926,7 +71926,7 @@
       </c>
       <c r="AS496" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT496" t="n">
@@ -72011,17 +72011,17 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -72040,17 +72040,17 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="O497" t="n">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="R497" t="n">
-        <v>0.01673755059193663</v>
+        <v>0.1876996744952893</v>
       </c>
       <c r="U497" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA497" t="inlineStr">
@@ -72070,7 +72070,7 @@
       </c>
       <c r="AS497" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT497" t="n">
@@ -72155,22 +72155,22 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -72184,17 +72184,17 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="O498" t="n">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="R498" t="n">
-        <v>0.245085562239072</v>
+        <v>0.0179330899199321</v>
       </c>
       <c r="U498" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA498" t="inlineStr">
@@ -72214,7 +72214,7 @@
       </c>
       <c r="AS498" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT498" t="n">
@@ -72299,17 +72299,17 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>D234</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>副伤寒</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
@@ -72328,17 +72328,17 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>2</v>
+        <v>206</v>
       </c>
       <c r="O499" t="n">
-        <v>2</v>
+        <v>206</v>
       </c>
       <c r="R499" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.2462811015670675</v>
       </c>
       <c r="U499" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA499" t="inlineStr">
@@ -72358,7 +72358,7 @@
       </c>
       <c r="AS499" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT499" t="n">
@@ -72443,17 +72443,17 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D234</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>副伤寒</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
@@ -72472,17 +72472,17 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O500" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R500" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U500" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AA500" t="inlineStr">
@@ -72502,7 +72502,7 @@
       </c>
       <c r="AS500" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AT500" t="n">
@@ -72587,27 +72587,27 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D236</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -72616,17 +72616,17 @@
         </is>
       </c>
       <c r="N501" t="n">
-        <v>909</v>
+        <v>17</v>
       </c>
       <c r="O501" t="n">
-        <v>909</v>
+        <v>17</v>
       </c>
       <c r="R501" t="n">
-        <v>1.086745249147885</v>
+        <v>0.02032416857592305</v>
       </c>
       <c r="U501" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AA501" t="inlineStr">
@@ -72646,7 +72646,7 @@
       </c>
       <c r="AS501" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AT501" t="n">
@@ -72731,17 +72731,17 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
@@ -72760,17 +72760,17 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>33</v>
+        <v>918</v>
       </c>
       <c r="O502" t="n">
-        <v>33</v>
+        <v>918</v>
       </c>
       <c r="R502" t="n">
-        <v>0.03945279782385062</v>
+        <v>1.097505103099845</v>
       </c>
       <c r="U502" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AA502" t="inlineStr">
@@ -72790,7 +72790,7 @@
       </c>
       <c r="AS502" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AT502" t="n">
@@ -72875,17 +72875,17 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>D008</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>乙型肝炎</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
@@ -72904,17 +72904,17 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="O503" t="n">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="R503" t="n">
-        <v>0.2952982140148819</v>
+        <v>0.04184387647984157</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AA503" t="inlineStr">
@@ -72934,7 +72934,7 @@
       </c>
       <c r="AS503" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AT503" t="n">
@@ -73019,17 +73019,17 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
@@ -73048,17 +73048,17 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>123</v>
+        <v>247</v>
       </c>
       <c r="O504" t="n">
-        <v>123</v>
+        <v>247</v>
       </c>
       <c r="R504" t="n">
-        <v>0.1470513373434432</v>
+        <v>0.2952982140148819</v>
       </c>
       <c r="U504" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AA504" t="inlineStr">
@@ -73078,7 +73078,7 @@
       </c>
       <c r="AS504" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AT504" t="n">
@@ -73163,17 +73163,17 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
@@ -73192,17 +73192,17 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="O505" t="n">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="R505" t="n">
-        <v>0.07412343833571934</v>
+        <v>0.1542245733114161</v>
       </c>
       <c r="U505" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AA505" t="inlineStr">
@@ -73222,7 +73222,7 @@
       </c>
       <c r="AS505" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AT505" t="n">
@@ -73307,17 +73307,17 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
@@ -73336,17 +73336,17 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="O506" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="R506" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.09086098892765598</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AA506" t="inlineStr">
@@ -73366,7 +73366,7 @@
       </c>
       <c r="AS506" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AT506" t="n">
@@ -73451,22 +73451,22 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -73480,17 +73480,17 @@
         </is>
       </c>
       <c r="N507" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="O507" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="R507" t="n">
-        <v>0.05738588774378273</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U507" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AA507" t="inlineStr">
@@ -73510,7 +73510,7 @@
       </c>
       <c r="AS507" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AT507" t="n">
@@ -73595,17 +73595,17 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
@@ -73624,17 +73624,17 @@
         </is>
       </c>
       <c r="N508" t="n">
-        <v>347</v>
+        <v>51</v>
       </c>
       <c r="O508" t="n">
-        <v>347</v>
+        <v>51</v>
       </c>
       <c r="R508" t="n">
-        <v>0.4148521468144293</v>
+        <v>0.06097250572776914</v>
       </c>
       <c r="U508" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AA508" t="inlineStr">
@@ -73654,7 +73654,7 @@
       </c>
       <c r="AS508" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT508" t="n">
@@ -73739,17 +73739,17 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
@@ -73768,17 +73768,17 @@
         </is>
       </c>
       <c r="N509" t="n">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="O509" t="n">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="R509" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.4363718547183478</v>
       </c>
       <c r="U509" t="inlineStr">
         <is>
-          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AA509" t="inlineStr">
@@ -73798,7 +73798,7 @@
       </c>
       <c r="AS509" t="inlineStr">
         <is>
-          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AT509" t="n">
@@ -73883,17 +73883,17 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Scarlet fever</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>猩红热</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -73912,17 +73912,17 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O510" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R510" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U510" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AA510" t="inlineStr">
@@ -73942,7 +73942,7 @@
       </c>
       <c r="AS510" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AT510" t="n">
@@ -74027,22 +74027,22 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Scarlet fever</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>猩红热</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -74056,17 +74056,17 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O511" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R511" t="n">
-        <v>0.01315093260795021</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U511" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AA511" t="inlineStr">
@@ -74086,7 +74086,7 @@
       </c>
       <c r="AS511" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AT511" t="n">
@@ -74171,22 +74171,22 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -74200,17 +74200,17 @@
         </is>
       </c>
       <c r="N512" t="n">
-        <v>546</v>
+        <v>12</v>
       </c>
       <c r="O512" t="n">
-        <v>546</v>
+        <v>12</v>
       </c>
       <c r="R512" t="n">
-        <v>0.6527644730855285</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U512" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA512" t="inlineStr">
@@ -74230,7 +74230,7 @@
       </c>
       <c r="AS512" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT512" t="n">
@@ -74315,17 +74315,17 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
@@ -74344,17 +74344,17 @@
         </is>
       </c>
       <c r="N513" t="n">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="O513" t="n">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="R513" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.6563510910695148</v>
       </c>
       <c r="U513" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA513" t="inlineStr">
@@ -74374,7 +74374,7 @@
       </c>
       <c r="AS513" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT513" t="n">
@@ -74459,17 +74459,17 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
@@ -74488,17 +74488,17 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>247</v>
+        <v>4</v>
       </c>
       <c r="O514" t="n">
-        <v>247</v>
+        <v>4</v>
       </c>
       <c r="R514" t="n">
-        <v>0.2952982140148819</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U514" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA514" t="inlineStr">
@@ -74518,7 +74518,7 @@
       </c>
       <c r="AS514" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT514" t="n">
@@ -74603,17 +74603,17 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -74632,17 +74632,17 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="O515" t="n">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="R515" t="n">
-        <v>0.02391078655990947</v>
+        <v>0.3000803713268638</v>
       </c>
       <c r="U515" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA515" t="inlineStr">
@@ -74662,7 +74662,7 @@
       </c>
       <c r="AS515" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT515" t="n">
@@ -74747,22 +74747,22 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -74776,17 +74776,17 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="O516" t="n">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="R516" t="n">
-        <v>0.7818827205090396</v>
+        <v>0.02510632588790494</v>
       </c>
       <c r="U516" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA516" t="inlineStr">
@@ -74806,7 +74806,7 @@
       </c>
       <c r="AS516" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT516" t="n">
@@ -74891,22 +74891,22 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -74920,17 +74920,17 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>33</v>
+        <v>726</v>
       </c>
       <c r="O517" t="n">
-        <v>33</v>
+        <v>726</v>
       </c>
       <c r="R517" t="n">
-        <v>0.03945279782385062</v>
+        <v>0.8679615521247137</v>
       </c>
       <c r="U517" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA517" t="inlineStr">
@@ -74950,7 +74950,7 @@
       </c>
       <c r="AS517" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT517" t="n">
@@ -75035,17 +75035,17 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
@@ -75064,17 +75064,17 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O518" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R518" t="n">
-        <v>0.03945279782385062</v>
+        <v>0.04543049446382799</v>
       </c>
       <c r="U518" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA518" t="inlineStr">
@@ -75094,7 +75094,7 @@
       </c>
       <c r="AS518" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT518" t="n">
@@ -75179,22 +75179,22 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -75208,17 +75208,17 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="O519" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="R519" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.04423495513583252</v>
       </c>
       <c r="U519" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA519" t="inlineStr">
@@ -75238,7 +75238,7 @@
       </c>
       <c r="AS519" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT519" t="n">
@@ -75323,22 +75323,22 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -75352,17 +75352,17 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O520" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R520" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA520" t="inlineStr">
@@ -75382,7 +75382,7 @@
       </c>
       <c r="AS520" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT520" t="n">
@@ -75467,17 +75467,17 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -75496,17 +75496,17 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="O521" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="R521" t="n">
-        <v>0.09444760691164239</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA521" t="inlineStr">
@@ -75526,7 +75526,7 @@
       </c>
       <c r="AS521" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT521" t="n">
@@ -75611,17 +75611,17 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
@@ -75640,17 +75640,17 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="O522" t="n">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="R522" t="n">
-        <v>0.1948729104632622</v>
+        <v>0.1052074608636017</v>
       </c>
       <c r="U522" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA522" t="inlineStr">
@@ -75670,7 +75670,7 @@
       </c>
       <c r="AS522" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT522" t="n">
@@ -75755,17 +75755,17 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
@@ -75784,17 +75784,17 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="O523" t="n">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="R523" t="n">
-        <v>0.07173235967972839</v>
+        <v>0.1960684497912576</v>
       </c>
       <c r="U523" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA523" t="inlineStr">
@@ -75814,7 +75814,7 @@
       </c>
       <c r="AS523" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT523" t="n">
@@ -75899,17 +75899,17 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -75928,17 +75928,17 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="O524" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="R524" t="n">
-        <v>0.01315093260795021</v>
+        <v>0.07531897766371483</v>
       </c>
       <c r="U524" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA524" t="inlineStr">
@@ -75958,7 +75958,7 @@
       </c>
       <c r="AS524" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT524" t="n">
@@ -76043,17 +76043,17 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -76072,17 +76072,17 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="O525" t="n">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="R525" t="n">
-        <v>0.2104149217272033</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U525" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA525" t="inlineStr">
@@ -76102,7 +76102,7 @@
       </c>
       <c r="AS525" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT525" t="n">
@@ -76187,17 +76187,17 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -76216,17 +76216,17 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="O526" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="R526" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.2151970790391852</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA526" t="inlineStr">
@@ -76246,7 +76246,7 @@
       </c>
       <c r="AS526" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT526" t="n">
@@ -76331,17 +76331,17 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -76360,17 +76360,17 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R527" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U527" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA527" t="inlineStr">
@@ -76390,7 +76390,7 @@
       </c>
       <c r="AS527" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT527" t="n">
@@ -76475,17 +76475,17 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -76504,17 +76504,17 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="O528" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="R528" t="n">
-        <v>0.2510632588790494</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U528" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA528" t="inlineStr">
@@ -76534,7 +76534,7 @@
       </c>
       <c r="AS528" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT528" t="n">
@@ -76619,17 +76619,17 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -76648,17 +76648,17 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="O529" t="n">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="R529" t="n">
-        <v>0.1434647193594568</v>
+        <v>0.2761695847669544</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA529" t="inlineStr">
@@ -76678,7 +76678,7 @@
       </c>
       <c r="AS529" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT529" t="n">
@@ -76763,17 +76763,17 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -76792,17 +76792,17 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="O530" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="R530" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.1530290339834206</v>
       </c>
       <c r="U530" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA530" t="inlineStr">
@@ -76822,7 +76822,7 @@
       </c>
       <c r="AS530" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT530" t="n">
@@ -76907,17 +76907,17 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
@@ -76946,7 +76946,7 @@
       </c>
       <c r="U531" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA531" t="inlineStr">
@@ -76966,7 +76966,7 @@
       </c>
       <c r="AS531" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT531" t="n">
@@ -77051,22 +77051,22 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -77080,17 +77080,17 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="O532" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="R532" t="n">
-        <v>0.04543049446382799</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U532" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA532" t="inlineStr">
@@ -77110,7 +77110,7 @@
       </c>
       <c r="AS532" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT532" t="n">
@@ -77195,22 +77195,22 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -77224,17 +77224,17 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O533" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R533" t="n">
-        <v>0.04184387647984157</v>
+        <v>0.04543049446382799</v>
       </c>
       <c r="U533" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA533" t="inlineStr">
@@ -77254,7 +77254,7 @@
       </c>
       <c r="AS533" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT533" t="n">
@@ -77339,22 +77339,22 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -77368,17 +77368,17 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="O534" t="n">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="R534" t="n">
-        <v>0.1542245733114161</v>
+        <v>0.04303941580783704</v>
       </c>
       <c r="U534" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA534" t="inlineStr">
@@ -77398,7 +77398,7 @@
       </c>
       <c r="AS534" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT534" t="n">
@@ -77483,17 +77483,17 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
@@ -77512,17 +77512,17 @@
         </is>
       </c>
       <c r="N535" t="n">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="O535" t="n">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="R535" t="n">
-        <v>0.005977696639977366</v>
+        <v>0.1757442812153346</v>
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA535" t="inlineStr">
@@ -77542,7 +77542,7 @@
       </c>
       <c r="AS535" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT535" t="n">
@@ -77627,22 +77627,22 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
@@ -77656,17 +77656,17 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>199</v>
+        <v>6</v>
       </c>
       <c r="O536" t="n">
-        <v>199</v>
+        <v>6</v>
       </c>
       <c r="R536" t="n">
-        <v>0.2379123262710992</v>
+        <v>0.007173235967972841</v>
       </c>
       <c r="U536" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA536" t="inlineStr">
@@ -77686,7 +77686,7 @@
       </c>
       <c r="AS536" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT536" t="n">
@@ -77771,17 +77771,17 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -77800,17 +77800,17 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="O537" t="n">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="R537" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.2534543375350404</v>
       </c>
       <c r="U537" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA537" t="inlineStr">
@@ -77830,7 +77830,7 @@
       </c>
       <c r="AS537" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT537" t="n">
@@ -77872,6 +77872,150 @@
         </is>
       </c>
       <c r="BC537" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N538" t="n">
+        <v>18</v>
+      </c>
+      <c r="O538" t="n">
+        <v>18</v>
+      </c>
+      <c r="R538" t="n">
+        <v>0.02151970790391852</v>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO538" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP538" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS538" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT538" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV538" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW538" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX538" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY538" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ538" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA538" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB538" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC538" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -77993,7 +78137,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10">
@@ -78003,7 +78147,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11">
@@ -78055,7 +78199,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60862</v>
+        <v>61198</v>
       </c>
     </row>
     <row r="16">

--- a/countries/de/2026-2029.xlsx
+++ b/countries/de/2026-2029.xlsx
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R8" t="n">
-        <v>0.09444760691164239</v>
+        <v>0.09564314623963786</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -5368,13 +5368,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O34" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1829175171833074</v>
+        <v>0.1841130565113029</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O49" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R49" t="n">
-        <v>0.2642141914869996</v>
+        <v>0.2654097308149951</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -15304,13 +15304,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O103" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R103" t="n">
-        <v>0.381377045630556</v>
+        <v>0.3825725849585515</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -19480,13 +19480,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R132" t="n">
-        <v>0.01554201126394116</v>
+        <v>0.01673755059193663</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O147" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R147" t="n">
-        <v>0.08727437094366955</v>
+        <v>0.08846991027166504</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -35032,13 +35032,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O240" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R240" t="n">
-        <v>0.2713874274549725</v>
+        <v>0.270191888126977</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -39064,13 +39064,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O268" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R268" t="n">
-        <v>0.5045175964140898</v>
+        <v>0.5057131357420852</v>
       </c>
       <c r="U268" t="inlineStr">
         <is>
@@ -43528,13 +43528,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="O299" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="R299" t="n">
-        <v>1.761029430137332</v>
+        <v>1.762224969465328</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
@@ -45400,13 +45400,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O312" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R312" t="n">
-        <v>0.4578915626222663</v>
+        <v>0.4590871019502618</v>
       </c>
       <c r="U312" t="inlineStr">
         <is>
@@ -47272,13 +47272,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O325" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R325" t="n">
-        <v>0.01912862924792757</v>
+        <v>0.02032416857592305</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
@@ -47704,13 +47704,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O328" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R328" t="n">
-        <v>0.2797562027509408</v>
+        <v>0.2785606634229453</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
@@ -48568,13 +48568,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O334" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R334" t="n">
-        <v>0.3682261130226058</v>
+        <v>0.3694216523506013</v>
       </c>
       <c r="U334" t="inlineStr">
         <is>
@@ -50152,13 +50152,13 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="O345" t="n">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="R345" t="n">
-        <v>1.655821969273731</v>
+        <v>1.657017508601726</v>
       </c>
       <c r="U345" t="inlineStr">
         <is>
@@ -51880,13 +51880,13 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O357" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R357" t="n">
-        <v>0.4734335738862075</v>
+        <v>0.4758246525421984</v>
       </c>
       <c r="U357" t="inlineStr">
         <is>
@@ -52024,13 +52024,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O358" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="R358" t="n">
-        <v>0.2211747756791626</v>
+        <v>0.222370315007158</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
@@ -53896,13 +53896,13 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O371" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R371" t="n">
-        <v>0.05379926975979631</v>
+        <v>0.05499480908779177</v>
       </c>
       <c r="U371" t="inlineStr">
         <is>
@@ -54040,13 +54040,13 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O372" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R372" t="n">
-        <v>0.3204045399027869</v>
+        <v>0.3192090005747914</v>
       </c>
       <c r="U372" t="inlineStr">
         <is>
@@ -54184,13 +54184,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O373" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R373" t="n">
-        <v>0.1518334946554251</v>
+        <v>0.1506379553274297</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -56776,13 +56776,13 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="O391" t="n">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="R391" t="n">
-        <v>1.499206317306324</v>
+        <v>1.50279293529031</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
@@ -57352,13 +57352,13 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O395" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R395" t="n">
-        <v>0.01075985395195926</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U395" t="inlineStr">
         <is>
@@ -57784,13 +57784,13 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O398" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R398" t="n">
-        <v>0.1291182474235111</v>
+        <v>0.1303137867515066</v>
       </c>
       <c r="U398" t="inlineStr">
         <is>
@@ -60952,13 +60952,13 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O420" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R420" t="n">
-        <v>0.2964937533428774</v>
+        <v>0.2976892926708729</v>
       </c>
       <c r="U420" t="inlineStr">
         <is>
@@ -61672,13 +61672,13 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O425" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R425" t="n">
-        <v>0.05858142707177819</v>
+        <v>0.05977696639977367</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -61816,13 +61816,13 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O426" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="R426" t="n">
-        <v>0.4531094053102844</v>
+        <v>0.4543049446382799</v>
       </c>
       <c r="U426" t="inlineStr">
         <is>
@@ -62968,13 +62968,13 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O434" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R434" t="n">
-        <v>0.3299688545267507</v>
+        <v>0.3287733151987552</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
@@ -63112,13 +63112,13 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O435" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R435" t="n">
-        <v>0.04184387647984157</v>
+        <v>0.04303941580783704</v>
       </c>
       <c r="U435" t="inlineStr">
         <is>
@@ -63400,13 +63400,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="O437" t="n">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="R437" t="n">
-        <v>1.407149789050672</v>
+        <v>1.419105182330627</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -63688,13 +63688,13 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O439" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R439" t="n">
-        <v>0.07651451699171029</v>
+        <v>0.07890559564770125</v>
       </c>
       <c r="U439" t="inlineStr">
         <is>
@@ -65128,13 +65128,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="O449" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="R449" t="n">
-        <v>0.3945279782385062</v>
+        <v>0.3981145962224927</v>
       </c>
       <c r="U449" t="inlineStr">
         <is>
@@ -65272,13 +65272,13 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="O450" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="R450" t="n">
-        <v>0.202046146431235</v>
+        <v>0.2056327644152214</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
@@ -66280,13 +66280,13 @@
         </is>
       </c>
       <c r="N457" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O457" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R457" t="n">
-        <v>0.2199792363511671</v>
+        <v>0.2211747756791626</v>
       </c>
       <c r="U457" t="inlineStr">
         <is>
@@ -67288,13 +67288,13 @@
         </is>
       </c>
       <c r="N464" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O464" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R464" t="n">
-        <v>0.3192090005747914</v>
+        <v>0.3168179219188005</v>
       </c>
       <c r="U464" t="inlineStr">
         <is>
@@ -67576,13 +67576,13 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O466" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R466" t="n">
-        <v>0.1422691800314613</v>
+        <v>0.1434647193594568</v>
       </c>
       <c r="U466" t="inlineStr">
         <is>
@@ -67864,13 +67864,13 @@
         </is>
       </c>
       <c r="N468" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O468" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R468" t="n">
-        <v>0.06216804505576462</v>
+        <v>0.06455912371175557</v>
       </c>
       <c r="U468" t="inlineStr">
         <is>
@@ -68008,13 +68008,13 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="O469" t="n">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="R469" t="n">
-        <v>0.5308194616299902</v>
+        <v>0.5391882369259585</v>
       </c>
       <c r="U469" t="inlineStr">
         <is>
@@ -69160,13 +69160,13 @@
         </is>
       </c>
       <c r="N477" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O477" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R477" t="n">
-        <v>0.2905160567029</v>
+        <v>0.2917115960308955</v>
       </c>
       <c r="U477" t="inlineStr">
         <is>
@@ -69448,13 +69448,13 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>1049</v>
+        <v>1085</v>
       </c>
       <c r="O479" t="n">
-        <v>1049</v>
+        <v>1085</v>
       </c>
       <c r="R479" t="n">
-        <v>1.254120755067252</v>
+        <v>1.297160170875089</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
@@ -69736,13 +69736,13 @@
         </is>
       </c>
       <c r="N481" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O481" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R481" t="n">
-        <v>0.07053682035173293</v>
+        <v>0.07173235967972839</v>
       </c>
       <c r="U481" t="inlineStr">
         <is>
@@ -70024,13 +70024,13 @@
         </is>
       </c>
       <c r="N483" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O483" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R483" t="n">
-        <v>0.1123806968315745</v>
+        <v>0.11357623615957</v>
       </c>
       <c r="U483" t="inlineStr">
         <is>
@@ -70312,13 +70312,13 @@
         </is>
       </c>
       <c r="N485" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O485" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R485" t="n">
-        <v>0.06814574169574199</v>
+        <v>0.06934128102373746</v>
       </c>
       <c r="U485" t="inlineStr">
         <is>
@@ -70600,13 +70600,13 @@
         </is>
       </c>
       <c r="N487" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O487" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="R487" t="n">
-        <v>0.247476640895063</v>
+        <v>0.2498677195510539</v>
       </c>
       <c r="U487" t="inlineStr">
         <is>
@@ -71032,13 +71032,13 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="O490" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="R490" t="n">
-        <v>0.3371420904947235</v>
+        <v>0.3502930231026737</v>
       </c>
       <c r="U490" t="inlineStr">
         <is>
@@ -71176,13 +71176,13 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O491" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="R491" t="n">
-        <v>0.2104149217272033</v>
+        <v>0.2128060003831942</v>
       </c>
       <c r="U491" t="inlineStr">
         <is>
@@ -71896,13 +71896,13 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O496" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R496" t="n">
-        <v>0.08846991027166504</v>
+        <v>0.0896654495996605</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
@@ -72040,13 +72040,13 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O497" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="R497" t="n">
-        <v>0.1876996744952893</v>
+        <v>0.1924818318072712</v>
       </c>
       <c r="U497" t="inlineStr">
         <is>
@@ -72328,13 +72328,13 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O499" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R499" t="n">
-        <v>0.2462811015670675</v>
+        <v>0.245085562239072</v>
       </c>
       <c r="U499" t="inlineStr">
         <is>
@@ -72472,13 +72472,13 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R500" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U500" t="inlineStr">
         <is>
@@ -72760,13 +72760,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="O502" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="R502" t="n">
-        <v>1.097505103099845</v>
+        <v>1.09870064242784</v>
       </c>
       <c r="U502" t="inlineStr">
         <is>
@@ -72904,13 +72904,13 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O503" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R503" t="n">
-        <v>0.04184387647984157</v>
+        <v>0.04303941580783704</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
@@ -73048,13 +73048,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O504" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R504" t="n">
-        <v>0.2952982140148819</v>
+        <v>0.2917115960308955</v>
       </c>
       <c r="U504" t="inlineStr">
         <is>
@@ -73192,13 +73192,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O505" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R505" t="n">
-        <v>0.1542245733114161</v>
+        <v>0.1554201126394116</v>
       </c>
       <c r="U505" t="inlineStr">
         <is>
@@ -73336,13 +73336,13 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="O506" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="R506" t="n">
-        <v>0.09086098892765598</v>
+        <v>0.09683868556763335</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
@@ -73624,13 +73624,13 @@
         </is>
       </c>
       <c r="N508" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O508" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R508" t="n">
-        <v>0.06097250572776914</v>
+        <v>0.06336358438376009</v>
       </c>
       <c r="U508" t="inlineStr">
         <is>
@@ -73768,13 +73768,13 @@
         </is>
       </c>
       <c r="N509" t="n">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="O509" t="n">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="R509" t="n">
-        <v>0.4363718547183478</v>
+        <v>0.4555004839662754</v>
       </c>
       <c r="U509" t="inlineStr">
         <is>
@@ -74344,13 +74344,13 @@
         </is>
       </c>
       <c r="N513" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="O513" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="R513" t="n">
-        <v>0.6563510910695148</v>
+        <v>0.6611332483814968</v>
       </c>
       <c r="U513" t="inlineStr">
         <is>
@@ -74488,13 +74488,13 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R514" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U514" t="inlineStr">
         <is>
@@ -74632,13 +74632,13 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O515" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="R515" t="n">
-        <v>0.3000803713268638</v>
+        <v>0.3024714499828547</v>
       </c>
       <c r="U515" t="inlineStr">
         <is>
@@ -74776,13 +74776,13 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O516" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R516" t="n">
-        <v>0.02510632588790494</v>
+        <v>0.02749740454389589</v>
       </c>
       <c r="U516" t="inlineStr">
         <is>
@@ -74920,13 +74920,13 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>726</v>
+        <v>780</v>
       </c>
       <c r="O517" t="n">
-        <v>726</v>
+        <v>780</v>
       </c>
       <c r="R517" t="n">
-        <v>0.8679615521247137</v>
+        <v>0.9325206758364692</v>
       </c>
       <c r="U517" t="inlineStr">
         <is>
@@ -75064,13 +75064,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O518" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="R518" t="n">
-        <v>0.04543049446382799</v>
+        <v>0.05021265177580988</v>
       </c>
       <c r="U518" t="inlineStr">
         <is>
@@ -75208,13 +75208,13 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="O519" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="R519" t="n">
-        <v>0.04423495513583252</v>
+        <v>0.05140819110380536</v>
       </c>
       <c r="U519" t="inlineStr">
         <is>
@@ -75640,13 +75640,13 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="O522" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="R522" t="n">
-        <v>0.1052074608636017</v>
+        <v>0.111185157503579</v>
       </c>
       <c r="U522" t="inlineStr">
         <is>
@@ -75784,13 +75784,13 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O523" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R523" t="n">
-        <v>0.1960684497912576</v>
+        <v>0.1972639891192531</v>
       </c>
       <c r="U523" t="inlineStr">
         <is>
@@ -76216,13 +76216,13 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O526" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R526" t="n">
-        <v>0.2151970790391852</v>
+        <v>0.2175881576951762</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
@@ -76648,13 +76648,13 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="O529" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="R529" t="n">
-        <v>0.2761695847669544</v>
+        <v>0.2917115960308955</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
@@ -76792,13 +76792,13 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="O530" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="R530" t="n">
-        <v>0.1530290339834206</v>
+        <v>0.1625933486073844</v>
       </c>
       <c r="U530" t="inlineStr">
         <is>
@@ -77080,13 +77080,13 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O532" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R532" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U532" t="inlineStr">
         <is>
@@ -77224,13 +77224,13 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O533" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R533" t="n">
-        <v>0.04543049446382799</v>
+        <v>0.04423495513583252</v>
       </c>
       <c r="U533" t="inlineStr">
         <is>
@@ -77368,13 +77368,13 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O534" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R534" t="n">
-        <v>0.04303941580783704</v>
+        <v>0.04543049446382799</v>
       </c>
       <c r="U534" t="inlineStr">
         <is>
@@ -77512,13 +77512,13 @@
         </is>
       </c>
       <c r="N535" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="O535" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="R535" t="n">
-        <v>0.1757442812153346</v>
+        <v>0.1829175171833074</v>
       </c>
       <c r="U535" t="inlineStr">
         <is>
@@ -77656,13 +77656,13 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O536" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R536" t="n">
-        <v>0.007173235967972841</v>
+        <v>0.009564314623963786</v>
       </c>
       <c r="U536" t="inlineStr">
         <is>
@@ -77800,13 +77800,13 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O537" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R537" t="n">
-        <v>0.2534543375350404</v>
+        <v>0.2558454161910313</v>
       </c>
       <c r="U537" t="inlineStr">
         <is>
@@ -77944,13 +77944,13 @@
         </is>
       </c>
       <c r="N538" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O538" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R538" t="n">
-        <v>0.02151970790391852</v>
+        <v>0.022715247231914</v>
       </c>
       <c r="U538" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61198</v>
+        <v>61441</v>
       </c>
     </row>
     <row r="16">

--- a/countries/de/2026-2029.xlsx
+++ b/countries/de/2026-2029.xlsx
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R8" t="n">
-        <v>0.09564314623963786</v>
+        <v>0.09683868556763335</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -17176,13 +17176,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="O116" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="R116" t="n">
-        <v>2.19740128485568</v>
+        <v>2.198596824183675</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O136" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R136" t="n">
-        <v>0.06097250572776914</v>
+        <v>0.06216804505576462</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -23656,13 +23656,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="O161" t="n">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="R161" t="n">
-        <v>1.972639891192531</v>
+        <v>1.973835430520526</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -27976,13 +27976,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O191" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R191" t="n">
-        <v>0.2331301689591173</v>
+        <v>0.2343257082871128</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -35752,13 +35752,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O245" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R245" t="n">
-        <v>0.08249221363168767</v>
+        <v>0.0812966743036922</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -37336,13 +37336,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="O256" t="n">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="R256" t="n">
-        <v>1.733532025593436</v>
+        <v>1.735923104249427</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
@@ -38632,13 +38632,13 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O265" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R265" t="n">
-        <v>0.4387629333743387</v>
+        <v>0.4399584727023342</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -41224,13 +41224,13 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O283" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R283" t="n">
-        <v>0.04782157311981893</v>
+        <v>0.04901711244781441</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
@@ -41368,13 +41368,13 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O284" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R284" t="n">
-        <v>0.2785606634229453</v>
+        <v>0.2797562027509408</v>
       </c>
       <c r="U284" t="inlineStr">
         <is>
@@ -43528,13 +43528,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="O299" t="n">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="R299" t="n">
-        <v>1.762224969465328</v>
+        <v>1.764616048121319</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
@@ -43672,13 +43672,13 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O300" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R300" t="n">
-        <v>0.08249221363168767</v>
+        <v>0.08368775295968314</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
@@ -45400,13 +45400,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O312" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="R312" t="n">
-        <v>0.4590871019502618</v>
+        <v>0.4602826412782573</v>
       </c>
       <c r="U312" t="inlineStr">
         <is>
@@ -45544,13 +45544,13 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O313" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R313" t="n">
-        <v>0.2582364948470223</v>
+        <v>0.2594320341750177</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
@@ -47272,13 +47272,13 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O325" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R325" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.02151970790391852</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
@@ -48424,13 +48424,13 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O333" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R333" t="n">
-        <v>0.07890559564770125</v>
+        <v>0.08010113497569672</v>
       </c>
       <c r="U333" t="inlineStr">
         <is>
@@ -52024,13 +52024,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O358" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R358" t="n">
-        <v>0.222370315007158</v>
+        <v>0.2235658543351535</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
@@ -54040,13 +54040,13 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O372" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R372" t="n">
-        <v>0.3192090005747914</v>
+        <v>0.3180134612467959</v>
       </c>
       <c r="U372" t="inlineStr">
         <is>
@@ -54184,13 +54184,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O373" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="R373" t="n">
-        <v>0.1506379553274297</v>
+        <v>0.1530290339834206</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -54328,13 +54328,13 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O374" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R374" t="n">
-        <v>0.1398781013754704</v>
+        <v>0.1410736407034659</v>
       </c>
       <c r="U374" t="inlineStr">
         <is>
@@ -54904,13 +54904,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O378" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R378" t="n">
-        <v>0.4076789108464564</v>
+        <v>0.4088744501744519</v>
       </c>
       <c r="U378" t="inlineStr">
         <is>
@@ -56776,13 +56776,13 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="O391" t="n">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="R391" t="n">
-        <v>1.50279293529031</v>
+        <v>1.507575092602292</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
@@ -56920,13 +56920,13 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O392" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R392" t="n">
-        <v>0.07771005631970578</v>
+        <v>0.07890559564770125</v>
       </c>
       <c r="U392" t="inlineStr">
         <is>
@@ -57064,13 +57064,13 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O393" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R393" t="n">
-        <v>0.0896654495996605</v>
+        <v>0.09086098892765598</v>
       </c>
       <c r="U393" t="inlineStr">
         <is>
@@ -59944,13 +59944,13 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O413" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R413" t="n">
-        <v>0.2534543375350404</v>
+        <v>0.2558454161910313</v>
       </c>
       <c r="U413" t="inlineStr">
         <is>
@@ -61672,13 +61672,13 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O425" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R425" t="n">
-        <v>0.05977696639977367</v>
+        <v>0.06216804505576462</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -61816,13 +61816,13 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O426" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R426" t="n">
-        <v>0.4543049446382799</v>
+        <v>0.4566960232942708</v>
       </c>
       <c r="U426" t="inlineStr">
         <is>
@@ -62248,13 +62248,13 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R429" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U429" t="inlineStr">
         <is>
@@ -63400,13 +63400,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="O437" t="n">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="R437" t="n">
-        <v>1.419105182330627</v>
+        <v>1.423887339642609</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -64696,13 +64696,13 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O446" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R446" t="n">
-        <v>0.2905160567029</v>
+        <v>0.2917115960308955</v>
       </c>
       <c r="U446" t="inlineStr">
         <is>
@@ -65272,13 +65272,13 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O450" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R450" t="n">
-        <v>0.2056327644152214</v>
+        <v>0.2068283037432169</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
@@ -66280,13 +66280,13 @@
         </is>
       </c>
       <c r="N457" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O457" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="R457" t="n">
-        <v>0.2211747756791626</v>
+        <v>0.2235658543351535</v>
       </c>
       <c r="U457" t="inlineStr">
         <is>
@@ -67000,13 +67000,13 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="O462" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="R462" t="n">
-        <v>1.030554900732098</v>
+        <v>1.031750440060094</v>
       </c>
       <c r="U462" t="inlineStr">
         <is>
@@ -67288,13 +67288,13 @@
         </is>
       </c>
       <c r="N464" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="O464" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="R464" t="n">
-        <v>0.3168179219188005</v>
+        <v>0.313231303934814</v>
       </c>
       <c r="U464" t="inlineStr">
         <is>
@@ -67576,13 +67576,13 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O466" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R466" t="n">
-        <v>0.1434647193594568</v>
+        <v>0.1446602586874523</v>
       </c>
       <c r="U466" t="inlineStr">
         <is>
@@ -67864,13 +67864,13 @@
         </is>
       </c>
       <c r="N468" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O468" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R468" t="n">
-        <v>0.06455912371175557</v>
+        <v>0.06695020236774651</v>
       </c>
       <c r="U468" t="inlineStr">
         <is>
@@ -68008,13 +68008,13 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O469" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R469" t="n">
-        <v>0.5391882369259585</v>
+        <v>0.540383776253954</v>
       </c>
       <c r="U469" t="inlineStr">
         <is>
@@ -68440,13 +68440,13 @@
         </is>
       </c>
       <c r="N472" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O472" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R472" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.007173235967972841</v>
       </c>
       <c r="U472" t="inlineStr">
         <is>
@@ -68872,13 +68872,13 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O475" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R475" t="n">
-        <v>0.005977696639977366</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U475" t="inlineStr">
         <is>
@@ -69448,13 +69448,13 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="O479" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="R479" t="n">
-        <v>1.297160170875089</v>
+        <v>1.321070957434998</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
@@ -69592,13 +69592,13 @@
         </is>
       </c>
       <c r="N480" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O480" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R480" t="n">
-        <v>0.07053682035173293</v>
+        <v>0.07173235967972839</v>
       </c>
       <c r="U480" t="inlineStr">
         <is>
@@ -70024,13 +70024,13 @@
         </is>
       </c>
       <c r="N483" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O483" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="R483" t="n">
-        <v>0.11357623615957</v>
+        <v>0.1183583934715519</v>
       </c>
       <c r="U483" t="inlineStr">
         <is>
@@ -70168,13 +70168,13 @@
         </is>
       </c>
       <c r="N484" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O484" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R484" t="n">
-        <v>0.1948729104632622</v>
+        <v>0.1960684497912576</v>
       </c>
       <c r="U484" t="inlineStr">
         <is>
@@ -71032,13 +71032,13 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="O490" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="R490" t="n">
-        <v>0.3502930231026737</v>
+        <v>0.3598573377266375</v>
       </c>
       <c r="U490" t="inlineStr">
         <is>
@@ -71176,13 +71176,13 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O491" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R491" t="n">
-        <v>0.2128060003831942</v>
+        <v>0.2140015397111897</v>
       </c>
       <c r="U491" t="inlineStr">
         <is>
@@ -71291,17 +71291,17 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
@@ -71320,17 +71320,17 @@
         </is>
       </c>
       <c r="N492" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O492" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R492" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.005977696639977366</v>
       </c>
       <c r="U492" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA492" t="inlineStr">
@@ -71350,7 +71350,7 @@
       </c>
       <c r="AS492" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT492" t="n">
@@ -71435,17 +71435,17 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
@@ -71464,17 +71464,17 @@
         </is>
       </c>
       <c r="N493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R493" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U493" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA493" t="inlineStr">
@@ -71494,7 +71494,7 @@
       </c>
       <c r="AS493" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT493" t="n">
@@ -71579,22 +71579,22 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>West Nile virus</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>西尼罗病毒</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -71608,17 +71608,17 @@
         </is>
       </c>
       <c r="N494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R494" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U494" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA494" t="inlineStr">
@@ -71638,7 +71638,7 @@
       </c>
       <c r="AS494" t="inlineStr">
         <is>
-          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT494" t="n">
@@ -71723,17 +71723,17 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -71752,17 +71752,17 @@
         </is>
       </c>
       <c r="N495" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="O495" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="R495" t="n">
-        <v>0.03825725849585514</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U495" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA495" t="inlineStr">
@@ -71782,7 +71782,7 @@
       </c>
       <c r="AS495" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AT495" t="n">
@@ -71867,22 +71867,22 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -71896,17 +71896,17 @@
         </is>
       </c>
       <c r="N496" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="O496" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="R496" t="n">
-        <v>0.0896654495996605</v>
+        <v>0.03825725849585514</v>
       </c>
       <c r="U496" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA496" t="inlineStr">
@@ -71926,7 +71926,7 @@
       </c>
       <c r="AS496" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT496" t="n">
@@ -72011,22 +72011,22 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -72040,17 +72040,17 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="O497" t="n">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="R497" t="n">
-        <v>0.1924818318072712</v>
+        <v>0.09205652825565144</v>
       </c>
       <c r="U497" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA497" t="inlineStr">
@@ -72070,7 +72070,7 @@
       </c>
       <c r="AS497" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT497" t="n">
@@ -72155,17 +72155,17 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
@@ -72184,17 +72184,17 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="O498" t="n">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="R498" t="n">
-        <v>0.0179330899199321</v>
+        <v>0.1948729104632622</v>
       </c>
       <c r="U498" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA498" t="inlineStr">
@@ -72214,7 +72214,7 @@
       </c>
       <c r="AS498" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT498" t="n">
@@ -72299,22 +72299,22 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -72328,17 +72328,17 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="O499" t="n">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="R499" t="n">
-        <v>0.245085562239072</v>
+        <v>0.0179330899199321</v>
       </c>
       <c r="U499" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA499" t="inlineStr">
@@ -72358,7 +72358,7 @@
       </c>
       <c r="AS499" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT499" t="n">
@@ -72443,17 +72443,17 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>D234</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>副伤寒</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
@@ -72472,17 +72472,17 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>3</v>
+        <v>205</v>
       </c>
       <c r="O500" t="n">
-        <v>3</v>
+        <v>205</v>
       </c>
       <c r="R500" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.245085562239072</v>
       </c>
       <c r="U500" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA500" t="inlineStr">
@@ -72502,7 +72502,7 @@
       </c>
       <c r="AS500" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT500" t="n">
@@ -72587,17 +72587,17 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D234</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>副伤寒</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
@@ -72616,17 +72616,17 @@
         </is>
       </c>
       <c r="N501" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O501" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="R501" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U501" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AA501" t="inlineStr">
@@ -72646,7 +72646,7 @@
       </c>
       <c r="AS501" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AT501" t="n">
@@ -72731,27 +72731,27 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D236</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -72760,17 +72760,17 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>919</v>
+        <v>17</v>
       </c>
       <c r="O502" t="n">
-        <v>919</v>
+        <v>17</v>
       </c>
       <c r="R502" t="n">
-        <v>1.09870064242784</v>
+        <v>0.02032416857592305</v>
       </c>
       <c r="U502" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AA502" t="inlineStr">
@@ -72790,7 +72790,7 @@
       </c>
       <c r="AS502" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AT502" t="n">
@@ -72875,17 +72875,17 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
@@ -72904,17 +72904,17 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>36</v>
+        <v>919</v>
       </c>
       <c r="O503" t="n">
-        <v>36</v>
+        <v>919</v>
       </c>
       <c r="R503" t="n">
-        <v>0.04303941580783704</v>
+        <v>1.09870064242784</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AA503" t="inlineStr">
@@ -72934,7 +72934,7 @@
       </c>
       <c r="AS503" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AT503" t="n">
@@ -73019,17 +73019,17 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>D008</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>乙型肝炎</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
@@ -73048,17 +73048,17 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="O504" t="n">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="R504" t="n">
-        <v>0.2917115960308955</v>
+        <v>0.04423495513583252</v>
       </c>
       <c r="U504" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AA504" t="inlineStr">
@@ -73078,7 +73078,7 @@
       </c>
       <c r="AS504" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AT504" t="n">
@@ -73163,17 +73163,17 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
@@ -73192,17 +73192,17 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="O505" t="n">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="R505" t="n">
-        <v>0.1554201126394116</v>
+        <v>0.2893205173749046</v>
       </c>
       <c r="U505" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AA505" t="inlineStr">
@@ -73222,7 +73222,7 @@
       </c>
       <c r="AS505" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AT505" t="n">
@@ -73307,17 +73307,17 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
@@ -73336,17 +73336,17 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="O506" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="R506" t="n">
-        <v>0.09683868556763335</v>
+        <v>0.1554201126394116</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AA506" t="inlineStr">
@@ -73366,7 +73366,7 @@
       </c>
       <c r="AS506" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AT506" t="n">
@@ -73451,17 +73451,17 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
@@ -73480,17 +73480,17 @@
         </is>
       </c>
       <c r="N507" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="O507" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="R507" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.1052074608636017</v>
       </c>
       <c r="U507" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AA507" t="inlineStr">
@@ -73510,7 +73510,7 @@
       </c>
       <c r="AS507" t="inlineStr">
         <is>
-          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AT507" t="n">
@@ -73595,22 +73595,22 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -73624,17 +73624,17 @@
         </is>
       </c>
       <c r="N508" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="O508" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="R508" t="n">
-        <v>0.06336358438376009</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U508" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AA508" t="inlineStr">
@@ -73654,7 +73654,7 @@
       </c>
       <c r="AS508" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_67a8383c9171c23bf4f8d0335669</t>
         </is>
       </c>
       <c r="AT508" t="n">
@@ -73739,17 +73739,17 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
@@ -73768,17 +73768,17 @@
         </is>
       </c>
       <c r="N509" t="n">
-        <v>381</v>
+        <v>54</v>
       </c>
       <c r="O509" t="n">
-        <v>381</v>
+        <v>54</v>
       </c>
       <c r="R509" t="n">
-        <v>0.4555004839662754</v>
+        <v>0.06455912371175557</v>
       </c>
       <c r="U509" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AA509" t="inlineStr">
@@ -73798,7 +73798,7 @@
       </c>
       <c r="AS509" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT509" t="n">
@@ -73883,17 +73883,17 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -73912,17 +73912,17 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="O510" t="n">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="R510" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.4686514165742255</v>
       </c>
       <c r="U510" t="inlineStr">
         <is>
-          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AA510" t="inlineStr">
@@ -73942,7 +73942,7 @@
       </c>
       <c r="AS510" t="inlineStr">
         <is>
-          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AT510" t="n">
@@ -74027,17 +74027,17 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Scarlet fever</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>猩红热</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
@@ -74056,17 +74056,17 @@
         </is>
       </c>
       <c r="N511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R511" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U511" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AA511" t="inlineStr">
@@ -74086,7 +74086,7 @@
       </c>
       <c r="AS511" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_cf73ff0499232520079e651b4d44</t>
         </is>
       </c>
       <c r="AT511" t="n">
@@ -74171,22 +74171,22 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Scarlet fever</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>猩红热</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -74200,17 +74200,17 @@
         </is>
       </c>
       <c r="N512" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O512" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R512" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U512" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AA512" t="inlineStr">
@@ -74230,7 +74230,7 @@
       </c>
       <c r="AS512" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AT512" t="n">
@@ -74315,22 +74315,22 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -74344,17 +74344,17 @@
         </is>
       </c>
       <c r="N513" t="n">
-        <v>553</v>
+        <v>4</v>
       </c>
       <c r="O513" t="n">
-        <v>553</v>
+        <v>4</v>
       </c>
       <c r="R513" t="n">
-        <v>0.6611332483814968</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U513" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AA513" t="inlineStr">
@@ -74374,7 +74374,7 @@
       </c>
       <c r="AS513" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AT513" t="n">
@@ -74459,22 +74459,22 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -74488,17 +74488,17 @@
         </is>
       </c>
       <c r="N514" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O514" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R514" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U514" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA514" t="inlineStr">
@@ -74518,7 +74518,7 @@
       </c>
       <c r="AS514" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT514" t="n">
@@ -74603,17 +74603,17 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -74632,17 +74632,17 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>253</v>
+        <v>553</v>
       </c>
       <c r="O515" t="n">
-        <v>253</v>
+        <v>553</v>
       </c>
       <c r="R515" t="n">
-        <v>0.3024714499828547</v>
+        <v>0.6611332483814968</v>
       </c>
       <c r="U515" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA515" t="inlineStr">
@@ -74662,7 +74662,7 @@
       </c>
       <c r="AS515" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT515" t="n">
@@ -74747,17 +74747,17 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
@@ -74776,17 +74776,17 @@
         </is>
       </c>
       <c r="N516" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O516" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="R516" t="n">
-        <v>0.02749740454389589</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U516" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA516" t="inlineStr">
@@ -74806,7 +74806,7 @@
       </c>
       <c r="AS516" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT516" t="n">
@@ -74891,22 +74891,22 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -74920,17 +74920,17 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>780</v>
+        <v>256</v>
       </c>
       <c r="O517" t="n">
-        <v>780</v>
+        <v>256</v>
       </c>
       <c r="R517" t="n">
-        <v>0.9325206758364692</v>
+        <v>0.3060580679668412</v>
       </c>
       <c r="U517" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA517" t="inlineStr">
@@ -74950,7 +74950,7 @@
       </c>
       <c r="AS517" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT517" t="n">
@@ -75035,22 +75035,22 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -75064,17 +75064,17 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O518" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="R518" t="n">
-        <v>0.05021265177580988</v>
+        <v>0.02869294387189136</v>
       </c>
       <c r="U518" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA518" t="inlineStr">
@@ -75094,7 +75094,7 @@
       </c>
       <c r="AS518" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT518" t="n">
@@ -75179,22 +75179,22 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -75208,17 +75208,17 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>43</v>
+        <v>829</v>
       </c>
       <c r="O519" t="n">
-        <v>43</v>
+        <v>829</v>
       </c>
       <c r="R519" t="n">
-        <v>0.05140819110380536</v>
+        <v>0.9911021029082474</v>
       </c>
       <c r="U519" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA519" t="inlineStr">
@@ -75238,7 +75238,7 @@
       </c>
       <c r="AS519" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT519" t="n">
@@ -75323,22 +75323,22 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -75352,17 +75352,17 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O520" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="R520" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.05140819110380536</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA520" t="inlineStr">
@@ -75382,7 +75382,7 @@
       </c>
       <c r="AS520" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT520" t="n">
@@ -75467,22 +75467,22 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -75496,17 +75496,17 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O521" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="R521" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.05738588774378273</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA521" t="inlineStr">
@@ -75526,7 +75526,7 @@
       </c>
       <c r="AS521" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT521" t="n">
@@ -75611,22 +75611,22 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -75640,17 +75640,17 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="O522" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="R522" t="n">
-        <v>0.111185157503579</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U522" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA522" t="inlineStr">
@@ -75670,7 +75670,7 @@
       </c>
       <c r="AS522" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT522" t="n">
@@ -75755,17 +75755,17 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
@@ -75784,17 +75784,17 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="O523" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="R523" t="n">
-        <v>0.1972639891192531</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U523" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA523" t="inlineStr">
@@ -75814,7 +75814,7 @@
       </c>
       <c r="AS523" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT523" t="n">
@@ -75899,17 +75899,17 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -75928,17 +75928,17 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="O524" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="R524" t="n">
-        <v>0.07531897766371483</v>
+        <v>0.1147717754875655</v>
       </c>
       <c r="U524" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA524" t="inlineStr">
@@ -75958,7 +75958,7 @@
       </c>
       <c r="AS524" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT524" t="n">
@@ -76043,17 +76043,17 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -76072,17 +76072,17 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="O525" t="n">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="R525" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.1960684497912576</v>
       </c>
       <c r="U525" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA525" t="inlineStr">
@@ -76102,7 +76102,7 @@
       </c>
       <c r="AS525" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT525" t="n">
@@ -76187,17 +76187,17 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -76216,17 +76216,17 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="O526" t="n">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="R526" t="n">
-        <v>0.2175881576951762</v>
+        <v>0.07651451699171029</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA526" t="inlineStr">
@@ -76246,7 +76246,7 @@
       </c>
       <c r="AS526" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT526" t="n">
@@ -76331,17 +76331,17 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -76360,17 +76360,17 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O527" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R527" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U527" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA527" t="inlineStr">
@@ -76390,7 +76390,7 @@
       </c>
       <c r="AS527" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT527" t="n">
@@ -76475,17 +76475,17 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -76504,17 +76504,17 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="O528" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="R528" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.2187836970231716</v>
       </c>
       <c r="U528" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA528" t="inlineStr">
@@ -76534,7 +76534,7 @@
       </c>
       <c r="AS528" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT528" t="n">
@@ -76619,17 +76619,17 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -76648,17 +76648,17 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>244</v>
+        <v>3</v>
       </c>
       <c r="O529" t="n">
-        <v>244</v>
+        <v>3</v>
       </c>
       <c r="R529" t="n">
-        <v>0.2917115960308955</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA529" t="inlineStr">
@@ -76678,7 +76678,7 @@
       </c>
       <c r="AS529" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT529" t="n">
@@ -76763,17 +76763,17 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -76792,17 +76792,17 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
       <c r="O530" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
       <c r="R530" t="n">
-        <v>0.1625933486073844</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U530" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA530" t="inlineStr">
@@ -76822,7 +76822,7 @@
       </c>
       <c r="AS530" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT530" t="n">
@@ -76907,17 +76907,17 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
@@ -76936,17 +76936,17 @@
         </is>
       </c>
       <c r="N531" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="O531" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="R531" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.3108402252788231</v>
       </c>
       <c r="U531" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA531" t="inlineStr">
@@ -76966,7 +76966,7 @@
       </c>
       <c r="AS531" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT531" t="n">
@@ -77051,17 +77051,17 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
@@ -77080,17 +77080,17 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="O532" t="n">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="R532" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.1697665845753572</v>
       </c>
       <c r="U532" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA532" t="inlineStr">
@@ -77110,7 +77110,7 @@
       </c>
       <c r="AS532" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT532" t="n">
@@ -77195,22 +77195,22 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -77224,17 +77224,17 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="O533" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="R533" t="n">
-        <v>0.04423495513583252</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U533" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA533" t="inlineStr">
@@ -77254,7 +77254,7 @@
       </c>
       <c r="AS533" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT533" t="n">
@@ -77339,17 +77339,17 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
@@ -77368,17 +77368,17 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="O534" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="R534" t="n">
-        <v>0.04543049446382799</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U534" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA534" t="inlineStr">
@@ -77398,7 +77398,7 @@
       </c>
       <c r="AS534" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT534" t="n">
@@ -77483,22 +77483,22 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -77512,17 +77512,17 @@
         </is>
       </c>
       <c r="N535" t="n">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="O535" t="n">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="R535" t="n">
-        <v>0.1829175171833074</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA535" t="inlineStr">
@@ -77542,7 +77542,7 @@
       </c>
       <c r="AS535" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT535" t="n">
@@ -77627,17 +77627,17 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
@@ -77656,17 +77656,17 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="O536" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="R536" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.04423495513583252</v>
       </c>
       <c r="U536" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA536" t="inlineStr">
@@ -77686,7 +77686,7 @@
       </c>
       <c r="AS536" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT536" t="n">
@@ -77771,17 +77771,17 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -77800,17 +77800,17 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
       <c r="O537" t="n">
-        <v>214</v>
+        <v>42</v>
       </c>
       <c r="R537" t="n">
-        <v>0.2558454161910313</v>
+        <v>0.05021265177580988</v>
       </c>
       <c r="U537" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA537" t="inlineStr">
@@ -77830,7 +77830,7 @@
       </c>
       <c r="AS537" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT537" t="n">
@@ -77915,22 +77915,22 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -77944,17 +77944,17 @@
         </is>
       </c>
       <c r="N538" t="n">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="O538" t="n">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="R538" t="n">
-        <v>0.022715247231914</v>
+        <v>0.1876996744952893</v>
       </c>
       <c r="U538" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA538" t="inlineStr">
@@ -77974,7 +77974,7 @@
       </c>
       <c r="AS538" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT538" t="n">
@@ -78016,6 +78016,438 @@
         </is>
       </c>
       <c r="BC538" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N539" t="n">
+        <v>8</v>
+      </c>
+      <c r="O539" t="n">
+        <v>8</v>
+      </c>
+      <c r="R539" t="n">
+        <v>0.009564314623963786</v>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO539" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP539" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS539" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AT539" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV539" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW539" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX539" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY539" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA539" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB539" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC539" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N540" t="n">
+        <v>217</v>
+      </c>
+      <c r="O540" t="n">
+        <v>217</v>
+      </c>
+      <c r="R540" t="n">
+        <v>0.2594320341750177</v>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO540" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP540" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS540" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AT540" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV540" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW540" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX540" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY540" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ540" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA540" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB540" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC540" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N541" t="n">
+        <v>19</v>
+      </c>
+      <c r="O541" t="n">
+        <v>19</v>
+      </c>
+      <c r="R541" t="n">
+        <v>0.022715247231914</v>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO541" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP541" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS541" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT541" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV541" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW541" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX541" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY541" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ541" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA541" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB541" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC541" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -78137,7 +78569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10">
@@ -78147,7 +78579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11">
@@ -78199,7 +78631,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61441</v>
+        <v>61660</v>
       </c>
     </row>
     <row r="16">

--- a/countries/de/2026-2029.xlsx
+++ b/countries/de/2026-2029.xlsx
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O55" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R55" t="n">
-        <v>0.09325206758364693</v>
+        <v>0.09444760691164239</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -20488,13 +20488,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O139" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R139" t="n">
-        <v>0.2175881576951762</v>
+        <v>0.2199792363511671</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -21208,13 +21208,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O144" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R144" t="n">
-        <v>0.1542245733114161</v>
+        <v>0.1530290339834206</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -26680,13 +26680,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O182" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R182" t="n">
-        <v>0.07292789900772388</v>
+        <v>0.07412343833571934</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -27976,13 +27976,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O191" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R191" t="n">
-        <v>0.2343257082871128</v>
+        <v>0.2331301689591173</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -28840,13 +28840,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O197" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R197" t="n">
-        <v>0.08368775295968314</v>
+        <v>0.08488329228767862</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
@@ -30856,13 +30856,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="O211" t="n">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="R211" t="n">
-        <v>1.783744677369246</v>
+        <v>1.786135756025237</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -31576,13 +31576,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R216" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -32872,13 +32872,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O225" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R225" t="n">
-        <v>0.2558454161910313</v>
+        <v>0.2546498768630359</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -37336,13 +37336,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="O256" t="n">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="R256" t="n">
-        <v>1.735923104249427</v>
+        <v>1.737118643577423</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
@@ -37480,13 +37480,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O257" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R257" t="n">
-        <v>0.07890559564770125</v>
+        <v>0.08010113497569672</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -41512,13 +41512,13 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O285" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R285" t="n">
-        <v>0.1948729104632622</v>
+        <v>0.1936773711352667</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
@@ -44392,13 +44392,13 @@
         </is>
       </c>
       <c r="N305" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O305" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R305" t="n">
-        <v>0.1422691800314613</v>
+        <v>0.1434647193594568</v>
       </c>
       <c r="U305" t="inlineStr">
         <is>
@@ -47704,13 +47704,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O328" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R328" t="n">
-        <v>0.2785606634229453</v>
+        <v>0.2797562027509408</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
@@ -51448,13 +51448,13 @@
         </is>
       </c>
       <c r="N354" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O354" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R354" t="n">
-        <v>0.3622484163826284</v>
+        <v>0.3634439557106239</v>
       </c>
       <c r="U354" t="inlineStr">
         <is>
@@ -52024,13 +52024,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O358" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R358" t="n">
-        <v>0.2235658543351535</v>
+        <v>0.224761393663149</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
@@ -52456,13 +52456,13 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O361" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R361" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U361" t="inlineStr">
         <is>
@@ -54040,13 +54040,13 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O372" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R372" t="n">
-        <v>0.3180134612467959</v>
+        <v>0.3168179219188005</v>
       </c>
       <c r="U372" t="inlineStr">
         <is>
@@ -54904,13 +54904,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O378" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="R378" t="n">
-        <v>0.4088744501744519</v>
+        <v>0.4112655288304429</v>
       </c>
       <c r="U378" t="inlineStr">
         <is>
@@ -56776,13 +56776,13 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="O391" t="n">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="R391" t="n">
-        <v>1.507575092602292</v>
+        <v>1.509966171258283</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
@@ -58648,13 +58648,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O404" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="R404" t="n">
-        <v>0.4638692592622436</v>
+        <v>0.4674558772462301</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -59800,13 +59800,13 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O412" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R412" t="n">
-        <v>0.07651451699171029</v>
+        <v>0.07890559564770125</v>
       </c>
       <c r="U412" t="inlineStr">
         <is>
@@ -60232,13 +60232,13 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O415" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R415" t="n">
-        <v>0.2307390903031264</v>
+        <v>0.2319346296311218</v>
       </c>
       <c r="U415" t="inlineStr">
         <is>
@@ -61096,13 +61096,13 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O421" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R421" t="n">
-        <v>0.1350959440634885</v>
+        <v>0.136291483391484</v>
       </c>
       <c r="U421" t="inlineStr">
         <is>
@@ -61672,13 +61672,13 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O425" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R425" t="n">
-        <v>0.06216804505576462</v>
+        <v>0.06336358438376009</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -62680,13 +62680,13 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O432" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R432" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U432" t="inlineStr">
         <is>
@@ -62968,13 +62968,13 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O434" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="R434" t="n">
-        <v>0.3287733151987552</v>
+        <v>0.3323599331827416</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
@@ -63400,13 +63400,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="O437" t="n">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="R437" t="n">
-        <v>1.423887339642609</v>
+        <v>1.432256114938577</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -65128,13 +65128,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="O449" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="R449" t="n">
-        <v>0.3981145962224927</v>
+        <v>0.401701214206479</v>
       </c>
       <c r="U449" t="inlineStr">
         <is>
@@ -65272,13 +65272,13 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O450" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R450" t="n">
-        <v>0.2068283037432169</v>
+        <v>0.2080238430712124</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
@@ -67000,13 +67000,13 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="O462" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="R462" t="n">
-        <v>1.031750440060094</v>
+        <v>1.032945979388089</v>
       </c>
       <c r="U462" t="inlineStr">
         <is>
@@ -67288,13 +67288,13 @@
         </is>
       </c>
       <c r="N464" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="O464" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R464" t="n">
-        <v>0.313231303934814</v>
+        <v>0.3108402252788231</v>
       </c>
       <c r="U464" t="inlineStr">
         <is>
@@ -67432,13 +67432,13 @@
         </is>
       </c>
       <c r="N465" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O465" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R465" t="n">
-        <v>0.1458557980154478</v>
+        <v>0.1470513373434432</v>
       </c>
       <c r="U465" t="inlineStr">
         <is>
@@ -67576,13 +67576,13 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O466" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R466" t="n">
-        <v>0.1446602586874523</v>
+        <v>0.1458557980154478</v>
       </c>
       <c r="U466" t="inlineStr">
         <is>
@@ -68008,13 +68008,13 @@
         </is>
       </c>
       <c r="N469" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O469" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R469" t="n">
-        <v>0.540383776253954</v>
+        <v>0.5415793155819495</v>
       </c>
       <c r="U469" t="inlineStr">
         <is>
@@ -68440,13 +68440,13 @@
         </is>
       </c>
       <c r="N472" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O472" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R472" t="n">
-        <v>0.007173235967972841</v>
+        <v>0.008368775295968314</v>
       </c>
       <c r="U472" t="inlineStr">
         <is>
@@ -69448,13 +69448,13 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>1105</v>
+        <v>1123</v>
       </c>
       <c r="O479" t="n">
-        <v>1105</v>
+        <v>1123</v>
       </c>
       <c r="R479" t="n">
-        <v>1.321070957434998</v>
+        <v>1.342590665338917</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
@@ -69736,13 +69736,13 @@
         </is>
       </c>
       <c r="N481" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O481" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="R481" t="n">
-        <v>0.07173235967972839</v>
+        <v>0.07531897766371483</v>
       </c>
       <c r="U481" t="inlineStr">
         <is>
@@ -71032,13 +71032,13 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="O490" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="R490" t="n">
-        <v>0.3598573377266375</v>
+        <v>0.3634439557106239</v>
       </c>
       <c r="U490" t="inlineStr">
         <is>
@@ -71176,13 +71176,13 @@
         </is>
       </c>
       <c r="N491" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O491" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R491" t="n">
-        <v>0.2140015397111897</v>
+        <v>0.2151970790391852</v>
       </c>
       <c r="U491" t="inlineStr">
         <is>
@@ -72040,13 +72040,13 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O497" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R497" t="n">
-        <v>0.09205652825565144</v>
+        <v>0.09325206758364693</v>
       </c>
       <c r="U497" t="inlineStr">
         <is>
@@ -72328,13 +72328,13 @@
         </is>
       </c>
       <c r="N499" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O499" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R499" t="n">
-        <v>0.0179330899199321</v>
+        <v>0.01912862924792757</v>
       </c>
       <c r="U499" t="inlineStr">
         <is>
@@ -72760,13 +72760,13 @@
         </is>
       </c>
       <c r="N502" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O502" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R502" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.02151970790391852</v>
       </c>
       <c r="U502" t="inlineStr">
         <is>
@@ -72904,13 +72904,13 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="O503" t="n">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="R503" t="n">
-        <v>1.09870064242784</v>
+        <v>1.099896181755835</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
@@ -73048,13 +73048,13 @@
         </is>
       </c>
       <c r="N504" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O504" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R504" t="n">
-        <v>0.04423495513583252</v>
+        <v>0.04303941580783704</v>
       </c>
       <c r="U504" t="inlineStr">
         <is>
@@ -73192,13 +73192,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O505" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R505" t="n">
-        <v>0.2893205173749046</v>
+        <v>0.2869294387189136</v>
       </c>
       <c r="U505" t="inlineStr">
         <is>
@@ -73336,13 +73336,13 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O506" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R506" t="n">
-        <v>0.1554201126394116</v>
+        <v>0.1530290339834206</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
@@ -73480,13 +73480,13 @@
         </is>
       </c>
       <c r="N507" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O507" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="R507" t="n">
-        <v>0.1052074608636017</v>
+        <v>0.1087940788475881</v>
       </c>
       <c r="U507" t="inlineStr">
         <is>
@@ -73768,13 +73768,13 @@
         </is>
       </c>
       <c r="N509" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O509" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R509" t="n">
-        <v>0.06455912371175557</v>
+        <v>0.06695020236774651</v>
       </c>
       <c r="U509" t="inlineStr">
         <is>
@@ -73912,13 +73912,13 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="O510" t="n">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="R510" t="n">
-        <v>0.4686514165742255</v>
+        <v>0.4746291132142029</v>
       </c>
       <c r="U510" t="inlineStr">
         <is>
@@ -74632,13 +74632,13 @@
         </is>
       </c>
       <c r="N515" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O515" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="R515" t="n">
-        <v>0.6611332483814968</v>
+        <v>0.6623287877094922</v>
       </c>
       <c r="U515" t="inlineStr">
         <is>
@@ -74891,17 +74891,17 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
@@ -74920,17 +74920,17 @@
         </is>
       </c>
       <c r="N517" t="n">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="O517" t="n">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="R517" t="n">
-        <v>0.3060580679668412</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U517" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_e5b87c80fee4668ef9fca38e47b4</t>
         </is>
       </c>
       <c r="AA517" t="inlineStr">
@@ -74950,7 +74950,7 @@
       </c>
       <c r="AS517" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_e5b87c80fee4668ef9fca38e47b4</t>
         </is>
       </c>
       <c r="AT517" t="n">
@@ -75035,17 +75035,17 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
@@ -75064,17 +75064,17 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>24</v>
+        <v>257</v>
       </c>
       <c r="O518" t="n">
-        <v>24</v>
+        <v>257</v>
       </c>
       <c r="R518" t="n">
-        <v>0.02869294387189136</v>
+        <v>0.3072536072948367</v>
       </c>
       <c r="U518" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA518" t="inlineStr">
@@ -75094,7 +75094,7 @@
       </c>
       <c r="AS518" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT518" t="n">
@@ -75179,22 +75179,22 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -75208,17 +75208,17 @@
         </is>
       </c>
       <c r="N519" t="n">
-        <v>829</v>
+        <v>24</v>
       </c>
       <c r="O519" t="n">
-        <v>829</v>
+        <v>24</v>
       </c>
       <c r="R519" t="n">
-        <v>0.9911021029082474</v>
+        <v>0.02869294387189136</v>
       </c>
       <c r="U519" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA519" t="inlineStr">
@@ -75238,7 +75238,7 @@
       </c>
       <c r="AS519" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT519" t="n">
@@ -75323,22 +75323,22 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -75352,17 +75352,17 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>43</v>
+        <v>885</v>
       </c>
       <c r="O520" t="n">
-        <v>43</v>
+        <v>885</v>
       </c>
       <c r="R520" t="n">
-        <v>0.05140819110380536</v>
+        <v>1.058052305275994</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA520" t="inlineStr">
@@ -75382,7 +75382,7 @@
       </c>
       <c r="AS520" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT520" t="n">
@@ -75467,17 +75467,17 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -75496,17 +75496,17 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O521" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R521" t="n">
-        <v>0.05738588774378273</v>
+        <v>0.05379926975979631</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA521" t="inlineStr">
@@ -75526,7 +75526,7 @@
       </c>
       <c r="AS521" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT521" t="n">
@@ -75611,22 +75611,22 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -75640,17 +75640,17 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="O522" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="R522" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.05858142707177819</v>
       </c>
       <c r="U522" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA522" t="inlineStr">
@@ -75670,7 +75670,7 @@
       </c>
       <c r="AS522" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT522" t="n">
@@ -75755,22 +75755,22 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -75784,17 +75784,17 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O523" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R523" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U523" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA523" t="inlineStr">
@@ -75814,7 +75814,7 @@
       </c>
       <c r="AS523" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT523" t="n">
@@ -75899,17 +75899,17 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -75928,17 +75928,17 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="O524" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="R524" t="n">
-        <v>0.1147717754875655</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U524" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA524" t="inlineStr">
@@ -75958,7 +75958,7 @@
       </c>
       <c r="AS524" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT524" t="n">
@@ -76043,17 +76043,17 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -76072,17 +76072,17 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="O525" t="n">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="R525" t="n">
-        <v>0.1960684497912576</v>
+        <v>0.1219450114555383</v>
       </c>
       <c r="U525" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA525" t="inlineStr">
@@ -76102,7 +76102,7 @@
       </c>
       <c r="AS525" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT525" t="n">
@@ -76187,17 +76187,17 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -76216,17 +76216,17 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="O526" t="n">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="R526" t="n">
-        <v>0.07651451699171029</v>
+        <v>0.1960684497912576</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA526" t="inlineStr">
@@ -76246,7 +76246,7 @@
       </c>
       <c r="AS526" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT526" t="n">
@@ -76331,17 +76331,17 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -76360,17 +76360,17 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="O527" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="R527" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.08010113497569672</v>
       </c>
       <c r="U527" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA527" t="inlineStr">
@@ -76390,7 +76390,7 @@
       </c>
       <c r="AS527" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT527" t="n">
@@ -76475,17 +76475,17 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -76504,17 +76504,17 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="O528" t="n">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="R528" t="n">
-        <v>0.2187836970231716</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U528" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA528" t="inlineStr">
@@ -76534,7 +76534,7 @@
       </c>
       <c r="AS528" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT528" t="n">
@@ -76619,17 +76619,17 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -76648,17 +76648,17 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="O529" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="R529" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.2235658543351535</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA529" t="inlineStr">
@@ -76678,7 +76678,7 @@
       </c>
       <c r="AS529" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT529" t="n">
@@ -76763,17 +76763,17 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -76792,17 +76792,17 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R530" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U530" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA530" t="inlineStr">
@@ -76822,7 +76822,7 @@
       </c>
       <c r="AS530" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT530" t="n">
@@ -76907,17 +76907,17 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
@@ -76936,17 +76936,17 @@
         </is>
       </c>
       <c r="N531" t="n">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="O531" t="n">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="R531" t="n">
-        <v>0.3108402252788231</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U531" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA531" t="inlineStr">
@@ -76966,7 +76966,7 @@
       </c>
       <c r="AS531" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT531" t="n">
@@ -77051,17 +77051,17 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
@@ -77080,17 +77080,17 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>142</v>
+        <v>276</v>
       </c>
       <c r="O532" t="n">
-        <v>142</v>
+        <v>276</v>
       </c>
       <c r="R532" t="n">
-        <v>0.1697665845753572</v>
+        <v>0.3299688545267507</v>
       </c>
       <c r="U532" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA532" t="inlineStr">
@@ -77110,7 +77110,7 @@
       </c>
       <c r="AS532" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT532" t="n">
@@ -77195,17 +77195,17 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
@@ -77224,17 +77224,17 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="O533" t="n">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="R533" t="n">
-        <v>0.01195539327995473</v>
+        <v>0.1745487418873391</v>
       </c>
       <c r="U533" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA533" t="inlineStr">
@@ -77254,7 +77254,7 @@
       </c>
       <c r="AS533" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT533" t="n">
@@ -77339,17 +77339,17 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
@@ -77368,17 +77368,17 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O534" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R534" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U534" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA534" t="inlineStr">
@@ -77398,7 +77398,7 @@
       </c>
       <c r="AS534" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT534" t="n">
@@ -77483,17 +77483,17 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
@@ -77512,17 +77512,17 @@
         </is>
       </c>
       <c r="N535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O535" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R535" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA535" t="inlineStr">
@@ -77542,7 +77542,7 @@
       </c>
       <c r="AS535" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT535" t="n">
@@ -77627,22 +77627,22 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
@@ -77656,17 +77656,17 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="O536" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="R536" t="n">
-        <v>0.04423495513583252</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U536" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA536" t="inlineStr">
@@ -77686,7 +77686,7 @@
       </c>
       <c r="AS536" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT536" t="n">
@@ -77771,22 +77771,22 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -77800,17 +77800,17 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O537" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R537" t="n">
-        <v>0.05021265177580988</v>
+        <v>0.04423495513583252</v>
       </c>
       <c r="U537" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA537" t="inlineStr">
@@ -77830,7 +77830,7 @@
       </c>
       <c r="AS537" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT537" t="n">
@@ -77915,22 +77915,22 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -77944,17 +77944,17 @@
         </is>
       </c>
       <c r="N538" t="n">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="O538" t="n">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="R538" t="n">
-        <v>0.1876996744952893</v>
+        <v>0.05260373043180083</v>
       </c>
       <c r="U538" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA538" t="inlineStr">
@@ -77974,7 +77974,7 @@
       </c>
       <c r="AS538" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT538" t="n">
@@ -78059,22 +78059,22 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D165</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>阿米巴病</t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
@@ -78088,17 +78088,17 @@
         </is>
       </c>
       <c r="N539" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O539" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R539" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U539" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_d7ac02abbcc27669281630ed8f28</t>
         </is>
       </c>
       <c r="AA539" t="inlineStr">
@@ -78118,7 +78118,7 @@
       </c>
       <c r="AS539" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_d7ac02abbcc27669281630ed8f28</t>
         </is>
       </c>
       <c r="AT539" t="n">
@@ -78203,22 +78203,22 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -78232,17 +78232,17 @@
         </is>
       </c>
       <c r="N540" t="n">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="O540" t="n">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="R540" t="n">
-        <v>0.2594320341750177</v>
+        <v>0.1984595284472486</v>
       </c>
       <c r="U540" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA540" t="inlineStr">
@@ -78262,7 +78262,7 @@
       </c>
       <c r="AS540" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT540" t="n">
@@ -78347,22 +78347,22 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
@@ -78376,17 +78376,17 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O541" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R541" t="n">
-        <v>0.022715247231914</v>
+        <v>0.009564314623963786</v>
       </c>
       <c r="U541" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA541" t="inlineStr">
@@ -78406,7 +78406,7 @@
       </c>
       <c r="AS541" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT541" t="n">
@@ -78448,6 +78448,5622 @@
         </is>
       </c>
       <c r="BC541" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N542" t="n">
+        <v>220</v>
+      </c>
+      <c r="O542" t="n">
+        <v>220</v>
+      </c>
+      <c r="R542" t="n">
+        <v>0.2630186521590042</v>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO542" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP542" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS542" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AT542" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV542" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW542" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX542" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY542" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ542" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA542" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB542" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC542" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N543" t="n">
+        <v>19</v>
+      </c>
+      <c r="O543" t="n">
+        <v>19</v>
+      </c>
+      <c r="R543" t="n">
+        <v>0.022715247231914</v>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA543" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO543" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP543" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS543" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT543" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV543" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW543" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX543" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY543" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ543" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA543" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB543" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC543" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N544" t="n">
+        <v>935</v>
+      </c>
+      <c r="O544" t="n">
+        <v>935</v>
+      </c>
+      <c r="R544" t="n">
+        <v>1.117829271675768</v>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+        </is>
+      </c>
+      <c r="AA544" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO544" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP544" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS544" t="inlineStr">
+        <is>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+        </is>
+      </c>
+      <c r="AT544" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV544" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW544" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX544" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY544" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ544" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA544" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB544" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC544" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N545" t="n">
+        <v>30</v>
+      </c>
+      <c r="O545" t="n">
+        <v>30</v>
+      </c>
+      <c r="R545" t="n">
+        <v>0.0358661798398642</v>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+        </is>
+      </c>
+      <c r="AA545" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO545" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP545" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS545" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+        </is>
+      </c>
+      <c r="AT545" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV545" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW545" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX545" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY545" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ545" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA545" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB545" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC545" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N546" t="n">
+        <v>246</v>
+      </c>
+      <c r="O546" t="n">
+        <v>246</v>
+      </c>
+      <c r="R546" t="n">
+        <v>0.2941026746868864</v>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+        </is>
+      </c>
+      <c r="AA546" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO546" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP546" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS546" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+        </is>
+      </c>
+      <c r="AT546" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV546" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW546" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX546" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY546" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ546" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA546" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB546" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC546" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N547" t="n">
+        <v>122</v>
+      </c>
+      <c r="O547" t="n">
+        <v>122</v>
+      </c>
+      <c r="R547" t="n">
+        <v>0.1458557980154478</v>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+        </is>
+      </c>
+      <c r="AA547" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO547" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP547" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS547" t="inlineStr">
+        <is>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+        </is>
+      </c>
+      <c r="AT547" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV547" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW547" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX547" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY547" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ547" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA547" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB547" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC547" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N548" t="n">
+        <v>54</v>
+      </c>
+      <c r="O548" t="n">
+        <v>54</v>
+      </c>
+      <c r="R548" t="n">
+        <v>0.06455912371175557</v>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+        </is>
+      </c>
+      <c r="AA548" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO548" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP548" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS548" t="inlineStr">
+        <is>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+        </is>
+      </c>
+      <c r="AT548" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV548" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW548" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX548" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY548" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ548" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA548" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB548" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC548" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N549" t="n">
+        <v>1</v>
+      </c>
+      <c r="O549" t="n">
+        <v>1</v>
+      </c>
+      <c r="R549" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+        </is>
+      </c>
+      <c r="AA549" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO549" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP549" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS549" t="inlineStr">
+        <is>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+        </is>
+      </c>
+      <c r="AT549" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV549" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW549" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX549" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY549" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ549" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA549" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB549" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC549" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N550" t="n">
+        <v>40</v>
+      </c>
+      <c r="O550" t="n">
+        <v>40</v>
+      </c>
+      <c r="R550" t="n">
+        <v>0.04782157311981893</v>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+        </is>
+      </c>
+      <c r="AA550" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO550" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP550" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS550" t="inlineStr">
+        <is>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+        </is>
+      </c>
+      <c r="AT550" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV550" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW550" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX550" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY550" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ550" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA550" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB550" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC550" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N551" t="n">
+        <v>315</v>
+      </c>
+      <c r="O551" t="n">
+        <v>315</v>
+      </c>
+      <c r="R551" t="n">
+        <v>0.3765948883185741</v>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+        </is>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO551" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP551" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS551" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+        </is>
+      </c>
+      <c r="AT551" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV551" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW551" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX551" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY551" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ551" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA551" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB551" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC551" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N552" t="n">
+        <v>7</v>
+      </c>
+      <c r="O552" t="n">
+        <v>7</v>
+      </c>
+      <c r="R552" t="n">
+        <v>0.008368775295968314</v>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AA552" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO552" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP552" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS552" t="inlineStr">
+        <is>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+        </is>
+      </c>
+      <c r="AT552" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV552" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW552" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX552" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY552" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ552" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA552" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB552" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC552" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N553" t="n">
+        <v>2</v>
+      </c>
+      <c r="O553" t="n">
+        <v>2</v>
+      </c>
+      <c r="R553" t="n">
+        <v>0.002391078655990946</v>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+        </is>
+      </c>
+      <c r="AA553" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO553" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP553" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS553" t="inlineStr">
+        <is>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+        </is>
+      </c>
+      <c r="AT553" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV553" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW553" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX553" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY553" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ553" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA553" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB553" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC553" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N554" t="n">
+        <v>14</v>
+      </c>
+      <c r="O554" t="n">
+        <v>14</v>
+      </c>
+      <c r="R554" t="n">
+        <v>0.01673755059193663</v>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+        </is>
+      </c>
+      <c r="AA554" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO554" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP554" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS554" t="inlineStr">
+        <is>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+        </is>
+      </c>
+      <c r="AT554" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV554" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW554" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX554" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY554" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ554" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA554" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB554" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC554" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N555" t="n">
+        <v>482</v>
+      </c>
+      <c r="O555" t="n">
+        <v>482</v>
+      </c>
+      <c r="R555" t="n">
+        <v>0.5762499560938181</v>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+        </is>
+      </c>
+      <c r="AA555" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO555" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP555" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS555" t="inlineStr">
+        <is>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+        </is>
+      </c>
+      <c r="AT555" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV555" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW555" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX555" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY555" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ555" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA555" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB555" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC555" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N556" t="n">
+        <v>7</v>
+      </c>
+      <c r="O556" t="n">
+        <v>7</v>
+      </c>
+      <c r="R556" t="n">
+        <v>0.008368775295968314</v>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+        </is>
+      </c>
+      <c r="AA556" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO556" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP556" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS556" t="inlineStr">
+        <is>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+        </is>
+      </c>
+      <c r="AT556" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV556" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW556" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX556" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY556" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ556" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA556" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB556" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC556" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N557" t="n">
+        <v>1</v>
+      </c>
+      <c r="O557" t="n">
+        <v>1</v>
+      </c>
+      <c r="R557" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO557" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP557" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS557" t="inlineStr">
+        <is>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+        </is>
+      </c>
+      <c r="AT557" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV557" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW557" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX557" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY557" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ557" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA557" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB557" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC557" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N558" t="n">
+        <v>201</v>
+      </c>
+      <c r="O558" t="n">
+        <v>201</v>
+      </c>
+      <c r="R558" t="n">
+        <v>0.2403034049270902</v>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+        </is>
+      </c>
+      <c r="AA558" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO558" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP558" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS558" t="inlineStr">
+        <is>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+        </is>
+      </c>
+      <c r="AT558" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV558" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW558" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX558" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY558" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ558" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA558" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB558" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC558" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N559" t="n">
+        <v>26</v>
+      </c>
+      <c r="O559" t="n">
+        <v>26</v>
+      </c>
+      <c r="R559" t="n">
+        <v>0.03108402252788231</v>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+        </is>
+      </c>
+      <c r="AA559" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO559" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP559" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS559" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+        </is>
+      </c>
+      <c r="AT559" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV559" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW559" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX559" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY559" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ559" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA559" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB559" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC559" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N560" t="n">
+        <v>529</v>
+      </c>
+      <c r="O560" t="n">
+        <v>529</v>
+      </c>
+      <c r="R560" t="n">
+        <v>0.6324403045096054</v>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+        </is>
+      </c>
+      <c r="AA560" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO560" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP560" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS560" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+        </is>
+      </c>
+      <c r="AT560" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV560" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW560" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX560" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY560" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ560" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA560" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB560" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC560" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N561" t="n">
+        <v>29</v>
+      </c>
+      <c r="O561" t="n">
+        <v>29</v>
+      </c>
+      <c r="R561" t="n">
+        <v>0.03467064051186873</v>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+        </is>
+      </c>
+      <c r="AA561" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO561" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP561" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS561" t="inlineStr">
+        <is>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+        </is>
+      </c>
+      <c r="AT561" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV561" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW561" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX561" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY561" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ561" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA561" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB561" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC561" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N562" t="n">
+        <v>21</v>
+      </c>
+      <c r="O562" t="n">
+        <v>21</v>
+      </c>
+      <c r="R562" t="n">
+        <v>0.02510632588790494</v>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+        </is>
+      </c>
+      <c r="AA562" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO562" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP562" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS562" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+        </is>
+      </c>
+      <c r="AT562" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV562" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW562" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX562" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY562" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ562" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA562" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB562" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC562" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>D103</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Hemolytic uremic syndrome</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>溶血性尿毒症综合征</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N563" t="n">
+        <v>1</v>
+      </c>
+      <c r="O563" t="n">
+        <v>1</v>
+      </c>
+      <c r="R563" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+        </is>
+      </c>
+      <c r="AA563" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO563" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP563" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS563" t="inlineStr">
+        <is>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+        </is>
+      </c>
+      <c r="AT563" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV563" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW563" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX563" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY563" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ563" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA563" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB563" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC563" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N564" t="n">
+        <v>71</v>
+      </c>
+      <c r="O564" t="n">
+        <v>71</v>
+      </c>
+      <c r="R564" t="n">
+        <v>0.08488329228767862</v>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+        </is>
+      </c>
+      <c r="AA564" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO564" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP564" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS564" t="inlineStr">
+        <is>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+        </is>
+      </c>
+      <c r="AT564" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV564" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW564" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX564" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY564" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ564" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA564" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB564" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC564" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N565" t="n">
+        <v>160</v>
+      </c>
+      <c r="O565" t="n">
+        <v>160</v>
+      </c>
+      <c r="R565" t="n">
+        <v>0.1912862924792757</v>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+        </is>
+      </c>
+      <c r="AA565" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO565" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP565" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS565" t="inlineStr">
+        <is>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+        </is>
+      </c>
+      <c r="AT565" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV565" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW565" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX565" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY565" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ565" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA565" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB565" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC565" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N566" t="n">
+        <v>53</v>
+      </c>
+      <c r="O566" t="n">
+        <v>53</v>
+      </c>
+      <c r="R566" t="n">
+        <v>0.06336358438376009</v>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+        </is>
+      </c>
+      <c r="AA566" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO566" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP566" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS566" t="inlineStr">
+        <is>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+        </is>
+      </c>
+      <c r="AT566" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV566" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW566" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX566" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY566" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ566" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA566" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB566" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC566" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N567" t="n">
+        <v>14</v>
+      </c>
+      <c r="O567" t="n">
+        <v>14</v>
+      </c>
+      <c r="R567" t="n">
+        <v>0.01673755059193663</v>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+        </is>
+      </c>
+      <c r="AA567" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO567" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP567" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS567" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+        </is>
+      </c>
+      <c r="AT567" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV567" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW567" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX567" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY567" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ567" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA567" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB567" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC567" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N568" t="n">
+        <v>151</v>
+      </c>
+      <c r="O568" t="n">
+        <v>151</v>
+      </c>
+      <c r="R568" t="n">
+        <v>0.1805264385273165</v>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+        </is>
+      </c>
+      <c r="AA568" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO568" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP568" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS568" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+        </is>
+      </c>
+      <c r="AT568" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV568" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW568" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX568" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY568" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ568" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA568" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB568" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC568" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N569" t="n">
+        <v>1</v>
+      </c>
+      <c r="O569" t="n">
+        <v>1</v>
+      </c>
+      <c r="R569" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+        </is>
+      </c>
+      <c r="AA569" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO569" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP569" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS569" t="inlineStr">
+        <is>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+        </is>
+      </c>
+      <c r="AT569" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV569" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW569" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX569" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY569" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ569" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA569" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB569" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC569" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N570" t="n">
+        <v>163</v>
+      </c>
+      <c r="O570" t="n">
+        <v>163</v>
+      </c>
+      <c r="R570" t="n">
+        <v>0.1948729104632622</v>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+        </is>
+      </c>
+      <c r="AA570" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO570" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP570" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS570" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+        </is>
+      </c>
+      <c r="AT570" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV570" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW570" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX570" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY570" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ570" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA570" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB570" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC570" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N571" t="n">
+        <v>78</v>
+      </c>
+      <c r="O571" t="n">
+        <v>78</v>
+      </c>
+      <c r="R571" t="n">
+        <v>0.09325206758364693</v>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+        </is>
+      </c>
+      <c r="AA571" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO571" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP571" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS571" t="inlineStr">
+        <is>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+        </is>
+      </c>
+      <c r="AT571" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV571" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW571" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX571" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY571" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ571" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA571" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB571" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC571" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N572" t="n">
+        <v>3</v>
+      </c>
+      <c r="O572" t="n">
+        <v>3</v>
+      </c>
+      <c r="R572" t="n">
+        <v>0.00358661798398642</v>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+        </is>
+      </c>
+      <c r="AA572" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO572" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP572" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS572" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+        </is>
+      </c>
+      <c r="AT572" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV572" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW572" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX572" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY572" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ572" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA572" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB572" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC572" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N573" t="n">
+        <v>1</v>
+      </c>
+      <c r="O573" t="n">
+        <v>1</v>
+      </c>
+      <c r="R573" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AA573" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO573" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP573" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS573" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AT573" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV573" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW573" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX573" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY573" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ573" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA573" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB573" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC573" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N574" t="n">
+        <v>25</v>
+      </c>
+      <c r="O574" t="n">
+        <v>25</v>
+      </c>
+      <c r="R574" t="n">
+        <v>0.02988848319988684</v>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+        </is>
+      </c>
+      <c r="AA574" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO574" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP574" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS574" t="inlineStr">
+        <is>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+        </is>
+      </c>
+      <c r="AT574" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV574" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW574" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX574" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY574" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ574" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA574" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB574" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC574" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N575" t="n">
+        <v>32</v>
+      </c>
+      <c r="O575" t="n">
+        <v>32</v>
+      </c>
+      <c r="R575" t="n">
+        <v>0.03825725849585514</v>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+        </is>
+      </c>
+      <c r="AA575" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO575" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP575" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS575" t="inlineStr">
+        <is>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+        </is>
+      </c>
+      <c r="AT575" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV575" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW575" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX575" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY575" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ575" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA575" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB575" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC575" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N576" t="n">
+        <v>159</v>
+      </c>
+      <c r="O576" t="n">
+        <v>159</v>
+      </c>
+      <c r="R576" t="n">
+        <v>0.1900907531512803</v>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+        </is>
+      </c>
+      <c r="AA576" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO576" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP576" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS576" t="inlineStr">
+        <is>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+        </is>
+      </c>
+      <c r="AT576" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV576" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW576" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX576" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY576" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ576" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA576" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB576" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC576" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N577" t="n">
+        <v>6</v>
+      </c>
+      <c r="O577" t="n">
+        <v>6</v>
+      </c>
+      <c r="R577" t="n">
+        <v>0.007173235967972841</v>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AA577" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO577" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP577" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS577" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AT577" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV577" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW577" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX577" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY577" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ577" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA577" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB577" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC577" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N578" t="n">
+        <v>147</v>
+      </c>
+      <c r="O578" t="n">
+        <v>147</v>
+      </c>
+      <c r="R578" t="n">
+        <v>0.1757442812153346</v>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AA578" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO578" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP578" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS578" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AT578" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV578" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW578" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX578" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY578" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ578" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA578" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB578" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC578" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N579" t="n">
+        <v>1</v>
+      </c>
+      <c r="O579" t="n">
+        <v>1</v>
+      </c>
+      <c r="R579" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+        </is>
+      </c>
+      <c r="AA579" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO579" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP579" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS579" t="inlineStr">
+        <is>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+        </is>
+      </c>
+      <c r="AT579" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV579" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW579" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX579" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY579" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ579" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA579" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB579" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC579" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N580" t="n">
+        <v>22</v>
+      </c>
+      <c r="O580" t="n">
+        <v>22</v>
+      </c>
+      <c r="R580" t="n">
+        <v>0.02630186521590041</v>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA580" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO580" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP580" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS580" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT580" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV580" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW580" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX580" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY580" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ580" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA580" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB580" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC580" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -78486,7 +84102,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -78569,7 +84185,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>540</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10">
@@ -78579,7 +84195,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>540</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11">
@@ -78631,7 +84247,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61660</v>
+        <v>65993</v>
       </c>
     </row>
     <row r="16">

--- a/countries/de/2026-2029.xlsx
+++ b/countries/de/2026-2029.xlsx
@@ -7240,13 +7240,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O47" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1458557980154478</v>
+        <v>0.1470513373434432</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -10120,13 +10120,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="O67" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="R67" t="n">
-        <v>2.025243621624332</v>
+        <v>2.026439160952327</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -14584,13 +14584,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O98" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R98" t="n">
-        <v>0.1530290339834206</v>
+        <v>0.1518334946554251</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -17176,13 +17176,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="O116" t="n">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="R116" t="n">
-        <v>2.198596824183675</v>
+        <v>2.202183442167662</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O137" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R137" t="n">
-        <v>0.3323599331827416</v>
+        <v>0.3335554725107371</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -22648,13 +22648,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O154" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R154" t="n">
-        <v>0.2295435509751309</v>
+        <v>0.2307390903031264</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -23656,13 +23656,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="O161" t="n">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="R161" t="n">
-        <v>1.973835430520526</v>
+        <v>1.975030969848522</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -28840,13 +28840,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O197" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R197" t="n">
-        <v>0.08488329228767862</v>
+        <v>0.08607883161567409</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
@@ -30856,13 +30856,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="O211" t="n">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="R211" t="n">
-        <v>1.786135756025237</v>
+        <v>1.787331295353233</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -31576,13 +31576,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R216" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -35032,13 +35032,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O240" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R240" t="n">
-        <v>0.270191888126977</v>
+        <v>0.2713874274549725</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -39208,13 +39208,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O269" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R269" t="n">
-        <v>0.2438900229110766</v>
+        <v>0.245085562239072</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -40504,13 +40504,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O278" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R278" t="n">
-        <v>0.01195539327995473</v>
+        <v>0.01315093260795021</v>
       </c>
       <c r="U278" t="inlineStr">
         <is>
@@ -41944,13 +41944,13 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O288" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R288" t="n">
-        <v>0.06695020236774651</v>
+        <v>0.06934128102373746</v>
       </c>
       <c r="U288" t="inlineStr">
         <is>
@@ -43672,13 +43672,13 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O300" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R300" t="n">
-        <v>0.08368775295968314</v>
+        <v>0.08488329228767862</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
@@ -47704,13 +47704,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O328" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R328" t="n">
-        <v>0.2797562027509408</v>
+        <v>0.2809517420789363</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
@@ -47848,13 +47848,13 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O329" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R329" t="n">
-        <v>0.1494424159994342</v>
+        <v>0.1518334946554251</v>
       </c>
       <c r="U329" t="inlineStr">
         <is>
@@ -48424,13 +48424,13 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O333" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R333" t="n">
-        <v>0.08010113497569672</v>
+        <v>0.0812966743036922</v>
       </c>
       <c r="U333" t="inlineStr">
         <is>
@@ -50152,13 +50152,13 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="O345" t="n">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="R345" t="n">
-        <v>1.657017508601726</v>
+        <v>1.659408587257717</v>
       </c>
       <c r="U345" t="inlineStr">
         <is>
@@ -53752,13 +53752,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O370" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R370" t="n">
-        <v>0.4865845064941577</v>
+        <v>0.4877800458221531</v>
       </c>
       <c r="U370" t="inlineStr">
         <is>
@@ -54184,13 +54184,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O373" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R373" t="n">
-        <v>0.1530290339834206</v>
+        <v>0.1542245733114161</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -54760,13 +54760,13 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O377" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R377" t="n">
-        <v>0.07651451699171029</v>
+        <v>0.07771005631970578</v>
       </c>
       <c r="U377" t="inlineStr">
         <is>
@@ -56776,13 +56776,13 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="O391" t="n">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="R391" t="n">
-        <v>1.509966171258283</v>
+        <v>1.511161710586278</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
@@ -58216,13 +58216,13 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O401" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R401" t="n">
-        <v>0.315622382590805</v>
+        <v>0.3168179219188005</v>
       </c>
       <c r="U401" t="inlineStr">
         <is>
@@ -58648,13 +58648,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O404" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R404" t="n">
-        <v>0.4674558772462301</v>
+        <v>0.4686514165742255</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -61096,13 +61096,13 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O421" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R421" t="n">
-        <v>0.136291483391484</v>
+        <v>0.1386825620474749</v>
       </c>
       <c r="U421" t="inlineStr">
         <is>
@@ -61240,13 +61240,13 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O422" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R422" t="n">
-        <v>0.1279227080955156</v>
+        <v>0.1291182474235111</v>
       </c>
       <c r="U422" t="inlineStr">
         <is>
@@ -61672,13 +61672,13 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O425" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R425" t="n">
-        <v>0.06336358438376009</v>
+        <v>0.06216804505576462</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
@@ -61816,13 +61816,13 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O426" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="R426" t="n">
-        <v>0.4566960232942708</v>
+        <v>0.4578915626222663</v>
       </c>
       <c r="U426" t="inlineStr">
         <is>
@@ -62968,13 +62968,13 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O434" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R434" t="n">
-        <v>0.3323599331827416</v>
+        <v>0.3311643938547461</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
@@ -63400,13 +63400,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="O437" t="n">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="R437" t="n">
-        <v>1.432256114938577</v>
+        <v>1.434647193594568</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -66424,13 +66424,13 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O458" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R458" t="n">
-        <v>0.01195539327995473</v>
+        <v>0.01315093260795021</v>
       </c>
       <c r="U458" t="inlineStr">
         <is>
@@ -67576,13 +67576,13 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O466" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R466" t="n">
-        <v>0.1458557980154478</v>
+        <v>0.1446602586874523</v>
       </c>
       <c r="U466" t="inlineStr">
         <is>
@@ -69448,13 +69448,13 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="O479" t="n">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="R479" t="n">
-        <v>1.342590665338917</v>
+        <v>1.349763901306889</v>
       </c>
       <c r="U479" t="inlineStr">
         <is>
@@ -70600,13 +70600,13 @@
         </is>
       </c>
       <c r="N487" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O487" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R487" t="n">
-        <v>0.2498677195510539</v>
+        <v>0.2510632588790494</v>
       </c>
       <c r="U487" t="inlineStr">
         <is>
@@ -71032,13 +71032,13 @@
         </is>
       </c>
       <c r="N490" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O490" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="R490" t="n">
-        <v>0.3634439557106239</v>
+        <v>0.3658350343666149</v>
       </c>
       <c r="U490" t="inlineStr">
         <is>
@@ -72040,13 +72040,13 @@
         </is>
       </c>
       <c r="N497" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O497" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R497" t="n">
-        <v>0.09325206758364693</v>
+        <v>0.09444760691164239</v>
       </c>
       <c r="U497" t="inlineStr">
         <is>
@@ -72184,13 +72184,13 @@
         </is>
       </c>
       <c r="N498" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O498" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R498" t="n">
-        <v>0.1948729104632622</v>
+        <v>0.1972639891192531</v>
       </c>
       <c r="U498" t="inlineStr">
         <is>
@@ -72472,13 +72472,13 @@
         </is>
       </c>
       <c r="N500" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O500" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R500" t="n">
-        <v>0.245085562239072</v>
+        <v>0.2462811015670675</v>
       </c>
       <c r="U500" t="inlineStr">
         <is>
@@ -72904,13 +72904,13 @@
         </is>
       </c>
       <c r="N503" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="O503" t="n">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="R503" t="n">
-        <v>1.099896181755835</v>
+        <v>1.103482799739822</v>
       </c>
       <c r="U503" t="inlineStr">
         <is>
@@ -73192,13 +73192,13 @@
         </is>
       </c>
       <c r="N505" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O505" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R505" t="n">
-        <v>0.2869294387189136</v>
+        <v>0.2857338993909181</v>
       </c>
       <c r="U505" t="inlineStr">
         <is>
@@ -73336,13 +73336,13 @@
         </is>
       </c>
       <c r="N506" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O506" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R506" t="n">
-        <v>0.1530290339834206</v>
+        <v>0.1542245733114161</v>
       </c>
       <c r="U506" t="inlineStr">
         <is>
@@ -73912,13 +73912,13 @@
         </is>
       </c>
       <c r="N510" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="O510" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="R510" t="n">
-        <v>0.4746291132142029</v>
+        <v>0.4794112705261849</v>
       </c>
       <c r="U510" t="inlineStr">
         <is>
@@ -75064,13 +75064,13 @@
         </is>
       </c>
       <c r="N518" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O518" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R518" t="n">
-        <v>0.3072536072948367</v>
+        <v>0.3096446859508276</v>
       </c>
       <c r="U518" t="inlineStr">
         <is>
@@ -75352,13 +75352,13 @@
         </is>
       </c>
       <c r="N520" t="n">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="O520" t="n">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="R520" t="n">
-        <v>1.058052305275994</v>
+        <v>1.107069417723809</v>
       </c>
       <c r="U520" t="inlineStr">
         <is>
@@ -75496,13 +75496,13 @@
         </is>
       </c>
       <c r="N521" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O521" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R521" t="n">
-        <v>0.05379926975979631</v>
+        <v>0.05499480908779177</v>
       </c>
       <c r="U521" t="inlineStr">
         <is>
@@ -75640,13 +75640,13 @@
         </is>
       </c>
       <c r="N522" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O522" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="R522" t="n">
-        <v>0.05858142707177819</v>
+        <v>0.06216804505576462</v>
       </c>
       <c r="U522" t="inlineStr">
         <is>
@@ -75755,22 +75755,22 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Hantavirus infection</t>
+          <t>Candida auris infection</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>汉坦病毒感染</t>
+          <t>耳念珠菌感染</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -75784,17 +75784,17 @@
         </is>
       </c>
       <c r="N523" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O523" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R523" t="n">
-        <v>0.004782157311981893</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U523" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
         </is>
       </c>
       <c r="AA523" t="inlineStr">
@@ -75814,7 +75814,7 @@
       </c>
       <c r="AS523" t="inlineStr">
         <is>
-          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
+          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
         </is>
       </c>
       <c r="AT523" t="n">
@@ -75899,22 +75899,22 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -75928,17 +75928,17 @@
         </is>
       </c>
       <c r="N524" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O524" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R524" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.004782157311981893</v>
       </c>
       <c r="U524" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA524" t="inlineStr">
@@ -75958,7 +75958,7 @@
       </c>
       <c r="AS524" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT524" t="n">
@@ -76043,17 +76043,17 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
@@ -76072,17 +76072,17 @@
         </is>
       </c>
       <c r="N525" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="O525" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="R525" t="n">
-        <v>0.1219450114555383</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U525" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA525" t="inlineStr">
@@ -76102,7 +76102,7 @@
       </c>
       <c r="AS525" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT525" t="n">
@@ -76187,17 +76187,17 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -76216,17 +76216,17 @@
         </is>
       </c>
       <c r="N526" t="n">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="O526" t="n">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="R526" t="n">
-        <v>0.1960684497912576</v>
+        <v>0.1279227080955156</v>
       </c>
       <c r="U526" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA526" t="inlineStr">
@@ -76246,7 +76246,7 @@
       </c>
       <c r="AS526" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT526" t="n">
@@ -76331,17 +76331,17 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
@@ -76360,17 +76360,17 @@
         </is>
       </c>
       <c r="N527" t="n">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="O527" t="n">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="R527" t="n">
-        <v>0.08010113497569672</v>
+        <v>0.1960684497912576</v>
       </c>
       <c r="U527" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA527" t="inlineStr">
@@ -76390,7 +76390,7 @@
       </c>
       <c r="AS527" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT527" t="n">
@@ -76475,17 +76475,17 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -76504,17 +76504,17 @@
         </is>
       </c>
       <c r="N528" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="O528" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="R528" t="n">
-        <v>0.01434647193594568</v>
+        <v>0.08249221363168767</v>
       </c>
       <c r="U528" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA528" t="inlineStr">
@@ -76534,7 +76534,7 @@
       </c>
       <c r="AS528" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT528" t="n">
@@ -76619,17 +76619,17 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -76648,17 +76648,17 @@
         </is>
       </c>
       <c r="N529" t="n">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="O529" t="n">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="R529" t="n">
-        <v>0.2235658543351535</v>
+        <v>0.01434647193594568</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA529" t="inlineStr">
@@ -76678,7 +76678,7 @@
       </c>
       <c r="AS529" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT529" t="n">
@@ -76763,17 +76763,17 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>Meningococcal disease</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>脑膜炎球菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
@@ -76792,17 +76792,17 @@
         </is>
       </c>
       <c r="N530" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="O530" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="R530" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.224761393663149</v>
       </c>
       <c r="U530" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA530" t="inlineStr">
@@ -76822,7 +76822,7 @@
       </c>
       <c r="AS530" t="inlineStr">
         <is>
-          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT530" t="n">
@@ -76907,17 +76907,17 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Meningococcal disease</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>脑膜炎球菌病</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
@@ -76946,7 +76946,7 @@
       </c>
       <c r="U531" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AA531" t="inlineStr">
@@ -76966,7 +76966,7 @@
       </c>
       <c r="AS531" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
         </is>
       </c>
       <c r="AT531" t="n">
@@ -77051,17 +77051,17 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
@@ -77080,17 +77080,17 @@
         </is>
       </c>
       <c r="N532" t="n">
-        <v>276</v>
+        <v>3</v>
       </c>
       <c r="O532" t="n">
-        <v>276</v>
+        <v>3</v>
       </c>
       <c r="R532" t="n">
-        <v>0.3299688545267507</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U532" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA532" t="inlineStr">
@@ -77110,7 +77110,7 @@
       </c>
       <c r="AS532" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT532" t="n">
@@ -77195,17 +77195,17 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
@@ -77224,17 +77224,17 @@
         </is>
       </c>
       <c r="N533" t="n">
-        <v>146</v>
+        <v>286</v>
       </c>
       <c r="O533" t="n">
-        <v>146</v>
+        <v>286</v>
       </c>
       <c r="R533" t="n">
-        <v>0.1745487418873391</v>
+        <v>0.3419242478067054</v>
       </c>
       <c r="U533" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA533" t="inlineStr">
@@ -77254,7 +77254,7 @@
       </c>
       <c r="AS533" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT533" t="n">
@@ -77339,17 +77339,17 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
@@ -77368,17 +77368,17 @@
         </is>
       </c>
       <c r="N534" t="n">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="O534" t="n">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="R534" t="n">
-        <v>0.01195539327995473</v>
+        <v>0.1757442812153346</v>
       </c>
       <c r="U534" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA534" t="inlineStr">
@@ -77398,7 +77398,7 @@
       </c>
       <c r="AS534" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT534" t="n">
@@ -77483,17 +77483,17 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>伤寒</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
@@ -77512,17 +77512,17 @@
         </is>
       </c>
       <c r="N535" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O535" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R535" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.01195539327995473</v>
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA535" t="inlineStr">
@@ -77542,7 +77542,7 @@
       </c>
       <c r="AS535" t="inlineStr">
         <is>
-          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT535" t="n">
@@ -77627,17 +77627,17 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
@@ -77656,17 +77656,17 @@
         </is>
       </c>
       <c r="N536" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O536" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R536" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U536" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA536" t="inlineStr">
@@ -77686,7 +77686,7 @@
       </c>
       <c r="AS536" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT536" t="n">
@@ -77771,22 +77771,22 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -77800,17 +77800,17 @@
         </is>
       </c>
       <c r="N537" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="O537" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="R537" t="n">
-        <v>0.04423495513583252</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U537" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA537" t="inlineStr">
@@ -77830,7 +77830,7 @@
       </c>
       <c r="AS537" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT537" t="n">
@@ -77915,22 +77915,22 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>West Nile virus</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>西尼罗病毒</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -77944,17 +77944,17 @@
         </is>
       </c>
       <c r="N538" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="O538" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="R538" t="n">
-        <v>0.05260373043180083</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U538" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AA538" t="inlineStr">
@@ -77974,7 +77974,7 @@
       </c>
       <c r="AS538" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_bbdd653bfa640555b27f82fd1353</t>
         </is>
       </c>
       <c r="AT538" t="n">
@@ -78059,22 +78059,22 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>D165</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>阿米巴病</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
@@ -78088,17 +78088,17 @@
         </is>
       </c>
       <c r="N539" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="O539" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="R539" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.04423495513583252</v>
       </c>
       <c r="U539" t="inlineStr">
         <is>
-          <t>HOLD_DE_d7ac02abbcc27669281630ed8f28</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA539" t="inlineStr">
@@ -78118,7 +78118,7 @@
       </c>
       <c r="AS539" t="inlineStr">
         <is>
-          <t>HOLD_DE_d7ac02abbcc27669281630ed8f28</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT539" t="n">
@@ -78203,22 +78203,22 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -78232,17 +78232,17 @@
         </is>
       </c>
       <c r="N540" t="n">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="O540" t="n">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="R540" t="n">
-        <v>0.1984595284472486</v>
+        <v>0.05260373043180083</v>
       </c>
       <c r="U540" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA540" t="inlineStr">
@@ -78262,7 +78262,7 @@
       </c>
       <c r="AS540" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT540" t="n">
@@ -78347,22 +78347,22 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D165</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>阿米巴病</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
@@ -78376,17 +78376,17 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O541" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R541" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U541" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_d7ac02abbcc27669281630ed8f28</t>
         </is>
       </c>
       <c r="AA541" t="inlineStr">
@@ -78406,7 +78406,7 @@
       </c>
       <c r="AS541" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_d7ac02abbcc27669281630ed8f28</t>
         </is>
       </c>
       <c r="AT541" t="n">
@@ -78491,22 +78491,22 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D199</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Rotavirus infection</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>轮状病毒感染</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
@@ -78520,17 +78520,17 @@
         </is>
       </c>
       <c r="N542" t="n">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="O542" t="n">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="R542" t="n">
-        <v>0.2630186521590042</v>
+        <v>0.1984595284472486</v>
       </c>
       <c r="U542" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AA542" t="inlineStr">
@@ -78550,7 +78550,7 @@
       </c>
       <c r="AS542" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
         </is>
       </c>
       <c r="AT542" t="n">
@@ -78635,22 +78635,22 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -78664,17 +78664,17 @@
         </is>
       </c>
       <c r="N543" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O543" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="R543" t="n">
-        <v>0.022715247231914</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U543" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AA543" t="inlineStr">
@@ -78694,7 +78694,7 @@
       </c>
       <c r="AS543" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
         </is>
       </c>
       <c r="AT543" t="n">
@@ -78779,27 +78779,27 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D227</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
         </is>
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
@@ -78808,17 +78808,17 @@
         </is>
       </c>
       <c r="N544" t="n">
-        <v>935</v>
+        <v>220</v>
       </c>
       <c r="O544" t="n">
-        <v>935</v>
+        <v>220</v>
       </c>
       <c r="R544" t="n">
-        <v>1.117829271675768</v>
+        <v>0.2630186521590042</v>
       </c>
       <c r="U544" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AA544" t="inlineStr">
@@ -78838,7 +78838,7 @@
       </c>
       <c r="AS544" t="inlineStr">
         <is>
-          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
         </is>
       </c>
       <c r="AT544" t="n">
@@ -78923,27 +78923,27 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D234</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>副伤寒</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
@@ -78952,17 +78952,17 @@
         </is>
       </c>
       <c r="N545" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O545" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R545" t="n">
-        <v>0.0358661798398642</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U545" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AA545" t="inlineStr">
@@ -78982,7 +78982,7 @@
       </c>
       <c r="AS545" t="inlineStr">
         <is>
-          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
         </is>
       </c>
       <c r="AT545" t="n">
@@ -79067,27 +79067,27 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>D008</t>
+          <t>D236</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>Hepatitis B</t>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>乙型肝炎</t>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
@@ -79096,17 +79096,17 @@
         </is>
       </c>
       <c r="N546" t="n">
-        <v>246</v>
+        <v>19</v>
       </c>
       <c r="O546" t="n">
-        <v>246</v>
+        <v>19</v>
       </c>
       <c r="R546" t="n">
-        <v>0.2941026746868864</v>
+        <v>0.022715247231914</v>
       </c>
       <c r="U546" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AA546" t="inlineStr">
@@ -79126,7 +79126,7 @@
       </c>
       <c r="AS546" t="inlineStr">
         <is>
-          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
         </is>
       </c>
       <c r="AT546" t="n">
@@ -79211,17 +79211,17 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>D009</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>Hepatitis C</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>丙型肝炎</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
@@ -79240,17 +79240,17 @@
         </is>
       </c>
       <c r="N547" t="n">
-        <v>122</v>
+        <v>1009</v>
       </c>
       <c r="O547" t="n">
-        <v>122</v>
+        <v>1009</v>
       </c>
       <c r="R547" t="n">
-        <v>0.1458557980154478</v>
+        <v>1.206299181947433</v>
       </c>
       <c r="U547" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AA547" t="inlineStr">
@@ -79270,7 +79270,7 @@
       </c>
       <c r="AS547" t="inlineStr">
         <is>
-          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
+          <t>HOLD_DE_254d1e1533c2313cd38064c471e8</t>
         </is>
       </c>
       <c r="AT547" t="n">
@@ -79355,17 +79355,17 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
@@ -79384,17 +79384,17 @@
         </is>
       </c>
       <c r="N548" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="O548" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="R548" t="n">
-        <v>0.06455912371175557</v>
+        <v>0.04184387647984157</v>
       </c>
       <c r="U548" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AA548" t="inlineStr">
@@ -79414,7 +79414,7 @@
       </c>
       <c r="AS548" t="inlineStr">
         <is>
-          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
+          <t>HOLD_DE_a24da742c3570a7186ddc81fe39d</t>
         </is>
       </c>
       <c r="AT548" t="n">
@@ -79499,17 +79499,17 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
@@ -79528,17 +79528,17 @@
         </is>
       </c>
       <c r="N549" t="n">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="O549" t="n">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="R549" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.315622382590805</v>
       </c>
       <c r="U549" t="inlineStr">
         <is>
-          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AA549" t="inlineStr">
@@ -79558,7 +79558,7 @@
       </c>
       <c r="AS549" t="inlineStr">
         <is>
-          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+          <t>HOLD_DE_3fe4070a01910244ac558ce89feb</t>
         </is>
       </c>
       <c r="AT549" t="n">
@@ -79643,22 +79643,22 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
@@ -79672,17 +79672,17 @@
         </is>
       </c>
       <c r="N550" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="O550" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="R550" t="n">
-        <v>0.04782157311981893</v>
+        <v>0.156615651967407</v>
       </c>
       <c r="U550" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AA550" t="inlineStr">
@@ -79702,7 +79702,7 @@
       </c>
       <c r="AS550" t="inlineStr">
         <is>
-          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+          <t>HOLD_DE_58b36fad94e3f55b6f553ce94f61</t>
         </is>
       </c>
       <c r="AT550" t="n">
@@ -79787,22 +79787,22 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -79816,17 +79816,17 @@
         </is>
       </c>
       <c r="N551" t="n">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="O551" t="n">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="R551" t="n">
-        <v>0.3765948883185741</v>
+        <v>0.07173235967972839</v>
       </c>
       <c r="U551" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AA551" t="inlineStr">
@@ -79846,7 +79846,7 @@
       </c>
       <c r="AS551" t="inlineStr">
         <is>
-          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+          <t>HOLD_DE_560e9fa27cdd32ad9a1d28cd0b0d</t>
         </is>
       </c>
       <c r="AT551" t="n">
@@ -79931,22 +79931,22 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>D031</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>Scarlet fever</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>猩红热</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -79960,17 +79960,17 @@
         </is>
       </c>
       <c r="N552" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O552" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R552" t="n">
-        <v>0.008368775295968314</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U552" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
         </is>
       </c>
       <c r="AA552" t="inlineStr">
@@ -79990,7 +79990,7 @@
       </c>
       <c r="AS552" t="inlineStr">
         <is>
-          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
         </is>
       </c>
       <c r="AT552" t="n">
@@ -80075,17 +80075,17 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K553" t="inlineStr">
@@ -80104,17 +80104,17 @@
         </is>
       </c>
       <c r="N553" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="O553" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="R553" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.05260373043180083</v>
       </c>
       <c r="U553" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AA553" t="inlineStr">
@@ -80134,7 +80134,7 @@
       </c>
       <c r="AS553" t="inlineStr">
         <is>
-          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT553" t="n">
@@ -80219,22 +80219,22 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
@@ -80248,17 +80248,17 @@
         </is>
       </c>
       <c r="N554" t="n">
-        <v>14</v>
+        <v>364</v>
       </c>
       <c r="O554" t="n">
-        <v>14</v>
+        <v>364</v>
       </c>
       <c r="R554" t="n">
-        <v>0.01673755059193663</v>
+        <v>0.4351763153903523</v>
       </c>
       <c r="U554" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AA554" t="inlineStr">
@@ -80278,7 +80278,7 @@
       </c>
       <c r="AS554" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
         </is>
       </c>
       <c r="AT554" t="n">
@@ -80363,22 +80363,22 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D031</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Scarlet fever</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>猩红热</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
@@ -80392,17 +80392,17 @@
         </is>
       </c>
       <c r="N555" t="n">
-        <v>482</v>
+        <v>7</v>
       </c>
       <c r="O555" t="n">
-        <v>482</v>
+        <v>7</v>
       </c>
       <c r="R555" t="n">
-        <v>0.5762499560938181</v>
+        <v>0.008368775295968314</v>
       </c>
       <c r="U555" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AA555" t="inlineStr">
@@ -80422,7 +80422,7 @@
       </c>
       <c r="AS555" t="inlineStr">
         <is>
-          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
+          <t>HOLD_DE_c4a11116520e85cee113bf27f857</t>
         </is>
       </c>
       <c r="AT555" t="n">
@@ -80507,22 +80507,22 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>D039</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>流行性腮腺炎</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
@@ -80536,17 +80536,17 @@
         </is>
       </c>
       <c r="N556" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O556" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R556" t="n">
-        <v>0.008368775295968314</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U556" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AA556" t="inlineStr">
@@ -80566,7 +80566,7 @@
       </c>
       <c r="AS556" t="inlineStr">
         <is>
-          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
+          <t>HOLD_DE_74d512ad41eaf3e22d516cca8020</t>
         </is>
       </c>
       <c r="AT556" t="n">
@@ -80651,22 +80651,22 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
@@ -80680,17 +80680,17 @@
         </is>
       </c>
       <c r="N557" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O557" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R557" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.01912862924792757</v>
       </c>
       <c r="U557" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AA557" t="inlineStr">
@@ -80710,7 +80710,7 @@
       </c>
       <c r="AS557" t="inlineStr">
         <is>
-          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
+          <t>HOLD_DE_ad052d1085b7281c5a415cb1f8fe</t>
         </is>
       </c>
       <c r="AT557" t="n">
@@ -80795,17 +80795,17 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
@@ -80824,17 +80824,17 @@
         </is>
       </c>
       <c r="N558" t="n">
-        <v>201</v>
+        <v>513</v>
       </c>
       <c r="O558" t="n">
-        <v>201</v>
+        <v>513</v>
       </c>
       <c r="R558" t="n">
-        <v>0.2403034049270902</v>
+        <v>0.6133116752616778</v>
       </c>
       <c r="U558" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AA558" t="inlineStr">
@@ -80854,7 +80854,7 @@
       </c>
       <c r="AS558" t="inlineStr">
         <is>
-          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
+          <t>HOLD_DE_7f5db8a8b4bbb456aed459172dc8</t>
         </is>
       </c>
       <c r="AT558" t="n">
@@ -80939,17 +80939,17 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>D065</t>
+          <t>D039</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Monkeypox</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>猴痘</t>
+          <t>流行性腮腺炎</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -80968,17 +80968,17 @@
         </is>
       </c>
       <c r="N559" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="O559" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="R559" t="n">
-        <v>0.03108402252788231</v>
+        <v>0.008368775295968314</v>
       </c>
       <c r="U559" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AA559" t="inlineStr">
@@ -80998,7 +80998,7 @@
       </c>
       <c r="AS559" t="inlineStr">
         <is>
-          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
+          <t>HOLD_DE_0bf12d70d32e8f6a2cc183cc1b99</t>
         </is>
       </c>
       <c r="AT559" t="n">
@@ -81083,22 +81083,22 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
@@ -81112,17 +81112,17 @@
         </is>
       </c>
       <c r="N560" t="n">
-        <v>529</v>
+        <v>1</v>
       </c>
       <c r="O560" t="n">
-        <v>529</v>
+        <v>1</v>
       </c>
       <c r="R560" t="n">
-        <v>0.6324403045096054</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U560" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AA560" t="inlineStr">
@@ -81142,7 +81142,7 @@
       </c>
       <c r="AS560" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
+          <t>HOLD_DE_29cd3daa11958d9c56ae3fe31136</t>
         </is>
       </c>
       <c r="AT560" t="n">
@@ -81227,22 +81227,22 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>D096</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>隐孢子虫病</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
@@ -81256,17 +81256,17 @@
         </is>
       </c>
       <c r="N561" t="n">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="O561" t="n">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="R561" t="n">
-        <v>0.03467064051186873</v>
+        <v>0.2558454161910313</v>
       </c>
       <c r="U561" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AA561" t="inlineStr">
@@ -81286,7 +81286,7 @@
       </c>
       <c r="AS561" t="inlineStr">
         <is>
-          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
+          <t>HOLD_DE_05d6c78e659357672953aebf8f89</t>
         </is>
       </c>
       <c r="AT561" t="n">
@@ -81371,22 +81371,22 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>D099</t>
+          <t>D065</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>Giardiasis</t>
+          <t>Monkeypox</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>贾第虫病</t>
+          <t>猴痘</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
@@ -81400,17 +81400,17 @@
         </is>
       </c>
       <c r="N562" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O562" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R562" t="n">
-        <v>0.02510632588790494</v>
+        <v>0.03706171916785967</v>
       </c>
       <c r="U562" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AA562" t="inlineStr">
@@ -81430,7 +81430,7 @@
       </c>
       <c r="AS562" t="inlineStr">
         <is>
-          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
+          <t>HOLD_DE_6d498fe2f8fff0e559a9778cf771</t>
         </is>
       </c>
       <c r="AT562" t="n">
@@ -81515,17 +81515,17 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>Hemolytic uremic syndrome</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>溶血性尿毒症综合征</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -81544,17 +81544,17 @@
         </is>
       </c>
       <c r="N563" t="n">
-        <v>1</v>
+        <v>660</v>
       </c>
       <c r="O563" t="n">
-        <v>1</v>
+        <v>660</v>
       </c>
       <c r="R563" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.7890559564770124</v>
       </c>
       <c r="U563" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AA563" t="inlineStr">
@@ -81574,7 +81574,7 @@
       </c>
       <c r="AS563" t="inlineStr">
         <is>
-          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
+          <t>HOLD_DE_bcf3ec79b1fa22e487fecbdd29cb</t>
         </is>
       </c>
       <c r="AT563" t="n">
@@ -81659,22 +81659,22 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D096</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>隐孢子虫病</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -81688,17 +81688,17 @@
         </is>
       </c>
       <c r="N564" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="O564" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="R564" t="n">
-        <v>0.08488329228767862</v>
+        <v>0.04184387647984157</v>
       </c>
       <c r="U564" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AA564" t="inlineStr">
@@ -81718,7 +81718,7 @@
       </c>
       <c r="AS564" t="inlineStr">
         <is>
-          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
+          <t>HOLD_DE_141fbc63db3a3fc81063e7f242e6</t>
         </is>
       </c>
       <c r="AT564" t="n">
@@ -81803,22 +81803,22 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D099</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>贾第虫病</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -81832,17 +81832,17 @@
         </is>
       </c>
       <c r="N565" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="O565" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="R565" t="n">
-        <v>0.1912862924792757</v>
+        <v>0.03227956185587778</v>
       </c>
       <c r="U565" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AA565" t="inlineStr">
@@ -81862,7 +81862,7 @@
       </c>
       <c r="AS565" t="inlineStr">
         <is>
-          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
+          <t>HOLD_DE_e5f12cc63c1550ced86113ed9668</t>
         </is>
       </c>
       <c r="AT565" t="n">
@@ -81947,22 +81947,22 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Hantavirus infection</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>汉坦病毒感染</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -81976,17 +81976,17 @@
         </is>
       </c>
       <c r="N566" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="O566" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="R566" t="n">
-        <v>0.06336358438376009</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U566" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AA566" t="inlineStr">
@@ -82006,7 +82006,7 @@
       </c>
       <c r="AS566" t="inlineStr">
         <is>
-          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
+          <t>HOLD_DE_5cd9254a79f73f7e76719209af51</t>
         </is>
       </c>
       <c r="AT566" t="n">
@@ -82091,17 +82091,17 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Hemolytic uremic syndrome</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>溶血性尿毒症综合征</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
@@ -82120,17 +82120,17 @@
         </is>
       </c>
       <c r="N567" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O567" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R567" t="n">
-        <v>0.01673755059193663</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U567" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AA567" t="inlineStr">
@@ -82150,7 +82150,7 @@
       </c>
       <c r="AS567" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_DE_a61a288370164339f3a7983800cd</t>
         </is>
       </c>
       <c r="AT567" t="n">
@@ -82235,17 +82235,17 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
@@ -82264,17 +82264,17 @@
         </is>
       </c>
       <c r="N568" t="n">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="O568" t="n">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="R568" t="n">
-        <v>0.1805264385273165</v>
+        <v>0.1099896181755835</v>
       </c>
       <c r="U568" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AA568" t="inlineStr">
@@ -82294,7 +82294,7 @@
       </c>
       <c r="AS568" t="inlineStr">
         <is>
-          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
+          <t>HOLD_DE_295316a229986b9959d2b9e07dab</t>
         </is>
       </c>
       <c r="AT568" t="n">
@@ -82379,17 +82379,17 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
@@ -82408,17 +82408,17 @@
         </is>
       </c>
       <c r="N569" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="O569" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="R569" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.2032416857592305</v>
       </c>
       <c r="U569" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AA569" t="inlineStr">
@@ -82438,7 +82438,7 @@
       </c>
       <c r="AS569" t="inlineStr">
         <is>
-          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
+          <t>HOLD_DE_86c6a86499a31ba0f180631d65d1</t>
         </is>
       </c>
       <c r="AT569" t="n">
@@ -82523,17 +82523,17 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
@@ -82552,17 +82552,17 @@
         </is>
       </c>
       <c r="N570" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="O570" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="R570" t="n">
-        <v>0.1948729104632622</v>
+        <v>0.07053682035173293</v>
       </c>
       <c r="U570" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AA570" t="inlineStr">
@@ -82582,7 +82582,7 @@
       </c>
       <c r="AS570" t="inlineStr">
         <is>
-          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
+          <t>HOLD_DE_d79d74d6e3f0785d9f599cb1b651</t>
         </is>
       </c>
       <c r="AT570" t="n">
@@ -82667,17 +82667,17 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
@@ -82696,17 +82696,17 @@
         </is>
       </c>
       <c r="N571" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="O571" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="R571" t="n">
-        <v>0.09325206758364693</v>
+        <v>0.01673755059193663</v>
       </c>
       <c r="U571" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA571" t="inlineStr">
@@ -82726,7 +82726,7 @@
       </c>
       <c r="AS571" t="inlineStr">
         <is>
-          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT571" t="n">
@@ -82811,17 +82811,17 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K572" t="inlineStr">
@@ -82840,17 +82840,17 @@
         </is>
       </c>
       <c r="N572" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="O572" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="R572" t="n">
-        <v>0.00358661798398642</v>
+        <v>0.1900907531512803</v>
       </c>
       <c r="U572" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AA572" t="inlineStr">
@@ -82870,7 +82870,7 @@
       </c>
       <c r="AS572" t="inlineStr">
         <is>
-          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
+          <t>HOLD_DE_b250db3ee9361ea08d0baa333747</t>
         </is>
       </c>
       <c r="AT572" t="n">
@@ -82955,17 +82955,17 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Vibriosis</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>弧菌病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
@@ -82994,7 +82994,7 @@
       </c>
       <c r="U573" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AA573" t="inlineStr">
@@ -83014,7 +83014,7 @@
       </c>
       <c r="AS573" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_DE_4ea6e71b5e9b20f8d58a1d7a049f</t>
         </is>
       </c>
       <c r="AT573" t="n">
@@ -83099,22 +83099,22 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>D142</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>Respiratory syncytial virus infection (RSV)</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>呼吸道合胞病毒感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
@@ -83128,17 +83128,17 @@
         </is>
       </c>
       <c r="N574" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="O574" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="R574" t="n">
-        <v>0.02988848319988684</v>
+        <v>0.2498677195510539</v>
       </c>
       <c r="U574" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AA574" t="inlineStr">
@@ -83158,7 +83158,7 @@
       </c>
       <c r="AS574" t="inlineStr">
         <is>
-          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
+          <t>HOLD_DE_b577741583987e73a68c7b256222</t>
         </is>
       </c>
       <c r="AT574" t="n">
@@ -83243,17 +83243,17 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>D155</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>耶尔森菌病</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K575" t="inlineStr">
@@ -83272,17 +83272,17 @@
         </is>
       </c>
       <c r="N575" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="O575" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="R575" t="n">
-        <v>0.03825725849585514</v>
+        <v>0.1087940788475881</v>
       </c>
       <c r="U575" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AA575" t="inlineStr">
@@ -83302,7 +83302,7 @@
       </c>
       <c r="AS575" t="inlineStr">
         <is>
-          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
+          <t>HOLD_DE_059854ba4ccf7917ff23b547178c</t>
         </is>
       </c>
       <c r="AT575" t="n">
@@ -83387,22 +83387,22 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>D199</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>Rotavirus infection</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>轮状病毒感染</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
@@ -83416,17 +83416,17 @@
         </is>
       </c>
       <c r="N576" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
       <c r="O576" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
       <c r="R576" t="n">
-        <v>0.1900907531512803</v>
+        <v>0.00358661798398642</v>
       </c>
       <c r="U576" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AA576" t="inlineStr">
@@ -83446,7 +83446,7 @@
       </c>
       <c r="AS576" t="inlineStr">
         <is>
-          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+          <t>HOLD_DE_b849fa63b7ae6fabb95bdf916fe8</t>
         </is>
       </c>
       <c r="AT576" t="n">
@@ -83531,22 +83531,22 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>伤寒</t>
         </is>
       </c>
       <c r="K577" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L577" t="inlineStr">
@@ -83560,17 +83560,17 @@
         </is>
       </c>
       <c r="N577" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O577" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R577" t="n">
-        <v>0.007173235967972841</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U577" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AA577" t="inlineStr">
@@ -83590,7 +83590,7 @@
       </c>
       <c r="AS577" t="inlineStr">
         <is>
-          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+          <t>HOLD_DE_cd1ba4c777ff5793402d1adae771</t>
         </is>
       </c>
       <c r="AT577" t="n">
@@ -83675,17 +83675,17 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>D227</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>Carbapenem-resistant Enterobacterales infection</t>
+          <t>Vibriosis</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+          <t>弧菌病</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
@@ -83704,17 +83704,17 @@
         </is>
       </c>
       <c r="N578" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="O578" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="R578" t="n">
-        <v>0.1757442812153346</v>
+        <v>0.001195539327995473</v>
       </c>
       <c r="U578" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA578" t="inlineStr">
@@ -83734,7 +83734,7 @@
       </c>
       <c r="AS578" t="inlineStr">
         <is>
-          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT578" t="n">
@@ -83819,22 +83819,22 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>D234</t>
+          <t>D142</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Respiratory syncytial virus infection (RSV)</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>副伤寒</t>
+          <t>呼吸道合胞病毒感染</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -83848,17 +83848,17 @@
         </is>
       </c>
       <c r="N579" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O579" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R579" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.02988848319988684</v>
       </c>
       <c r="U579" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AA579" t="inlineStr">
@@ -83878,7 +83878,7 @@
       </c>
       <c r="AS579" t="inlineStr">
         <is>
-          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+          <t>HOLD_DE_26519904c83fe8dc106484ae7d9c</t>
         </is>
       </c>
       <c r="AT579" t="n">
@@ -83963,17 +83963,17 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>D236</t>
+          <t>D155</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+          <t>耶尔森菌病</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
@@ -83992,17 +83992,17 @@
         </is>
       </c>
       <c r="N580" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="O580" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="R580" t="n">
-        <v>0.02630186521590041</v>
+        <v>0.04303941580783704</v>
       </c>
       <c r="U580" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AA580" t="inlineStr">
@@ -84022,7 +84022,7 @@
       </c>
       <c r="AS580" t="inlineStr">
         <is>
-          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+          <t>HOLD_DE_f8a42d099ba513454344dfcd2d5b</t>
         </is>
       </c>
       <c r="AT580" t="n">
@@ -84064,6 +84064,726 @@
         </is>
       </c>
       <c r="BC580" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N581" t="n">
+        <v>196</v>
+      </c>
+      <c r="O581" t="n">
+        <v>196</v>
+      </c>
+      <c r="R581" t="n">
+        <v>0.2343257082871128</v>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+        </is>
+      </c>
+      <c r="AA581" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO581" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP581" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS581" t="inlineStr">
+        <is>
+          <t>HOLD_DE_52a585aee0ab7be71a4aa362be02</t>
+        </is>
+      </c>
+      <c r="AT581" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV581" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW581" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX581" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY581" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ581" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA581" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB581" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC581" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N582" t="n">
+        <v>9</v>
+      </c>
+      <c r="O582" t="n">
+        <v>9</v>
+      </c>
+      <c r="R582" t="n">
+        <v>0.01075985395195926</v>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AA582" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO582" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP582" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS582" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e35abc87a6dbbcbd594d5232c594</t>
+        </is>
+      </c>
+      <c r="AT582" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV582" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW582" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX582" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY582" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ582" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA582" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB582" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC582" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N583" t="n">
+        <v>172</v>
+      </c>
+      <c r="O583" t="n">
+        <v>172</v>
+      </c>
+      <c r="R583" t="n">
+        <v>0.2056327644152214</v>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AA583" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO583" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP583" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS583" t="inlineStr">
+        <is>
+          <t>HOLD_DE_3059f17f5d9a83da53708e7a0f25</t>
+        </is>
+      </c>
+      <c r="AT583" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV583" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW583" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX583" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY583" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ583" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA583" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB583" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC583" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N584" t="n">
+        <v>2</v>
+      </c>
+      <c r="O584" t="n">
+        <v>2</v>
+      </c>
+      <c r="R584" t="n">
+        <v>0.002391078655990946</v>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+        </is>
+      </c>
+      <c r="AA584" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO584" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP584" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS584" t="inlineStr">
+        <is>
+          <t>HOLD_DE_ad719d2726b8d2f22f4647a5f85a</t>
+        </is>
+      </c>
+      <c r="AT584" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV584" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW584" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX584" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY584" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ584" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA584" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB584" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC584" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N585" t="n">
+        <v>25</v>
+      </c>
+      <c r="O585" t="n">
+        <v>25</v>
+      </c>
+      <c r="R585" t="n">
+        <v>0.02988848319988684</v>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA585" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO585" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP585" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS585" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT585" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV585" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW585" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX585" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY585" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ585" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA585" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB585" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC585" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -84185,7 +84905,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10">
@@ -84195,7 +84915,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11">
@@ -84247,7 +84967,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65993</v>
+        <v>66656</v>
       </c>
     </row>
     <row r="16">
